--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>511317</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.295500010251999</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.287000000476837</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.295500010251999</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.291500002145767</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>140197</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.287000000476837</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.289000004529953</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.287000000476837</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>240167</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.288500010967255</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>395905</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.295500010251999</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.287499994039536</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.295500010251999</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>109486</v>
+        <v>123733</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.284999996423721</v>
+        <v>0.28549998998642</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.280000001192093</v>
+        <v>0.279500007629395</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.283499985933304</v>
+        <v>0.28549998998642</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.280000001192093</v>
+        <v>0.282000005245209</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>1323989</v>
+        <v>109486</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.298500001430511</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.28150001168251</v>
+        <v>0.280000001192093</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.28150001168251</v>
+        <v>0.283499985933304</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.293999999761581</v>
+        <v>0.280000001192093</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>743383</v>
+        <v>1323989</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.298000007867813</v>
+        <v>0.298500001430511</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.287999987602234</v>
+        <v>0.28150001168251</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.294999986886978</v>
+        <v>0.28150001168251</v>
       </c>
       <c r="F2717" t="n">
-        <v>0.294999986886978</v>
+        <v>0.293999999761581</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>237737</v>
+        <v>743383</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.296999990940094</v>
+        <v>0.298000007867813</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.290499985218048</v>
+        <v>0.287999987602234</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.293999999761581</v>
+        <v>0.294999986886978</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.296000003814697</v>
+        <v>0.294999986886978</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>511317</v>
+        <v>237737</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.295500010251999</v>
+        <v>0.296999990940094</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.287000000476837</v>
+        <v>0.290499985218048</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.295500010251999</v>
+        <v>0.293999999761581</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.291500002145767</v>
+        <v>0.296000003814697</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>140197</v>
+        <v>511317</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.28999999165535</v>
+        <v>0.295500010251999</v>
       </c>
       <c r="D2720" t="n">
         <v>0.287000000476837</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.289000004529953</v>
+        <v>0.295500010251999</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.287000000476837</v>
+        <v>0.291500002145767</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>240167</v>
+        <v>140197</v>
       </c>
       <c r="C2721" t="n">
         <v>0.28999999165535</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.284999996423721</v>
+        <v>0.287000000476837</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.288500010967255</v>
+        <v>0.289000004529953</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.28999999165535</v>
+        <v>0.287000000476837</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>395905</v>
+        <v>240167</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.295500010251999</v>
+        <v>0.28999999165535</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.287499994039536</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="E2722" t="n">
+        <v>0.288500010967255</v>
+      </c>
+      <c r="F2722" t="n">
         <v>0.28999999165535</v>
       </c>
-      <c r="F2722" t="n">
-        <v>0.295500010251999</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>173099</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.294999986886978</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.293999999761581</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67819237709045</v>
+        <v>3.67819261550903</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599781036377</v>
+        <v>3.59599804878235</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4932553768158</v>
+        <v>3.49325513839722</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G11" t="n">
-        <v>3.39985275268555</v>
+        <v>3.39985299110413</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4278736114502</v>
+        <v>3.42787384986877</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.43160939216614</v>
+        <v>3.43160963058472</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062359809875</v>
+        <v>3.36062383651733</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G21" t="n">
-        <v>3.3269989490509</v>
+        <v>3.32699871063232</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G24" t="n">
-        <v>3.22425556182861</v>
+        <v>3.22425580024719</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2578809261322</v>
+        <v>3.25788068771362</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>2.64329195022583</v>
+        <v>2.64329218864441</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405595779419</v>
+        <v>2.77405548095703</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45835494995117</v>
+        <v>2.45835518836975</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.4919798374176</v>
+        <v>2.49198007583618</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604193687439</v>
+        <v>2.57604217529297</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395945549011</v>
+        <v>2.46395921707153</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G41" t="n">
-        <v>2.79460430145264</v>
+        <v>2.79460406303406</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G42" t="n">
-        <v>2.77592349052429</v>
+        <v>2.77592372894287</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G45" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61527109146118</v>
+        <v>2.61527132987976</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G54" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065333366394</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G60" t="n">
-        <v>2.63768768310547</v>
+        <v>2.63768792152405</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G64" t="n">
-        <v>2.58164644241333</v>
+        <v>2.58164620399475</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>2.64889621734619</v>
+        <v>2.64889597892761</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G67" t="n">
-        <v>2.4994523525238</v>
+        <v>2.49945259094238</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>2.44714641571045</v>
+        <v>2.44714665412903</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.6264796257019</v>
+        <v>2.62647986412048</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.6264796257019</v>
+        <v>2.62647986412048</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065333366394</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>2.61527109146118</v>
+        <v>2.61527132987976</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702820777893</v>
+        <v>2.64702844619751</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G84" t="n">
-        <v>2.62834787368774</v>
+        <v>2.62834763526917</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263223648071</v>
+        <v>2.65263247489929</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G87" t="n">
-        <v>2.62087559700012</v>
+        <v>2.62087535858154</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>2.62461137771606</v>
+        <v>2.62461161613464</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066040992737</v>
+        <v>2.51066017150879</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.5517578125</v>
+        <v>2.55175757408142</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538246154785</v>
+        <v>2.58538269996643</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098672866821</v>
+        <v>2.59098649024963</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702820777893</v>
+        <v>2.64702844619751</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.74487447738647</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.74487447738647</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G102" t="n">
-        <v>2.80777764320374</v>
+        <v>2.80777740478516</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G106" t="n">
-        <v>2.93358445167542</v>
+        <v>2.93358421325684</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92595958709717</v>
+        <v>2.92595934867859</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>2.87068104743958</v>
+        <v>2.870680809021</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91071009635925</v>
+        <v>2.91071033477783</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G121" t="n">
-        <v>2.89546084403992</v>
+        <v>2.8954610824585</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760096549988</v>
+        <v>2.56760120391846</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.4780113697052</v>
+        <v>2.47801113128662</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G143" t="n">
-        <v>2.60381841659546</v>
+        <v>2.60381817817688</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64003491401672</v>
+        <v>2.6400351524353</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G154" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220456123352</v>
+        <v>2.35220432281494</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220456123352</v>
+        <v>2.35220432281494</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.1749312877655</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.1749312877655</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399309158325</v>
+        <v>2.19399333000183</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.213054895401</v>
+        <v>2.21305465698242</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G182" t="n">
-        <v>2.12727737426758</v>
+        <v>2.12727761268616</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484318733215</v>
+        <v>2.05484294891357</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724808692932</v>
+        <v>2.08724784851074</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.0624680519104</v>
+        <v>2.06246781349182</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956452846527</v>
+        <v>1.99956440925598</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765849113464</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G192" t="n">
-        <v>1.98812758922577</v>
+        <v>1.98812747001648</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193978309631</v>
+        <v>1.99193966388702</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G199" t="n">
-        <v>1.92713046073914</v>
+        <v>1.92713057994843</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96144151687622</v>
+        <v>1.96144139766693</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616250038147</v>
+        <v>1.90616261959076</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803936958313</v>
+        <v>1.86803948879242</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185168266296</v>
+        <v>1.87185156345367</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803936958313</v>
+        <v>1.86803948879242</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G217" t="n">
-        <v>1.85469627380371</v>
+        <v>1.85469615459442</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038521766663</v>
+        <v>1.82038533687592</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G221" t="n">
-        <v>1.8022768497467</v>
+        <v>1.80227673053741</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>1.81561982631683</v>
+        <v>1.81561994552612</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179286956787</v>
+        <v>1.79179275035858</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179286956787</v>
+        <v>1.79179275035858</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G235" t="n">
-        <v>1.75081026554108</v>
+        <v>1.75081038475037</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G236" t="n">
-        <v>1.77559053897858</v>
+        <v>1.77559041976929</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509179592133</v>
+        <v>1.74509191513062</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G238" t="n">
-        <v>1.77082514762878</v>
+        <v>1.77082502841949</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273106575012</v>
+        <v>1.77273118495941</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372843265533</v>
+        <v>1.83372831344604</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.877570271492</v>
+        <v>1.87757015228271</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616250038147</v>
+        <v>1.90616261959076</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G251" t="n">
-        <v>1.96144151687622</v>
+        <v>1.96144139766693</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674934387207</v>
+        <v>2.05674958229065</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437373161316</v>
+        <v>2.06437397003174</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G263" t="n">
-        <v>2.00909543037415</v>
+        <v>2.00909519195557</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="n">
-        <v>2.12727737426758</v>
+        <v>2.12727761268616</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G266" t="n">
-        <v>2.13108968734741</v>
+        <v>2.13108992576599</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334719657898</v>
+        <v>1.96334731578827</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.9347550868988</v>
+        <v>1.93475496768951</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193978309631</v>
+        <v>1.99193966388702</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765849113464</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330338478088</v>
+        <v>1.90330326557159</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.81561982631683</v>
+        <v>1.81561994552612</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G292" t="n">
-        <v>1.92713046073914</v>
+        <v>1.92713057994843</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.92141175270081</v>
+        <v>1.9214118719101</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G295" t="n">
-        <v>1.91950559616089</v>
+        <v>1.9195054769516</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G302" t="n">
-        <v>1.87280476093292</v>
+        <v>1.87280488014221</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471079826355</v>
+        <v>1.87471091747284</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G306" t="n">
-        <v>1.86994552612305</v>
+        <v>1.86994540691376</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.0491247177124</v>
+        <v>2.04912495613098</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.0624680519104</v>
+        <v>2.06246781349182</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645680427551</v>
+        <v>2.30645656585693</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G334" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G335" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938949584961</v>
+        <v>2.40938973426819</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>2.57331967353821</v>
+        <v>2.57331943511963</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058832168579</v>
+        <v>2.60058856010437</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806646347046</v>
+        <v>2.70806670188904</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715969085693</v>
+        <v>2.77715992927551</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.7291784286499</v>
+        <v>2.72917866706848</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514095306396</v>
+        <v>2.82514119148254</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.8980724811554</v>
+        <v>2.89807271957397</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363183021545</v>
+        <v>3.00363159179688</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757561683655</v>
+        <v>3.14757537841797</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343867301941</v>
+        <v>3.29343891143799</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818446159363</v>
+        <v>3.22818422317505</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596053123474</v>
+        <v>3.18596076965332</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040165901184</v>
+        <v>3.08040189743042</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707249641418</v>
+        <v>3.20707225799561</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020296096802</v>
+        <v>3.18020272254944</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647616386414</v>
+        <v>3.50647592544556</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809077262878</v>
+        <v>3.46809101104736</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899802207947</v>
+        <v>3.39899778366089</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889831542969</v>
+        <v>3.44889855384827</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940769195557</v>
+        <v>3.57940745353699</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264340400696</v>
+        <v>3.69264364242554</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122725486755</v>
+        <v>3.63122749328613</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223373413086</v>
+        <v>3.51223397254944</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502921104431</v>
+        <v>2.49502944946289</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736464500427</v>
+        <v>2.86736440658569</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.84817218780518</v>
+        <v>2.8481719493866</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230889320374</v>
+        <v>2.70230865478516</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928367614746</v>
+        <v>2.86928391456604</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877477645874</v>
+        <v>2.73877453804016</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563829421997</v>
+        <v>2.57563805580139</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614719390869</v>
+        <v>2.70614743232727</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685550689697</v>
+        <v>2.73685526847839</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503546714783</v>
+        <v>2.68503570556641</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281803131104</v>
+        <v>2.83281779289246</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019092559814</v>
+        <v>2.80019068717957</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75029015541077</v>
+        <v>2.75028991699219</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978101730347</v>
+        <v>2.61978077888489</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301672935486</v>
+        <v>2.73301696777344</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735862731934</v>
+        <v>2.67735838890076</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190524101257</v>
+        <v>2.71190500259399</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.7042281627655</v>
+        <v>2.70422792434692</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.3721969127655</v>
+        <v>2.37219715118408</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>0.29449999332428</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>270279</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.294999986886978</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.291500002145767</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.291500002145767</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.291999995708466</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.291999995708466</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67819261550903</v>
+        <v>3.67819213867188</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599804878235</v>
+        <v>3.59599781036377</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655418395996</v>
+        <v>3.44655394554138</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.49325513839722</v>
+        <v>3.4932553768158</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>3.39798450469971</v>
+        <v>3.39798474311829</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G12" t="n">
-        <v>3.32886648178101</v>
+        <v>3.32886672019958</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.42787384986877</v>
+        <v>3.42787337303162</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G16" t="n">
-        <v>3.47083878517151</v>
+        <v>3.47083854675293</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062383651733</v>
+        <v>3.36062359809875</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.25788068771362</v>
+        <v>3.2578809261322</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96272873878479</v>
+        <v>2.96272850036621</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G27" t="n">
-        <v>2.6787850856781</v>
+        <v>2.67878484725952</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405548095703</v>
+        <v>2.77405571937561</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G31" t="n">
-        <v>2.64142417907715</v>
+        <v>2.64142441749573</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45835518836975</v>
+        <v>2.45835494995117</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.49198007583618</v>
+        <v>2.4919798374176</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604217529297</v>
+        <v>2.57604193687439</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52747297286987</v>
+        <v>2.52747273445129</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395921707153</v>
+        <v>2.46395945549011</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G41" t="n">
-        <v>2.79460406303406</v>
+        <v>2.79460430145264</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G45" t="n">
-        <v>2.73856282234192</v>
+        <v>2.73856258392334</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988201141357</v>
+        <v>2.71988224983215</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526377677917</v>
+        <v>2.78526401519775</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G54" t="n">
-        <v>2.73856282234192</v>
+        <v>2.73856258392334</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065333366394</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603486061096</v>
+        <v>2.74603509902954</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.71801400184631</v>
+        <v>2.71801424026489</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988201141357</v>
+        <v>2.71988224983215</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G60" t="n">
-        <v>2.63768792152405</v>
+        <v>2.63768768310547</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G64" t="n">
-        <v>2.58164620399475</v>
+        <v>2.58164644241333</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>2.64889597892761</v>
+        <v>2.64889621734619</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G67" t="n">
-        <v>2.49945259094238</v>
+        <v>2.49945211410522</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>2.44714665412903</v>
+        <v>2.44714641571045</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791042327881</v>
+        <v>2.57791018486023</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G70" t="n">
-        <v>2.56296563148499</v>
+        <v>2.56296586990356</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G72" t="n">
-        <v>2.59659075737</v>
+        <v>2.59659099578857</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911848068237</v>
+        <v>2.58911871910095</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>2.60219502449036</v>
+        <v>2.60219478607178</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59285473823547</v>
+        <v>2.59285497665405</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.62647986412048</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.62647986412048</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065333366394</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702820777893</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263247489929</v>
+        <v>2.65263223648071</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>2.62461161613464</v>
+        <v>2.62461137771606</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911848068237</v>
+        <v>2.58911871910095</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066017150879</v>
+        <v>2.51066040992737</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538269996643</v>
+        <v>2.58538222312927</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098649024963</v>
+        <v>2.59098672866821</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>2.65450048446655</v>
+        <v>2.65450024604797</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702820777893</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487447738647</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487447738647</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G102" t="n">
-        <v>2.80777740478516</v>
+        <v>2.80777764320374</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G106" t="n">
-        <v>2.93358421325684</v>
+        <v>2.93358445167542</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92595934867859</v>
+        <v>2.92595958709717</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>2.870680809021</v>
+        <v>2.87068104743958</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91071033477783</v>
+        <v>2.91071009635925</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G121" t="n">
-        <v>2.8954610824585</v>
+        <v>2.89546084403992</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760120391846</v>
+        <v>2.56760096549988</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.47801113128662</v>
+        <v>2.4780113697052</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G143" t="n">
-        <v>2.60381817817688</v>
+        <v>2.60381841659546</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>2.6400351524353</v>
+        <v>2.64003491401672</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G154" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.17493152618408</v>
+        <v>2.1749312877655</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.17493152618408</v>
+        <v>2.1749312877655</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399333000183</v>
+        <v>2.19399309158325</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.21305465698242</v>
+        <v>2.213054895401</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G182" t="n">
-        <v>2.12727761268616</v>
+        <v>2.12727737426758</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484294891357</v>
+        <v>2.05484318733215</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724784851074</v>
+        <v>2.08724808692932</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956440925598</v>
+        <v>1.99956452846527</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765837192535</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G192" t="n">
-        <v>1.98812747001648</v>
+        <v>1.98812758922577</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.99003374576569</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.99003374576569</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G199" t="n">
-        <v>1.92713057994843</v>
+        <v>1.92713046073914</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96144139766693</v>
+        <v>1.96144151687622</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803936958313</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185156345367</v>
+        <v>1.87185168266296</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803936958313</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G217" t="n">
-        <v>1.85469615459442</v>
+        <v>1.85469627380371</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038533687592</v>
+        <v>1.82038521766663</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G221" t="n">
-        <v>1.80227673053741</v>
+        <v>1.8022768497467</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>1.81561994552612</v>
+        <v>1.81561982631683</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G235" t="n">
-        <v>1.75081038475037</v>
+        <v>1.75081026554108</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G236" t="n">
-        <v>1.77559041976929</v>
+        <v>1.77559053897858</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509191513062</v>
+        <v>1.74509179592133</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G238" t="n">
-        <v>1.77082502841949</v>
+        <v>1.77082514762878</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273118495941</v>
+        <v>1.77273106575012</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372831344604</v>
+        <v>1.83372843265533</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.87757015228271</v>
+        <v>1.877570271492</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G251" t="n">
-        <v>1.96144139766693</v>
+        <v>1.96144151687622</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674958229065</v>
+        <v>2.05674934387207</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437397003174</v>
+        <v>2.06437373161316</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G263" t="n">
-        <v>2.00909519195557</v>
+        <v>2.00909543037415</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="n">
-        <v>2.12727761268616</v>
+        <v>2.12727737426758</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G266" t="n">
-        <v>2.13108992576599</v>
+        <v>2.13108968734741</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334731578827</v>
+        <v>1.96334719657898</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.93475496768951</v>
+        <v>1.9347550868988</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765837192535</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330326557159</v>
+        <v>1.90330338478088</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.81561994552612</v>
+        <v>1.81561982631683</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G292" t="n">
-        <v>1.92713057994843</v>
+        <v>1.92713046073914</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.9214118719101</v>
+        <v>1.92141175270081</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G295" t="n">
-        <v>1.9195054769516</v>
+        <v>1.91950559616089</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G302" t="n">
-        <v>1.87280488014221</v>
+        <v>1.87280476093292</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471091747284</v>
+        <v>1.87471079826355</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G306" t="n">
-        <v>1.86994540691376</v>
+        <v>1.86994552612305</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.99003374576569</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.04912495613098</v>
+        <v>2.0491247177124</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645656585693</v>
+        <v>2.30645680427551</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G334" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G335" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938973426819</v>
+        <v>2.40938949584961</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>2.57331943511963</v>
+        <v>2.57331967353821</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058856010437</v>
+        <v>2.60058832168579</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806670188904</v>
+        <v>2.70806646347046</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715992927551</v>
+        <v>2.77715969085693</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.72917866706848</v>
+        <v>2.7291784286499</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514119148254</v>
+        <v>2.82514095306396</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.89807271957397</v>
+        <v>2.8980724811554</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363159179688</v>
+        <v>3.00363183021545</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757537841797</v>
+        <v>3.14757561683655</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343891143799</v>
+        <v>3.29343867301941</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818422317505</v>
+        <v>3.22818446159363</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596076965332</v>
+        <v>3.18596053123474</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040189743042</v>
+        <v>3.08040165901184</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707225799561</v>
+        <v>3.20707249641418</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020272254944</v>
+        <v>3.18020296096802</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647592544556</v>
+        <v>3.50647616386414</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809101104736</v>
+        <v>3.46809077262878</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899778366089</v>
+        <v>3.39899802207947</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889855384827</v>
+        <v>3.44889831542969</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940745353699</v>
+        <v>3.57940769195557</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264364242554</v>
+        <v>3.69264340400696</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122749328613</v>
+        <v>3.63122725486755</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223397254944</v>
+        <v>3.51223373413086</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502944946289</v>
+        <v>2.49502921104431</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736440658569</v>
+        <v>2.86736464500427</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.8481719493866</v>
+        <v>2.84817218780518</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230865478516</v>
+        <v>2.70230889320374</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928391456604</v>
+        <v>2.86928367614746</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877453804016</v>
+        <v>2.73877477645874</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563805580139</v>
+        <v>2.57563829421997</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614743232727</v>
+        <v>2.70614719390869</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685526847839</v>
+        <v>2.73685550689697</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503570556641</v>
+        <v>2.68503546714783</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281779289246</v>
+        <v>2.83281803131104</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019068717957</v>
+        <v>2.80019092559814</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75028991699219</v>
+        <v>2.75029015541077</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978077888489</v>
+        <v>2.61978101730347</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301696777344</v>
+        <v>2.73301672935486</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735838890076</v>
+        <v>2.67735862731934</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190500259399</v>
+        <v>2.71190524101257</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.70422792434692</v>
+        <v>2.7042281627655</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.37219715118408</v>
+        <v>2.3721969127655</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>0.291999995708466</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>126811</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.293500006198883</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.288500010967255</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.291999995708466</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.288500010967255</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.288500010967255</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62588691711426</v>
+        <v>3.62588715553284</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>3.41292929649353</v>
+        <v>3.41292905807495</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930417060852</v>
+        <v>3.37930393218994</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655394554138</v>
+        <v>3.44655418395996</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4932553768158</v>
+        <v>3.49325513839722</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G11" t="n">
-        <v>3.39985299110413</v>
+        <v>3.39985275268555</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.42787337303162</v>
+        <v>3.4278736114502</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127575874329</v>
+        <v>3.52127599716187</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G21" t="n">
-        <v>3.32699871063232</v>
+        <v>3.3269989490509</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G24" t="n">
-        <v>3.22425580024719</v>
+        <v>3.22425603866577</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2578809261322</v>
+        <v>3.25788068771362</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96272850036621</v>
+        <v>2.96272873878479</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G27" t="n">
-        <v>2.67878484725952</v>
+        <v>2.6787850856781</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>2.64329218864441</v>
+        <v>2.64329195022583</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636849403381</v>
+        <v>2.65636873245239</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G31" t="n">
-        <v>2.64142441749573</v>
+        <v>2.64142417907715</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>2.40978574752808</v>
+        <v>2.4097855091095</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52747273445129</v>
+        <v>2.52747297286987</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120899200439</v>
+        <v>2.53120923042297</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G42" t="n">
-        <v>2.77592372894287</v>
+        <v>2.77592349052429</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G49" t="n">
-        <v>2.62274360656738</v>
+        <v>2.62274384498596</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526401519775</v>
+        <v>2.78526425361633</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065285682678</v>
+        <v>2.68065333366394</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350689888</v>
+        <v>2.75350713729858</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603509902954</v>
+        <v>2.74603486061096</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>2.44714641571045</v>
+        <v>2.44714665412903</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791018486023</v>
+        <v>2.57791042327881</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G72" t="n">
-        <v>2.59659099578857</v>
+        <v>2.59659051895142</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>2.60219478607178</v>
+        <v>2.60219526290894</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59285497665405</v>
+        <v>2.59285473823547</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395190238953</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384077072144</v>
+        <v>2.66384053230286</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065285682678</v>
+        <v>2.68065333366394</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702820777893</v>
+        <v>2.64702844619751</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395190238953</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208389282227</v>
+        <v>2.63208365440369</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>2.62461137771606</v>
+        <v>2.62461161613464</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55175757408142</v>
+        <v>2.5517578125</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G94" t="n">
-        <v>2.5648341178894</v>
+        <v>2.56483435630798</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702820777893</v>
+        <v>2.64702844619751</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.74487447738647</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.74487447738647</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G106" t="n">
-        <v>2.93358445167542</v>
+        <v>2.93358421325684</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>2.87068104743958</v>
+        <v>2.870680809021</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G111" t="n">
-        <v>2.96598887443542</v>
+        <v>2.965989112854</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G113" t="n">
-        <v>2.97170758247375</v>
+        <v>2.97170734405518</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7315309047699</v>
+        <v>2.73153066635132</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3</v>
       </c>
       <c r="G122" t="n">
-        <v>2.85924363136292</v>
+        <v>2.85924386978149</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>2.65719056129456</v>
+        <v>2.65719079971313</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>2.59619331359863</v>
+        <v>2.59619355201721</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G132" t="n">
-        <v>2.46276235580444</v>
+        <v>2.46276211738586</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.57141327857971</v>
+        <v>2.57141351699829</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G140" t="n">
-        <v>2.60572409629822</v>
+        <v>2.6057243347168</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G142" t="n">
-        <v>2.59428715705872</v>
+        <v>2.59428739547729</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G143" t="n">
-        <v>2.60381841659546</v>
+        <v>2.60381817817688</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64003491401672</v>
+        <v>2.6400351524353</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G147" t="n">
-        <v>2.65719056129456</v>
+        <v>2.65719079971313</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G148" t="n">
-        <v>2.65337824821472</v>
+        <v>2.6533784866333</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698459625244</v>
+        <v>2.37698483467102</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G151" t="n">
-        <v>2.31408143043518</v>
+        <v>2.3140811920166</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G152" t="n">
-        <v>2.24164724349976</v>
+        <v>2.24164700508118</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G154" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>2.2111485004425</v>
+        <v>2.21114873886108</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.1749312877655</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.1749312877655</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.19208669662476</v>
+        <v>2.19208693504333</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258543968201</v>
+        <v>2.22258567810059</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G168" t="n">
-        <v>2.24736571311951</v>
+        <v>2.24736595153809</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.17683744430542</v>
+        <v>2.176837682724</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G171" t="n">
-        <v>2.2244918346405</v>
+        <v>2.22449207305908</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24164724349976</v>
+        <v>2.24164700508118</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G175" t="n">
-        <v>2.2244918346405</v>
+        <v>2.22449207305908</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G179" t="n">
-        <v>2.19780540466309</v>
+        <v>2.19780516624451</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G182" t="n">
-        <v>2.12727737426758</v>
+        <v>2.12727761268616</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.07771730422974</v>
+        <v>2.07771706581116</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G184" t="n">
-        <v>2.07771730422974</v>
+        <v>2.07771706581116</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484318733215</v>
+        <v>2.05484294891357</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G186" t="n">
-        <v>2.05865573883057</v>
+        <v>2.05865550041199</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G192" t="n">
-        <v>1.98812758922577</v>
+        <v>1.98812747001648</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G195" t="n">
-        <v>1.96525359153748</v>
+        <v>1.96525371074677</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G201" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G203" t="n">
-        <v>1.94619190692902</v>
+        <v>1.94619202613831</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96144151687622</v>
+        <v>1.96144139766693</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G206" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G208" t="n">
-        <v>1.90806889533997</v>
+        <v>1.90806877613068</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186632633209</v>
+        <v>1.89186644554138</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G213" t="n">
-        <v>1.8642270565033</v>
+        <v>1.86422693729401</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G216" t="n">
-        <v>1.84802460670471</v>
+        <v>1.84802448749542</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G217" t="n">
-        <v>1.85469627380371</v>
+        <v>1.85469615459442</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038521766663</v>
+        <v>1.82038533687592</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95762884616852</v>
+        <v>1.95762872695923</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G225" t="n">
-        <v>1.8394467830658</v>
+        <v>1.83944690227509</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>1.78130877017975</v>
+        <v>1.78130888938904</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>1.80608904361725</v>
+        <v>1.80608892440796</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G235" t="n">
-        <v>1.75081026554108</v>
+        <v>1.75081038475037</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G236" t="n">
-        <v>1.77559053897858</v>
+        <v>1.77559041976929</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G238" t="n">
-        <v>1.77082514762878</v>
+        <v>1.77082502841949</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273106575012</v>
+        <v>1.77273118495941</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G240" t="n">
-        <v>1.79465210437775</v>
+        <v>1.79465198516846</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G243" t="n">
-        <v>1.84993076324463</v>
+        <v>1.84993088245392</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.877570271492</v>
+        <v>1.87757015228271</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G246" t="n">
-        <v>1.91378700733185</v>
+        <v>1.91378712654114</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G249" t="n">
-        <v>1.95953512191772</v>
+        <v>1.95953500270844</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G251" t="n">
-        <v>1.96144151687622</v>
+        <v>1.96144139766693</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G254" t="n">
-        <v>1.97097218036652</v>
+        <v>1.97097206115723</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575233459473</v>
+        <v>1.99575245380402</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252662658691</v>
+        <v>2.14252686500549</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437373161316</v>
+        <v>2.06437397003174</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="n">
-        <v>2.12727737426758</v>
+        <v>2.12727761268616</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G266" t="n">
-        <v>2.13108968734741</v>
+        <v>2.13108992576599</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.09677863121033</v>
+        <v>2.09677886962891</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G268" t="n">
-        <v>2.00718927383423</v>
+        <v>2.00718903541565</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G270" t="n">
-        <v>1.91378700733185</v>
+        <v>1.91378712654114</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334719657898</v>
+        <v>1.96334743499756</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.9347550868988</v>
+        <v>1.93475496768951</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G278" t="n">
-        <v>1.94619190692902</v>
+        <v>1.94619202613831</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G282" t="n">
-        <v>1.8642270565033</v>
+        <v>1.86422693729401</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G287" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G291" t="n">
-        <v>1.93666136264801</v>
+        <v>1.93666124343872</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.92141175270081</v>
+        <v>1.92141199111938</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G296" t="n">
-        <v>1.89091312885284</v>
+        <v>1.89091324806213</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478437423706</v>
+        <v>1.97478449344635</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G301" t="n">
-        <v>1.95762884616852</v>
+        <v>1.95762872695923</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471079826355</v>
+        <v>1.87471091747284</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661707401276</v>
+        <v>1.87661695480347</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G310" t="n">
-        <v>2.01481413841248</v>
+        <v>2.0148138999939</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G313" t="n">
-        <v>2.10249757766724</v>
+        <v>2.10249733924866</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.0491247177124</v>
+        <v>2.04912495613098</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730666160583</v>
+        <v>2.16730690002441</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>2.22067928314209</v>
+        <v>2.22067904472351</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G319" t="n">
-        <v>2.3502984046936</v>
+        <v>2.35029864311218</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G322" t="n">
-        <v>2.24736571311951</v>
+        <v>2.24736595153809</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G323" t="n">
-        <v>2.28548884391785</v>
+        <v>2.28548908233643</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>2.22067928314209</v>
+        <v>2.22067904472351</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G329" t="n">
-        <v>2.30836272239685</v>
+        <v>2.30836296081543</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645680427551</v>
+        <v>2.30645704269409</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G334" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G335" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>2.39414000511169</v>
+        <v>2.39414024353027</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270330429077</v>
+        <v>2.38270306587219</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938949584961</v>
+        <v>2.40938973426819</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41129541397095</v>
+        <v>2.41129565238953</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G349" t="n">
-        <v>2.68578314781189</v>
+        <v>2.68578290939331</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>2.68578314781189</v>
+        <v>2.68578290939331</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G351" t="n">
-        <v>2.68578314781189</v>
+        <v>2.68578290939331</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G354" t="n">
-        <v>2.60572409629822</v>
+        <v>2.6057243347168</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058832168579</v>
+        <v>2.60058856010437</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806646347046</v>
+        <v>2.70806670188904</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715969085693</v>
+        <v>2.77715992927551</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.7291784286499</v>
+        <v>2.72917866706848</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514095306396</v>
+        <v>2.82514119148254</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.8980724811554</v>
+        <v>2.89807271957397</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363183021545</v>
+        <v>3.00363159179688</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757561683655</v>
+        <v>3.14757537841797</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343867301941</v>
+        <v>3.29343891143799</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818446159363</v>
+        <v>3.22818422317505</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596053123474</v>
+        <v>3.18596076965332</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040165901184</v>
+        <v>3.08040189743042</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707249641418</v>
+        <v>3.20707225799561</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020296096802</v>
+        <v>3.18020272254944</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647616386414</v>
+        <v>3.50647592544556</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809077262878</v>
+        <v>3.46809101104736</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899802207947</v>
+        <v>3.39899778366089</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889831542969</v>
+        <v>3.44889855384827</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940769195557</v>
+        <v>3.57940745353699</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264340400696</v>
+        <v>3.69264364242554</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122725486755</v>
+        <v>3.63122749328613</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223373413086</v>
+        <v>3.51223397254944</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502921104431</v>
+        <v>2.49502944946289</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736464500427</v>
+        <v>2.86736440658569</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.84817218780518</v>
+        <v>2.8481719493866</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230889320374</v>
+        <v>2.70230865478516</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928367614746</v>
+        <v>2.86928391456604</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877477645874</v>
+        <v>2.73877453804016</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563829421997</v>
+        <v>2.57563805580139</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614719390869</v>
+        <v>2.70614743232727</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685550689697</v>
+        <v>2.73685526847839</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503546714783</v>
+        <v>2.68503570556641</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281803131104</v>
+        <v>2.83281779289246</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019092559814</v>
+        <v>2.80019068717957</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75029015541077</v>
+        <v>2.75028991699219</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978101730347</v>
+        <v>2.61978077888489</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301672935486</v>
+        <v>2.73301696777344</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735862731934</v>
+        <v>2.67735838890076</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190524101257</v>
+        <v>2.71190500259399</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.7042281627655</v>
+        <v>2.70422792434692</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.3721969127655</v>
+        <v>2.37219715118408</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>0.288500010967255</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>170509</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.288500010967255</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.288500010967255</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67819213867188</v>
+        <v>3.67819237709045</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62588715553284</v>
+        <v>3.62588691711426</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>3.41292905807495</v>
+        <v>3.41292929649353</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930393218994</v>
+        <v>3.37930417060852</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.49325513839722</v>
+        <v>3.49325561523438</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G12" t="n">
-        <v>3.32886672019958</v>
+        <v>3.32886648178101</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G16" t="n">
-        <v>3.47083854675293</v>
+        <v>3.47083878517151</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.43160963058472</v>
+        <v>3.43160939216614</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127599716187</v>
+        <v>3.52127575874329</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G21" t="n">
-        <v>3.3269989490509</v>
+        <v>3.32699871063232</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G22" t="n">
-        <v>3.31579041481018</v>
+        <v>3.3157901763916</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G24" t="n">
-        <v>3.22425603866577</v>
+        <v>3.22425556182861</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636873245239</v>
+        <v>2.65636849403381</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72922253608704</v>
+        <v>2.72922229766846</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4097855091095</v>
+        <v>2.40978574752808</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120923042297</v>
+        <v>2.53120899200439</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G45" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61527132987976</v>
+        <v>2.61527109146118</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G49" t="n">
-        <v>2.62274384498596</v>
+        <v>2.62274360656738</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526425361633</v>
+        <v>2.78526401519775</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80581259727478</v>
+        <v>2.8058123588562</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G54" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065333366394</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350713729858</v>
+        <v>2.75350689888</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G63" t="n">
-        <v>2.66010451316833</v>
+        <v>2.66010427474976</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G67" t="n">
-        <v>2.49945211410522</v>
+        <v>2.4994523525238</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>2.44714665412903</v>
+        <v>2.44714641571045</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G70" t="n">
-        <v>2.56296586990356</v>
+        <v>2.56296563148499</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G72" t="n">
-        <v>2.59659051895142</v>
+        <v>2.59659075737</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911871910095</v>
+        <v>2.58911848068237</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>2.60219526290894</v>
+        <v>2.60219502449036</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395190238953</v>
+        <v>2.63395166397095</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384053230286</v>
+        <v>2.66384077072144</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065333366394</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>2.61527132987976</v>
+        <v>2.61527109146118</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702796936035</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395190238953</v>
+        <v>2.63395166397095</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263223648071</v>
+        <v>2.65263247489929</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208365440369</v>
+        <v>2.63208413124084</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>2.62461161613464</v>
+        <v>2.62461137771606</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911871910095</v>
+        <v>2.58911848068237</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538222312927</v>
+        <v>2.58538246154785</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56483435630798</v>
+        <v>2.5648341178894</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>2.65450024604797</v>
+        <v>2.65450048446655</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702796936035</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G104" t="n">
-        <v>2.84971308708191</v>
+        <v>2.84971284866333</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88783621788025</v>
+        <v>2.88783645629883</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G106" t="n">
-        <v>2.93358421325684</v>
+        <v>2.93358445167542</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92595958709717</v>
+        <v>2.92595934867859</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G117" t="n">
-        <v>2.73153066635132</v>
+        <v>2.7315309047699</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G121" t="n">
-        <v>2.89546084403992</v>
+        <v>2.8954610824585</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>2.65719079971313</v>
+        <v>2.65719056129456</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72200012207031</v>
+        <v>2.72199988365173</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>2.59619355201721</v>
+        <v>2.59619331359863</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G132" t="n">
-        <v>2.46276211738586</v>
+        <v>2.46276235580444</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.4780113697052</v>
+        <v>2.47801113128662</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563575744629</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.57141351699829</v>
+        <v>2.57141327857971</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53329014778137</v>
+        <v>2.53328990936279</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G142" t="n">
-        <v>2.59428739547729</v>
+        <v>2.59428691864014</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>2.6400351524353</v>
+        <v>2.64003491401672</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G147" t="n">
-        <v>2.65719079971313</v>
+        <v>2.65719056129456</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G148" t="n">
-        <v>2.6533784866333</v>
+        <v>2.65337824821472</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.4551374912262</v>
+        <v>2.45513725280762</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698483467102</v>
+        <v>2.37698459625244</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G151" t="n">
-        <v>2.3140811920166</v>
+        <v>2.31408143043518</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G154" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>2.33504915237427</v>
+        <v>2.33504939079285</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>2.21114873886108</v>
+        <v>2.2111485004425</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258567810059</v>
+        <v>2.22258543968201</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.176837682724</v>
+        <v>2.17683744430542</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G171" t="n">
-        <v>2.22449207305908</v>
+        <v>2.2244918346405</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G173" t="n">
-        <v>2.26070880889893</v>
+        <v>2.2607090473175</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G175" t="n">
-        <v>2.22449207305908</v>
+        <v>2.2244918346405</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G179" t="n">
-        <v>2.19780516624451</v>
+        <v>2.19780540466309</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G181" t="n">
-        <v>2.14633917808533</v>
+        <v>2.14633893966675</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G182" t="n">
-        <v>2.12727761268616</v>
+        <v>2.12727737426758</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.07771706581116</v>
+        <v>2.07771754264832</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G184" t="n">
-        <v>2.07771706581116</v>
+        <v>2.07771754264832</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484294891357</v>
+        <v>2.05484318733215</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G188" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G192" t="n">
-        <v>1.98812747001648</v>
+        <v>1.98812758922577</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G195" t="n">
-        <v>1.96525371074677</v>
+        <v>1.96525359153748</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000445842743</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191061496735</v>
+        <v>1.95191049575806</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96144139766693</v>
+        <v>1.96144151687622</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>1.91759955883026</v>
+        <v>1.91759967803955</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>1.8871009349823</v>
+        <v>1.88710105419159</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186644554138</v>
+        <v>1.89186632633209</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G216" t="n">
-        <v>1.84802448749542</v>
+        <v>1.84802460670471</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G218" t="n">
-        <v>1.81657290458679</v>
+        <v>1.81657302379608</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038533687592</v>
+        <v>1.82038509845734</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95762872695923</v>
+        <v>1.95762884616852</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>1.80608892440796</v>
+        <v>1.80608904361725</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G235" t="n">
-        <v>1.75081038475037</v>
+        <v>1.75081026554108</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G236" t="n">
-        <v>1.77559041976929</v>
+        <v>1.77559053897858</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509179592133</v>
+        <v>1.74509191513062</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G238" t="n">
-        <v>1.77082502841949</v>
+        <v>1.77082514762878</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273118495941</v>
+        <v>1.77273106575012</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G240" t="n">
-        <v>1.79465198516846</v>
+        <v>1.79465210437775</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660231113434</v>
+        <v>1.85660243034363</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G243" t="n">
-        <v>1.84993088245392</v>
+        <v>1.84993076324463</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G249" t="n">
-        <v>1.95953500270844</v>
+        <v>1.95953512191772</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G251" t="n">
-        <v>1.96144139766693</v>
+        <v>1.96144151687622</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G254" t="n">
-        <v>1.97097206115723</v>
+        <v>1.97097218036652</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575245380402</v>
+        <v>1.99575233459473</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G256" t="n">
-        <v>2.00528311729431</v>
+        <v>2.00528287887573</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252686500549</v>
+        <v>2.14252662658691</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G259" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674934387207</v>
+        <v>2.05674958229065</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G261" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="n">
-        <v>2.12727761268616</v>
+        <v>2.12727737426758</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.93475496768951</v>
+        <v>1.9347550868988</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G276" t="n">
-        <v>1.95381665229797</v>
+        <v>1.95381653308868</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G284" t="n">
-        <v>1.81657290458679</v>
+        <v>1.81657302379608</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G289" t="n">
-        <v>1.94237983226776</v>
+        <v>1.94237995147705</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.92141199111938</v>
+        <v>1.9214118719101</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000445842743</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478449344635</v>
+        <v>1.97478437423706</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G301" t="n">
-        <v>1.95762872695923</v>
+        <v>1.95762884616852</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471091747284</v>
+        <v>1.87471079826355</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661695480347</v>
+        <v>1.87661707401276</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>1.8871009349823</v>
+        <v>1.88710105419159</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G310" t="n">
-        <v>2.0148138999939</v>
+        <v>2.01481413841248</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G311" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.04912495613098</v>
+        <v>2.0491247177124</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730690002441</v>
+        <v>2.16730666160583</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35029864311218</v>
+        <v>2.3502984046936</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G323" t="n">
-        <v>2.28548908233643</v>
+        <v>2.28548884391785</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645704269409</v>
+        <v>2.30645680427551</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G334" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G335" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G337" t="n">
-        <v>2.42463874816895</v>
+        <v>2.42463850975037</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>2.42082643508911</v>
+        <v>2.42082667350769</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270306587219</v>
+        <v>2.38270330429077</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41129565238953</v>
+        <v>2.41129541397095</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563575744629</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G349" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578338623047</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578338623047</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G351" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578338623047</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>2.57331967353821</v>
+        <v>2.57331943511963</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058856010437</v>
+        <v>2.60058832168579</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806670188904</v>
+        <v>2.70806646347046</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715992927551</v>
+        <v>2.77715969085693</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.72917866706848</v>
+        <v>2.7291784286499</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514119148254</v>
+        <v>2.82514095306396</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.89807271957397</v>
+        <v>2.8980724811554</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363159179688</v>
+        <v>3.00363183021545</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757537841797</v>
+        <v>3.14757561683655</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343891143799</v>
+        <v>3.29343867301941</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818422317505</v>
+        <v>3.22818446159363</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596076965332</v>
+        <v>3.18596053123474</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040189743042</v>
+        <v>3.08040165901184</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707225799561</v>
+        <v>3.20707249641418</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020272254944</v>
+        <v>3.18020296096802</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647592544556</v>
+        <v>3.50647616386414</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809101104736</v>
+        <v>3.46809077262878</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899778366089</v>
+        <v>3.39899802207947</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889855384827</v>
+        <v>3.44889831542969</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940745353699</v>
+        <v>3.57940769195557</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264364242554</v>
+        <v>3.69264340400696</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122749328613</v>
+        <v>3.63122725486755</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223397254944</v>
+        <v>3.51223373413086</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502944946289</v>
+        <v>2.49502921104431</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736440658569</v>
+        <v>2.86736464500427</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.8481719493866</v>
+        <v>2.84817218780518</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230865478516</v>
+        <v>2.70230889320374</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928391456604</v>
+        <v>2.86928367614746</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877453804016</v>
+        <v>2.73877477645874</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563805580139</v>
+        <v>2.57563829421997</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614743232727</v>
+        <v>2.70614719390869</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685526847839</v>
+        <v>2.73685550689697</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503570556641</v>
+        <v>2.68503546714783</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281779289246</v>
+        <v>2.83281803131104</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019068717957</v>
+        <v>2.80019092559814</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75028991699219</v>
+        <v>2.75029015541077</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978077888489</v>
+        <v>2.61978101730347</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301696777344</v>
+        <v>2.73301672935486</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735838890076</v>
+        <v>2.67735862731934</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190500259399</v>
+        <v>2.71190524101257</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.70422792434692</v>
+        <v>2.7042281627655</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.37219715118408</v>
+        <v>2.3721969127655</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>0.284999996423721</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>90861</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.284500002861023</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67819237709045</v>
+        <v>3.67819213867188</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599804878235</v>
+        <v>3.59599781036377</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930393218994</v>
+        <v>3.37930417060852</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655394554138</v>
+        <v>3.44655418395996</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G11" t="n">
-        <v>3.39985275268555</v>
+        <v>3.39985299110413</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G14" t="n">
-        <v>3.36622786521912</v>
+        <v>3.36622762680054</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G16" t="n">
-        <v>3.47083878517151</v>
+        <v>3.47083854675293</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127623558044</v>
+        <v>3.52127599716187</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062359809875</v>
+        <v>3.36062383651733</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G21" t="n">
-        <v>3.32699871063232</v>
+        <v>3.3269989490509</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G22" t="n">
-        <v>3.31579041481018</v>
+        <v>3.3157901763916</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2541446685791</v>
+        <v>3.25414490699768</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.25788068771362</v>
+        <v>3.2578809261322</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636849403381</v>
+        <v>2.65636873245239</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4097855091095</v>
+        <v>2.40978527069092</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.49198007583618</v>
+        <v>2.4919798374176</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>2.50318837165833</v>
+        <v>2.50318813323975</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604217529297</v>
+        <v>2.57604193687439</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52747273445129</v>
+        <v>2.52747297286987</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395921707153</v>
+        <v>2.46395945549011</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120923042297</v>
+        <v>2.53120899200439</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G41" t="n">
-        <v>2.79460430145264</v>
+        <v>2.79460406303406</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>2.76471519470215</v>
+        <v>2.76471543312073</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>2.76471519470215</v>
+        <v>2.76471543312073</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G49" t="n">
-        <v>2.62274384498596</v>
+        <v>2.62274360656738</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8058123588562</v>
+        <v>2.80581259727478</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>2.76471519470215</v>
+        <v>2.76471543312073</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350689888</v>
+        <v>2.75350713729858</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603509902954</v>
+        <v>2.74603486061096</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.71801447868347</v>
+        <v>2.71801424026489</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65076446533203</v>
+        <v>2.65076422691345</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G62" t="n">
-        <v>2.68625688552856</v>
+        <v>2.68625712394714</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>2.64889645576477</v>
+        <v>2.64889597892761</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G66" t="n">
-        <v>2.50318837165833</v>
+        <v>2.50318813323975</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791018486023</v>
+        <v>2.57791042327881</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G71" t="n">
-        <v>2.52373671531677</v>
+        <v>2.52373647689819</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G72" t="n">
-        <v>2.59659075737</v>
+        <v>2.59659051895142</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.6264796257019</v>
+        <v>2.62647938728333</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395190238953</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.6264796257019</v>
+        <v>2.62647938728333</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395190238953</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263223648071</v>
+        <v>2.65263247489929</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208365440369</v>
+        <v>2.63208389282227</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G87" t="n">
-        <v>2.62087559700012</v>
+        <v>2.62087535858154</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>2.62461161613464</v>
+        <v>2.62461137771606</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066017150879</v>
+        <v>2.51066040992737</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56483387947083</v>
+        <v>2.5648341178894</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>2.65450024604797</v>
+        <v>2.65450048446655</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487400054932</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487400054932</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G104" t="n">
-        <v>2.84971308708191</v>
+        <v>2.84971284866333</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G111" t="n">
-        <v>2.965989112854</v>
+        <v>2.96598887443542</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G117" t="n">
-        <v>2.73153066635132</v>
+        <v>2.7315309047699</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85352540016174</v>
+        <v>2.85352563858032</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G121" t="n">
-        <v>2.89546084403992</v>
+        <v>2.8954610824585</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760096549988</v>
+        <v>2.56760120391846</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72200012207031</v>
+        <v>2.72199988365173</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>2.59619355201721</v>
+        <v>2.59619331359863</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G132" t="n">
-        <v>2.46276211738586</v>
+        <v>2.46276235580444</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.4780113697052</v>
+        <v>2.47801113128662</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563623428345</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>2.55425786972046</v>
+        <v>2.55425763130188</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.57141351699829</v>
+        <v>2.57141327857971</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G140" t="n">
-        <v>2.6057243347168</v>
+        <v>2.60572409629822</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53329014778137</v>
+        <v>2.53328990936279</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G142" t="n">
-        <v>2.59428739547729</v>
+        <v>2.59428715705872</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.55425786972046</v>
+        <v>2.55425763130188</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G148" t="n">
-        <v>2.6533784866333</v>
+        <v>2.65337824821472</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.4551374912262</v>
+        <v>2.45513725280762</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G151" t="n">
-        <v>2.3140811920166</v>
+        <v>2.31408143043518</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G152" t="n">
-        <v>2.24164700508118</v>
+        <v>2.24164724349976</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220456123352</v>
+        <v>2.35220432281494</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220456123352</v>
+        <v>2.35220432281494</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>2.21114873886108</v>
+        <v>2.2111485004425</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.17493152618408</v>
+        <v>2.17493176460266</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.17493152618408</v>
+        <v>2.17493176460266</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399309158325</v>
+        <v>2.19399333000183</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G171" t="n">
-        <v>2.22449207305908</v>
+        <v>2.2244918346405</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.213054895401</v>
+        <v>2.21305465698242</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24164700508118</v>
+        <v>2.24164724349976</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G175" t="n">
-        <v>2.22449207305908</v>
+        <v>2.2244918346405</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G179" t="n">
-        <v>2.19780516624451</v>
+        <v>2.19780540466309</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.07771706581116</v>
+        <v>2.07771730422974</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G184" t="n">
-        <v>2.07771706581116</v>
+        <v>2.07771730422974</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G186" t="n">
-        <v>2.05865550041199</v>
+        <v>2.05865573883057</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724808692932</v>
+        <v>2.08724784851074</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G188" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.0624680519104</v>
+        <v>2.06246781349182</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956452846527</v>
+        <v>1.99956464767456</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765849113464</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193978309631</v>
+        <v>1.99193966388702</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G195" t="n">
-        <v>1.96525371074677</v>
+        <v>1.96525359153748</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191061496735</v>
+        <v>1.95191049575806</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G202" t="n">
-        <v>1.92903637886047</v>
+        <v>1.92903649806976</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G205" t="n">
-        <v>1.92903637886047</v>
+        <v>1.92903649806976</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616250038147</v>
+        <v>1.90616261959076</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>1.91759955883026</v>
+        <v>1.91759967803955</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803936958313</v>
+        <v>1.86803948879242</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185168266296</v>
+        <v>1.87185156345367</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803936958313</v>
+        <v>1.86803948879242</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G216" t="n">
-        <v>1.84802448749542</v>
+        <v>1.84802460670471</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G221" t="n">
-        <v>1.8022768497467</v>
+        <v>1.80227673053741</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95762872695923</v>
+        <v>1.95762884616852</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G225" t="n">
-        <v>1.83944690227509</v>
+        <v>1.8394467830658</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179286956787</v>
+        <v>1.79179275035858</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>1.80608892440796</v>
+        <v>1.80608904361725</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179286956787</v>
+        <v>1.79179275035858</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509179592133</v>
+        <v>1.74509191513062</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273118495941</v>
+        <v>1.7727313041687</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G240" t="n">
-        <v>1.79465198516846</v>
+        <v>1.79465210437775</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660231113434</v>
+        <v>1.85660243034363</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G243" t="n">
-        <v>1.84993088245392</v>
+        <v>1.84993076324463</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.87757015228271</v>
+        <v>1.87757003307343</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G246" t="n">
-        <v>1.91378712654114</v>
+        <v>1.91378700733185</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616250038147</v>
+        <v>1.90616261959076</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G254" t="n">
-        <v>1.97097206115723</v>
+        <v>1.97097218036652</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575245380402</v>
+        <v>1.99575257301331</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G259" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674934387207</v>
+        <v>2.05674958229065</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G261" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437397003174</v>
+        <v>2.06437373161316</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G270" t="n">
-        <v>1.91378712654114</v>
+        <v>1.91378700733185</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193978309631</v>
+        <v>1.99193966388702</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765849113464</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330338478088</v>
+        <v>1.90330326557159</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>1.8689923286438</v>
+        <v>1.86899244785309</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G285" t="n">
-        <v>1.81371366977692</v>
+        <v>1.81371355056763</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G293" t="n">
-        <v>1.90235030651093</v>
+        <v>1.90235018730164</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G296" t="n">
-        <v>1.89091324806213</v>
+        <v>1.89091312885284</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478449344635</v>
+        <v>1.97478461265564</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G301" t="n">
-        <v>1.95762872695923</v>
+        <v>1.95762884616852</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G305" t="n">
-        <v>1.8689923286438</v>
+        <v>1.86899244785309</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G311" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.0624680519104</v>
+        <v>2.06246781349182</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>2.22067904472351</v>
+        <v>2.22067928314209</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35029864311218</v>
+        <v>2.3502984046936</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G323" t="n">
-        <v>2.28548908233643</v>
+        <v>2.28548884391785</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>2.22067904472351</v>
+        <v>2.22067928314209</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G329" t="n">
-        <v>2.30836296081543</v>
+        <v>2.30836272239685</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645704269409</v>
+        <v>2.30645680427551</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36554789543152</v>
+        <v>2.3655481338501</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938973426819</v>
+        <v>2.40938949584961</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41129565238953</v>
+        <v>2.41129541397095</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563623428345</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G349" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578314781189</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578314781189</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G351" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578314781189</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>2.57331967353821</v>
+        <v>2.57331943511963</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G354" t="n">
-        <v>2.6057243347168</v>
+        <v>2.60572409629822</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>0.282499998807907</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>520956</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.28549998998642</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.277999997138977</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.277999997138977</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.277999997138977</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.267500013113022</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.262499988079071</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>373573</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.270500004291534</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -63285,7 +63285,7 @@
         <v>373573</v>
       </c>
       <c r="C2736" t="n">
-        <v>0.270500004291534</v>
+        <v>0.270999997854233</v>
       </c>
       <c r="D2736" t="n">
         <v>0.261999994516373</v>
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.26800000667572</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.270999997854233</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>283916</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.273000001907349</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.264499992132187</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.264999985694885</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.264999985694885</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>259302</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.268999993801117</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.268999993801117</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.268999993801117</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.259999990463257</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>395463</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.268999993801117</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.258500009775162</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.268999993801117</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>169767</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.257999986410141</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599781036377</v>
+        <v>3.59599804878235</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930393218994</v>
+        <v>3.37930417060852</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655394554138</v>
+        <v>3.44655418395996</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4278736114502</v>
+        <v>3.42787384986877</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.38864421844482</v>
+        <v>3.3886444568634</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.43160963058472</v>
+        <v>3.4316098690033</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G22" t="n">
-        <v>3.31579065322876</v>
+        <v>3.31579041481018</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>2.64329218864441</v>
+        <v>2.64329195022583</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405571937561</v>
+        <v>2.77405548095703</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636825561523</v>
+        <v>2.65636873245239</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.49198007583618</v>
+        <v>2.4919798374176</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>2.50318837165833</v>
+        <v>2.5031886100769</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395921707153</v>
+        <v>2.46395897865295</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120899200439</v>
+        <v>2.53120923042297</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G42" t="n">
-        <v>2.77592396736145</v>
+        <v>2.77592372894287</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988201141357</v>
+        <v>2.719881772995</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G47" t="n">
-        <v>2.67318058013916</v>
+        <v>2.67318081855774</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61527109146118</v>
+        <v>2.61527132987976</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6227433681488</v>
+        <v>2.62274360656738</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350689888</v>
+        <v>2.75350713729858</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988201141357</v>
+        <v>2.719881772995</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G64" t="n">
-        <v>2.58164620399475</v>
+        <v>2.58164644241333</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G66" t="n">
-        <v>2.50318837165833</v>
+        <v>2.5031886100769</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G67" t="n">
-        <v>2.49945259094238</v>
+        <v>2.4994523525238</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791042327881</v>
+        <v>2.57791018486023</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G70" t="n">
-        <v>2.56296563148499</v>
+        <v>2.56296586990356</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G71" t="n">
-        <v>2.52373647689819</v>
+        <v>2.52373671531677</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911848068237</v>
+        <v>2.58911895751953</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59285473823547</v>
+        <v>2.59285449981689</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395142555237</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>2.61527109146118</v>
+        <v>2.61527132987976</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395142555237</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G84" t="n">
-        <v>2.62834763526917</v>
+        <v>2.62834787368774</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263247489929</v>
+        <v>2.65263223648071</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911848068237</v>
+        <v>2.58911895751953</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066040992737</v>
+        <v>2.51066017150879</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.5517578125</v>
+        <v>2.55175757408142</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098672866821</v>
+        <v>2.59098649024963</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>2.65450048446655</v>
+        <v>2.65450024604797</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487400054932</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487400054932</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G102" t="n">
-        <v>2.80777740478516</v>
+        <v>2.80777764320374</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G104" t="n">
-        <v>2.84971308708191</v>
+        <v>2.84971284866333</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92595934867859</v>
+        <v>2.92595958709717</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G113" t="n">
-        <v>2.97170758247375</v>
+        <v>2.97170734405518</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91071033477783</v>
+        <v>2.91071009635925</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85352540016174</v>
+        <v>2.85352563858032</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3</v>
       </c>
       <c r="G122" t="n">
-        <v>2.85924363136292</v>
+        <v>2.85924386978149</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>2.65719056129456</v>
+        <v>2.65719079971313</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72200012207031</v>
+        <v>2.72199988365173</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563623428345</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>2.55425786972046</v>
+        <v>2.55425763130188</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53329014778137</v>
+        <v>2.53328990936279</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.55425786972046</v>
+        <v>2.55425763130188</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G147" t="n">
-        <v>2.65719056129456</v>
+        <v>2.65719079971313</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.4551374912262</v>
+        <v>2.45513725280762</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698459625244</v>
+        <v>2.37698483467102</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.17493152618408</v>
+        <v>2.17493176460266</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.17493152618408</v>
+        <v>2.17493176460266</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.19208669662476</v>
+        <v>2.19208693504333</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258543968201</v>
+        <v>2.22258567810059</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G168" t="n">
-        <v>2.24736571311951</v>
+        <v>2.24736595153809</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.17683744430542</v>
+        <v>2.176837682724</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G188" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956440925598</v>
+        <v>1.99956464767456</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G199" t="n">
-        <v>1.92713057994843</v>
+        <v>1.92713046073914</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191061496735</v>
+        <v>1.95191049575806</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G201" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G202" t="n">
-        <v>1.92903637886047</v>
+        <v>1.92903649806976</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G203" t="n">
-        <v>1.94619190692902</v>
+        <v>1.94619202613831</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G205" t="n">
-        <v>1.92903637886047</v>
+        <v>1.92903649806976</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G206" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G208" t="n">
-        <v>1.90806889533997</v>
+        <v>1.90806877613068</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>1.91759955883026</v>
+        <v>1.91759967803955</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186632633209</v>
+        <v>1.89186644554138</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G213" t="n">
-        <v>1.8642270565033</v>
+        <v>1.86422693729401</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>1.81561994552612</v>
+        <v>1.81561982631683</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>1.78130877017975</v>
+        <v>1.78130888938904</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273118495941</v>
+        <v>1.7727313041687</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372831344604</v>
+        <v>1.83372843265533</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660231113434</v>
+        <v>1.85660243034363</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.87757015228271</v>
+        <v>1.87757003307343</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G249" t="n">
-        <v>1.95953512191772</v>
+        <v>1.95953500270844</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575233459473</v>
+        <v>1.99575257301331</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252662658691</v>
+        <v>2.14252686500549</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G259" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G261" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437397003174</v>
+        <v>2.06437373161316</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G263" t="n">
-        <v>2.00909519195557</v>
+        <v>2.00909543037415</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.09677863121033</v>
+        <v>2.09677886962891</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G268" t="n">
-        <v>2.00718927383423</v>
+        <v>2.00718903541565</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334731578827</v>
+        <v>1.96334743499756</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G278" t="n">
-        <v>1.94619190692902</v>
+        <v>1.94619202613831</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>1.8689923286438</v>
+        <v>1.86899244785309</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G282" t="n">
-        <v>1.8642270565033</v>
+        <v>1.86422693729401</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.81561994552612</v>
+        <v>1.81561982631683</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G285" t="n">
-        <v>1.81371366977692</v>
+        <v>1.81371355056763</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G287" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G291" t="n">
-        <v>1.93666136264801</v>
+        <v>1.93666124343872</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G292" t="n">
-        <v>1.92713057994843</v>
+        <v>1.92713046073914</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G293" t="n">
-        <v>1.90235030651093</v>
+        <v>1.90235018730164</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.9214118719101</v>
+        <v>1.92141199111938</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G295" t="n">
-        <v>1.9195054769516</v>
+        <v>1.91950559616089</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478437423706</v>
+        <v>1.97478461265564</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G302" t="n">
-        <v>1.87280488014221</v>
+        <v>1.87280476093292</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661707401276</v>
+        <v>1.87661695480347</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G305" t="n">
-        <v>1.8689923286438</v>
+        <v>1.86899244785309</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G306" t="n">
-        <v>1.86994540691376</v>
+        <v>1.86994552612305</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G310" t="n">
-        <v>2.01481413841248</v>
+        <v>2.0148138999939</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G311" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G313" t="n">
-        <v>2.10249757766724</v>
+        <v>2.10249733924866</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730666160583</v>
+        <v>2.16730690002441</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G322" t="n">
-        <v>2.24736571311951</v>
+        <v>2.24736595153809</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645656585693</v>
+        <v>2.30645680427551</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>2.39414000511169</v>
+        <v>2.39414024353027</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270330429077</v>
+        <v>2.38270306587219</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36554789543152</v>
+        <v>2.3655481338501</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938973426819</v>
+        <v>2.40938949584961</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563623428345</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -71646,7 +71646,7 @@
         <v>46309.2916666667</v>
       </c>
       <c r="B2742" t="n">
-        <v>793520</v>
+        <v>800447</v>
       </c>
       <c r="C2742" t="n">
         <v>0.282999992370605</v>
@@ -71664,6 +71664,32 @@
         <v>0.282499998807907</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>140658</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.28150001168251</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.27700001001358</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.278499990701675</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.275999993085861</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.275999993085861</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599804878235</v>
+        <v>3.59599781036377</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62588691711426</v>
+        <v>3.62588667869568</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>3.41292929649353</v>
+        <v>3.41292905807495</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655418395996</v>
+        <v>3.44655394554138</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.49325513839722</v>
+        <v>3.4932553768158</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>3.39798450469971</v>
+        <v>3.39798474311829</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G11" t="n">
-        <v>3.39985299110413</v>
+        <v>3.39985275268555</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.42787384986877</v>
+        <v>3.4278736114502</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3886444568634</v>
+        <v>3.38864421844482</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127575874329</v>
+        <v>3.52127599716187</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062383651733</v>
+        <v>3.36062359809875</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G21" t="n">
-        <v>3.32699871063232</v>
+        <v>3.3269989490509</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636873245239</v>
+        <v>2.65636849403381</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45835518836975</v>
+        <v>2.45835494995117</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.4919798374176</v>
+        <v>2.49198007583618</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5031886100769</v>
+        <v>2.50318837165833</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604217529297</v>
+        <v>2.57604193687439</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395897865295</v>
+        <v>2.46395921707153</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G45" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.719881772995</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61527132987976</v>
+        <v>2.61527109146118</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526401519775</v>
+        <v>2.78526425361633</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>2.78339600563049</v>
+        <v>2.78339576721191</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G54" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065285682678</v>
+        <v>2.68065309524536</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350713729858</v>
+        <v>2.75350689888</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.71801400184631</v>
+        <v>2.71801424026489</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.719881772995</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G60" t="n">
-        <v>2.63768792152405</v>
+        <v>2.63768768310547</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65076422691345</v>
+        <v>2.65076446533203</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G64" t="n">
-        <v>2.58164644241333</v>
+        <v>2.58164620399475</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G66" t="n">
-        <v>2.5031886100769</v>
+        <v>2.50318837165833</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791018486023</v>
+        <v>2.57791042327881</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59285449981689</v>
+        <v>2.59285473823547</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.62647986412048</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395142555237</v>
+        <v>2.63395166397095</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.62647986412048</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384053230286</v>
+        <v>2.66384077072144</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065285682678</v>
+        <v>2.68065309524536</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>2.61527132987976</v>
+        <v>2.61527109146118</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395142555237</v>
+        <v>2.63395166397095</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G84" t="n">
-        <v>2.62834787368774</v>
+        <v>2.62834763526917</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263223648071</v>
+        <v>2.65263247489929</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208365440369</v>
+        <v>2.63208389282227</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066017150879</v>
+        <v>2.51066040992737</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55175757408142</v>
+        <v>2.5517578125</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52934098243713</v>
+        <v>2.52934074401855</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098649024963</v>
+        <v>2.59098672866821</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.74487400054932</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.74487400054932</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G115" t="n">
-        <v>2.82874512672424</v>
+        <v>2.82874536514282</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85352563858032</v>
+        <v>2.85352540016174</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>2.65909671783447</v>
+        <v>2.65909695625305</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760120391846</v>
+        <v>2.56760096549988</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72199988365173</v>
+        <v>2.72200012207031</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>2.59619331359863</v>
+        <v>2.59619355201721</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G132" t="n">
-        <v>2.46276235580444</v>
+        <v>2.46276211738586</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563623428345</v>
+        <v>2.48563599586487</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>2.55425763130188</v>
+        <v>2.55425786972046</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.57141327857971</v>
+        <v>2.57141351699829</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G140" t="n">
-        <v>2.60572409629822</v>
+        <v>2.6057243347168</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53328990936279</v>
+        <v>2.53329014778137</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.55425763130188</v>
+        <v>2.55425786972046</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.45513725280762</v>
+        <v>2.4551374912262</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698483467102</v>
+        <v>2.37698459625244</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G152" t="n">
-        <v>2.24164724349976</v>
+        <v>2.24164700508118</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G153" t="n">
-        <v>2.24927186965942</v>
+        <v>2.24927163124084</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G155" t="n">
-        <v>2.32551836967468</v>
+        <v>2.32551860809326</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>2.33504915237427</v>
+        <v>2.33504939079285</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.17493176460266</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.17493176460266</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258567810059</v>
+        <v>2.22258543968201</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399333000183</v>
+        <v>2.19399309158325</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.176837682724</v>
+        <v>2.17683744430542</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.21305465698242</v>
+        <v>2.213054895401</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24164724349976</v>
+        <v>2.24164700508118</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G180" t="n">
-        <v>2.153963804245</v>
+        <v>2.15396356582642</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484294891357</v>
+        <v>2.05484318733215</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G186" t="n">
-        <v>2.05865573883057</v>
+        <v>2.05865550041199</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724784851074</v>
+        <v>2.08724808692932</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956464767456</v>
+        <v>1.99956452846527</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000433921814</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191049575806</v>
+        <v>1.95191061496735</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G202" t="n">
-        <v>1.92903649806976</v>
+        <v>1.92903637886047</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G205" t="n">
-        <v>1.92903649806976</v>
+        <v>1.92903637886047</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803925037384</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186644554138</v>
+        <v>1.89186632633209</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185156345367</v>
+        <v>1.87185168266296</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803925037384</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038533687592</v>
+        <v>1.82038521766663</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95762884616852</v>
+        <v>1.95762872695923</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G225" t="n">
-        <v>1.8394467830658</v>
+        <v>1.83944690227509</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G230" t="n">
-        <v>1.78512132167816</v>
+        <v>1.78512120246887</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G232" t="n">
-        <v>1.81847906112671</v>
+        <v>1.818479180336</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.71554625034332</v>
+        <v>1.71554613113403</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509191513062</v>
+        <v>1.74509179592133</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.7727313041687</v>
+        <v>1.77273118495941</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372843265533</v>
+        <v>1.83372831344604</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660243034363</v>
+        <v>1.85660231113434</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G243" t="n">
-        <v>1.84993076324463</v>
+        <v>1.84993088245392</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G246" t="n">
-        <v>1.91378700733185</v>
+        <v>1.91378712654114</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G254" t="n">
-        <v>1.97097218036652</v>
+        <v>1.97097206115723</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575257301331</v>
+        <v>1.99575245380402</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252686500549</v>
+        <v>2.14252662658691</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674958229065</v>
+        <v>2.05674934387207</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437373161316</v>
+        <v>2.06437420845032</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G270" t="n">
-        <v>1.91378700733185</v>
+        <v>1.91378712654114</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334743499756</v>
+        <v>1.96334755420685</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.93475496768951</v>
+        <v>1.9347550868988</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330326557159</v>
+        <v>1.90330338478088</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G280" t="n">
-        <v>1.85946154594421</v>
+        <v>1.8594616651535</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>1.86899244785309</v>
+        <v>1.8689923286438</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G285" t="n">
-        <v>1.81371355056763</v>
+        <v>1.81371366977692</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G288" t="n">
-        <v>1.89472568035126</v>
+        <v>1.89472556114197</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G293" t="n">
-        <v>1.90235018730164</v>
+        <v>1.90235030651093</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.92141199111938</v>
+        <v>1.9214118719101</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G296" t="n">
-        <v>1.89091312885284</v>
+        <v>1.89091336727142</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000433921814</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478461265564</v>
+        <v>1.97478449344635</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G301" t="n">
-        <v>1.95762884616852</v>
+        <v>1.95762872695923</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471091747284</v>
+        <v>1.87471079826355</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661695480347</v>
+        <v>1.87661707401276</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G305" t="n">
-        <v>1.86899244785309</v>
+        <v>1.8689923286438</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G313" t="n">
-        <v>2.10249733924866</v>
+        <v>2.10249757766724</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730690002441</v>
+        <v>2.16730666160583</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>2.22067928314209</v>
+        <v>2.22067904472351</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G319" t="n">
-        <v>2.3502984046936</v>
+        <v>2.35029864311218</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>2.25880265235901</v>
+        <v>2.25880241394043</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.25880265235901</v>
+        <v>2.25880241394043</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G323" t="n">
-        <v>2.28548884391785</v>
+        <v>2.28548908233643</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>2.22067928314209</v>
+        <v>2.22067904472351</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G329" t="n">
-        <v>2.30836272239685</v>
+        <v>2.30836296081543</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645680427551</v>
+        <v>2.30645704269409</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G337" t="n">
-        <v>2.42463874816895</v>
+        <v>2.42463850975037</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270306587219</v>
+        <v>2.38270330429077</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.3655481338501</v>
+        <v>2.36554765701294</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938949584961</v>
+        <v>2.40938973426819</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41129541397095</v>
+        <v>2.41129565238953</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563623428345</v>
+        <v>2.48563599586487</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G354" t="n">
-        <v>2.60572409629822</v>
+        <v>2.6057243347168</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058856010437</v>
+        <v>2.60058832168579</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806670188904</v>
+        <v>2.70806646347046</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715992927551</v>
+        <v>2.77715969085693</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.72917866706848</v>
+        <v>2.7291784286499</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514119148254</v>
+        <v>2.82514095306396</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.89807271957397</v>
+        <v>2.8980724811554</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363159179688</v>
+        <v>3.00363183021545</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757537841797</v>
+        <v>3.14757561683655</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343891143799</v>
+        <v>3.29343867301941</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818422317505</v>
+        <v>3.22818446159363</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596076965332</v>
+        <v>3.18596053123474</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040189743042</v>
+        <v>3.08040165901184</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707225799561</v>
+        <v>3.20707249641418</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020272254944</v>
+        <v>3.18020296096802</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647592544556</v>
+        <v>3.50647616386414</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809101104736</v>
+        <v>3.46809077262878</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899778366089</v>
+        <v>3.39899802207947</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889855384827</v>
+        <v>3.44889831542969</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940745353699</v>
+        <v>3.57940769195557</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264364242554</v>
+        <v>3.69264340400696</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122749328613</v>
+        <v>3.63122725486755</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223397254944</v>
+        <v>3.51223373413086</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502944946289</v>
+        <v>2.49502921104431</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736440658569</v>
+        <v>2.86736464500427</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.8481719493866</v>
+        <v>2.84817218780518</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230865478516</v>
+        <v>2.70230889320374</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928391456604</v>
+        <v>2.86928367614746</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877453804016</v>
+        <v>2.73877477645874</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563805580139</v>
+        <v>2.57563829421997</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614743232727</v>
+        <v>2.70614719390869</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685526847839</v>
+        <v>2.73685550689697</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503570556641</v>
+        <v>2.68503546714783</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281779289246</v>
+        <v>2.83281803131104</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019068717957</v>
+        <v>2.80019092559814</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75028991699219</v>
+        <v>2.75029015541077</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978077888489</v>
+        <v>2.61978101730347</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301696777344</v>
+        <v>2.73301672935486</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735838890076</v>
+        <v>2.67735862731934</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190500259399</v>
+        <v>2.71190524101257</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.70422792434692</v>
+        <v>2.7042281627655</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.37219715118408</v>
+        <v>2.3721969127655</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -71678,7 +71678,7 @@
         <v>0.28150001168251</v>
       </c>
       <c r="D2743" t="n">
-        <v>0.27700001001358</v>
+        <v>0.275999993085861</v>
       </c>
       <c r="E2743" t="n">
         <v>0.278499990701675</v>
@@ -71690,6 +71690,32 @@
         <v>0.275999993085861</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>237845</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.278499990701675</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.27250000834465</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.275999993085861</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.274500012397766</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.274500012397766</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67819261550903</v>
+        <v>3.67819237709045</v>
       </c>
       <c r="H2" t="n">
         <v>809052</v>
@@ -456,7 +456,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599804878235</v>
+        <v>3.59599781036377</v>
       </c>
       <c r="H3" t="n">
         <v>611692</v>
@@ -485,7 +485,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62588691711426</v>
+        <v>3.62588667869568</v>
       </c>
       <c r="H4" t="n">
         <v>748185</v>
@@ -514,7 +514,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H5" t="n">
         <v>807816</v>
@@ -543,7 +543,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>3.41292929649353</v>
+        <v>3.41292905807495</v>
       </c>
       <c r="H6" t="n">
         <v>652737</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655418395996</v>
+        <v>3.44655394554138</v>
       </c>
       <c r="H8" t="n">
         <v>335339</v>
@@ -630,7 +630,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.49325513839722</v>
+        <v>3.4932553768158</v>
       </c>
       <c r="H9" t="n">
         <v>197035</v>
@@ -659,7 +659,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>3.39798450469971</v>
+        <v>3.39798474311829</v>
       </c>
       <c r="H10" t="n">
         <v>829652</v>
@@ -688,7 +688,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G11" t="n">
-        <v>3.39985299110413</v>
+        <v>3.39985275268555</v>
       </c>
       <c r="H11" t="n">
         <v>1221987</v>
@@ -746,7 +746,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.42787384986877</v>
+        <v>3.4278736114502</v>
       </c>
       <c r="H13" t="n">
         <v>410306</v>
@@ -804,7 +804,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3886444568634</v>
+        <v>3.38864421844482</v>
       </c>
       <c r="H15" t="n">
         <v>742869</v>
@@ -862,7 +862,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.43160963058472</v>
+        <v>3.4316098690033</v>
       </c>
       <c r="H17" t="n">
         <v>415584</v>
@@ -891,7 +891,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127575874329</v>
+        <v>3.52127599716187</v>
       </c>
       <c r="H18" t="n">
         <v>372353</v>
@@ -920,7 +920,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H19" t="n">
         <v>400278</v>
@@ -949,7 +949,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062383651733</v>
+        <v>3.36062359809875</v>
       </c>
       <c r="H20" t="n">
         <v>463309</v>
@@ -978,7 +978,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G21" t="n">
-        <v>3.32699871063232</v>
+        <v>3.3269989490509</v>
       </c>
       <c r="H21" t="n">
         <v>602002</v>
@@ -1094,7 +1094,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.25788068771362</v>
+        <v>3.2578809261322</v>
       </c>
       <c r="H25" t="n">
         <v>832589</v>
@@ -1181,7 +1181,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>2.64329218864441</v>
+        <v>2.64329195022583</v>
       </c>
       <c r="H28" t="n">
         <v>888507</v>
@@ -1297,7 +1297,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72922253608704</v>
+        <v>2.72922229766846</v>
       </c>
       <c r="H32" t="n">
         <v>485309</v>
@@ -1355,7 +1355,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45835518836975</v>
+        <v>2.45835494995117</v>
       </c>
       <c r="H34" t="n">
         <v>1399376</v>
@@ -1442,7 +1442,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604217529297</v>
+        <v>2.57604193687439</v>
       </c>
       <c r="H37" t="n">
         <v>886852</v>
@@ -1529,7 +1529,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120899200439</v>
+        <v>2.53120923042297</v>
       </c>
       <c r="H40" t="n">
         <v>622697</v>
@@ -1558,7 +1558,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G41" t="n">
-        <v>2.79460406303406</v>
+        <v>2.79460430145264</v>
       </c>
       <c r="H41" t="n">
         <v>2765448</v>
@@ -1761,7 +1761,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61527132987976</v>
+        <v>2.61527109146118</v>
       </c>
       <c r="H48" t="n">
         <v>1729959</v>
@@ -1819,7 +1819,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526377677917</v>
+        <v>2.78526425361633</v>
       </c>
       <c r="H50" t="n">
         <v>3240146</v>
@@ -1848,7 +1848,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>2.78339600563049</v>
+        <v>2.78339576721191</v>
       </c>
       <c r="H51" t="n">
         <v>927105</v>
@@ -1877,7 +1877,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80581259727478</v>
+        <v>2.8058123588562</v>
       </c>
       <c r="H52" t="n">
         <v>881692</v>
@@ -1964,7 +1964,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065333366394</v>
+        <v>2.68065309524536</v>
       </c>
       <c r="H55" t="n">
         <v>571416</v>
@@ -2051,7 +2051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.71801400184631</v>
+        <v>2.71801424026489</v>
       </c>
       <c r="H58" t="n">
         <v>634534</v>
@@ -2109,7 +2109,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G60" t="n">
-        <v>2.63768792152405</v>
+        <v>2.63768768310547</v>
       </c>
       <c r="H60" t="n">
         <v>807171</v>
@@ -2138,7 +2138,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65076422691345</v>
+        <v>2.65076446533203</v>
       </c>
       <c r="H61" t="n">
         <v>421361</v>
@@ -2254,7 +2254,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>2.64889597892761</v>
+        <v>2.64889621734619</v>
       </c>
       <c r="H65" t="n">
         <v>389941</v>
@@ -2312,7 +2312,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G67" t="n">
-        <v>2.49945259094238</v>
+        <v>2.4994523525238</v>
       </c>
       <c r="H67" t="n">
         <v>487491</v>
@@ -2399,7 +2399,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G70" t="n">
-        <v>2.56296563148499</v>
+        <v>2.56296586990356</v>
       </c>
       <c r="H70" t="n">
         <v>616769</v>
@@ -2486,7 +2486,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911848068237</v>
+        <v>2.58911895751953</v>
       </c>
       <c r="H73" t="n">
         <v>526922</v>
@@ -2573,7 +2573,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.62647986412048</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H76" t="n">
         <v>520133</v>
@@ -2631,7 +2631,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.62647986412048</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H78" t="n">
         <v>392451</v>
@@ -2689,7 +2689,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065333366394</v>
+        <v>2.68065309524536</v>
       </c>
       <c r="H80" t="n">
         <v>263802</v>
@@ -2718,7 +2718,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>2.61527132987976</v>
+        <v>2.61527109146118</v>
       </c>
       <c r="H81" t="n">
         <v>515442</v>
@@ -2747,7 +2747,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702820777893</v>
       </c>
       <c r="H82" t="n">
         <v>202750</v>
@@ -2950,7 +2950,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911848068237</v>
+        <v>2.58911895751953</v>
       </c>
       <c r="H89" t="n">
         <v>154887</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066017150879</v>
+        <v>2.51066040992737</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3008,7 +3008,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55175757408142</v>
+        <v>2.5517578125</v>
       </c>
       <c r="H91" t="n">
         <v>189126</v>
@@ -3037,7 +3037,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52934098243713</v>
+        <v>2.52934074401855</v>
       </c>
       <c r="H92" t="n">
         <v>162932</v>
@@ -3066,7 +3066,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538269996643</v>
+        <v>2.58538246154785</v>
       </c>
       <c r="H93" t="n">
         <v>366421</v>
@@ -3095,7 +3095,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G94" t="n">
-        <v>2.5648341178894</v>
+        <v>2.56483387947083</v>
       </c>
       <c r="H94" t="n">
         <v>359206</v>
@@ -3124,7 +3124,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098649024963</v>
+        <v>2.59098672866821</v>
       </c>
       <c r="H95" t="n">
         <v>301461</v>
@@ -3153,7 +3153,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>2.65450048446655</v>
+        <v>2.65450024604797</v>
       </c>
       <c r="H96" t="n">
         <v>228387</v>
@@ -3182,7 +3182,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702820777893</v>
       </c>
       <c r="H97" t="n">
         <v>251024</v>
@@ -3327,7 +3327,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G102" t="n">
-        <v>2.80777740478516</v>
+        <v>2.80777764320374</v>
       </c>
       <c r="H102" t="n">
         <v>317585</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G104" t="n">
-        <v>2.84971308708191</v>
+        <v>2.84971284866333</v>
       </c>
       <c r="H104" t="n">
         <v>323531</v>
@@ -3472,7 +3472,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92595934867859</v>
+        <v>2.92595958709717</v>
       </c>
       <c r="H107" t="n">
         <v>323008</v>
@@ -3646,7 +3646,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G113" t="n">
-        <v>2.97170758247375</v>
+        <v>2.97170734405518</v>
       </c>
       <c r="H113" t="n">
         <v>368199</v>
@@ -3675,7 +3675,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91071033477783</v>
+        <v>2.91071009635925</v>
       </c>
       <c r="H114" t="n">
         <v>1063201</v>
@@ -3704,7 +3704,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G115" t="n">
-        <v>2.82874512672424</v>
+        <v>2.82874536514282</v>
       </c>
       <c r="H115" t="n">
         <v>388875</v>
@@ -3907,7 +3907,7 @@
         <v>3</v>
       </c>
       <c r="G122" t="n">
-        <v>2.85924363136292</v>
+        <v>2.85924386978149</v>
       </c>
       <c r="H122" t="n">
         <v>166984</v>
@@ -3965,7 +3965,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>2.65909671783447</v>
+        <v>2.65909695625305</v>
       </c>
       <c r="H124" t="n">
         <v>451934</v>
@@ -3994,7 +3994,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760120391846</v>
+        <v>2.56760096549988</v>
       </c>
       <c r="H125" t="n">
         <v>525319</v>
@@ -4081,7 +4081,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>2.65719056129456</v>
+        <v>2.65719079971313</v>
       </c>
       <c r="H128" t="n">
         <v>191013</v>
@@ -4139,7 +4139,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>2.59619331359863</v>
+        <v>2.59619355201721</v>
       </c>
       <c r="H130" t="n">
         <v>222114</v>
@@ -4197,7 +4197,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G132" t="n">
-        <v>2.46276235580444</v>
+        <v>2.46276211738586</v>
       </c>
       <c r="H132" t="n">
         <v>543169</v>
@@ -4313,7 +4313,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.57141327857971</v>
+        <v>2.57141351699829</v>
       </c>
       <c r="H136" t="n">
         <v>548868</v>
@@ -4429,7 +4429,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G140" t="n">
-        <v>2.60572409629822</v>
+        <v>2.6057243347168</v>
       </c>
       <c r="H140" t="n">
         <v>864905</v>
@@ -4632,7 +4632,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G147" t="n">
-        <v>2.65719056129456</v>
+        <v>2.65719079971313</v>
       </c>
       <c r="H147" t="n">
         <v>531605</v>
@@ -4777,7 +4777,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G152" t="n">
-        <v>2.24164724349976</v>
+        <v>2.24164700508118</v>
       </c>
       <c r="H152" t="n">
         <v>402686</v>
@@ -4806,7 +4806,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G153" t="n">
-        <v>2.24927186965942</v>
+        <v>2.24927163124084</v>
       </c>
       <c r="H153" t="n">
         <v>332222</v>
@@ -4864,7 +4864,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G155" t="n">
-        <v>2.32551836967468</v>
+        <v>2.32551860809326</v>
       </c>
       <c r="H155" t="n">
         <v>305944</v>
@@ -4893,7 +4893,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H156" t="n">
         <v>229323</v>
@@ -4951,7 +4951,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H158" t="n">
         <v>512824</v>
@@ -4980,7 +4980,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>2.33504915237427</v>
+        <v>2.33504939079285</v>
       </c>
       <c r="H159" t="n">
         <v>248797</v>
@@ -5154,7 +5154,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.19208669662476</v>
+        <v>2.19208693504333</v>
       </c>
       <c r="H165" t="n">
         <v>340810</v>
@@ -5241,7 +5241,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G168" t="n">
-        <v>2.24736571311951</v>
+        <v>2.24736595153809</v>
       </c>
       <c r="H168" t="n">
         <v>197676</v>
@@ -5270,7 +5270,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399333000183</v>
+        <v>2.19399309158325</v>
       </c>
       <c r="H169" t="n">
         <v>313201</v>
@@ -5357,7 +5357,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.21305465698242</v>
+        <v>2.213054895401</v>
       </c>
       <c r="H172" t="n">
         <v>375938</v>
@@ -5415,7 +5415,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24164724349976</v>
+        <v>2.24164700508118</v>
       </c>
       <c r="H174" t="n">
         <v>233862</v>
@@ -5473,7 +5473,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H176" t="n">
         <v>181659</v>
@@ -5589,7 +5589,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G180" t="n">
-        <v>2.153963804245</v>
+        <v>2.15396356582642</v>
       </c>
       <c r="H180" t="n">
         <v>353939</v>
@@ -5734,7 +5734,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484294891357</v>
+        <v>2.05484318733215</v>
       </c>
       <c r="H185" t="n">
         <v>188205</v>
@@ -5763,7 +5763,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G186" t="n">
-        <v>2.05865573883057</v>
+        <v>2.05865550041199</v>
       </c>
       <c r="H186" t="n">
         <v>162410</v>
@@ -5792,7 +5792,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724784851074</v>
+        <v>2.08724808692932</v>
       </c>
       <c r="H187" t="n">
         <v>178971</v>
@@ -5821,7 +5821,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G188" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H188" t="n">
         <v>141186</v>
@@ -5850,7 +5850,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H189" t="n">
         <v>178603</v>
@@ -5879,7 +5879,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956440925598</v>
+        <v>1.99956452846527</v>
       </c>
       <c r="H190" t="n">
         <v>412606</v>
@@ -5908,7 +5908,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H191" t="n">
         <v>217002</v>
@@ -5995,7 +5995,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H194" t="n">
         <v>156156</v>
@@ -6053,7 +6053,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H196" t="n">
         <v>598584</v>
@@ -6082,7 +6082,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H197" t="n">
         <v>249799</v>
@@ -6140,7 +6140,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G199" t="n">
-        <v>1.92713057994843</v>
+        <v>1.92713046073914</v>
       </c>
       <c r="H199" t="n">
         <v>354166</v>
@@ -6198,7 +6198,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G201" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H201" t="n">
         <v>949601</v>
@@ -6256,7 +6256,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G203" t="n">
-        <v>1.94619190692902</v>
+        <v>1.94619202613831</v>
       </c>
       <c r="H203" t="n">
         <v>236649</v>
@@ -6343,7 +6343,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G206" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H206" t="n">
         <v>789726</v>
@@ -6372,7 +6372,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H207" t="n">
         <v>580889</v>
@@ -6401,7 +6401,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G208" t="n">
-        <v>1.90806889533997</v>
+        <v>1.90806877613068</v>
       </c>
       <c r="H208" t="n">
         <v>711737</v>
@@ -6430,7 +6430,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>1.91759955883026</v>
+        <v>1.91759967803955</v>
       </c>
       <c r="H209" t="n">
         <v>998577</v>
@@ -6488,7 +6488,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803925037384</v>
       </c>
       <c r="H211" t="n">
         <v>545183</v>
@@ -6546,7 +6546,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G213" t="n">
-        <v>1.8642270565033</v>
+        <v>1.86422693729401</v>
       </c>
       <c r="H213" t="n">
         <v>633127</v>
@@ -6575,7 +6575,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185156345367</v>
+        <v>1.87185168266296</v>
       </c>
       <c r="H214" t="n">
         <v>537617</v>
@@ -6604,7 +6604,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803925037384</v>
       </c>
       <c r="H215" t="n">
         <v>225249</v>
@@ -6720,7 +6720,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038533687592</v>
+        <v>1.82038521766663</v>
       </c>
       <c r="H219" t="n">
         <v>227009</v>
@@ -6807,7 +6807,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95762884616852</v>
+        <v>1.95762872695923</v>
       </c>
       <c r="H222" t="n">
         <v>2654520</v>
@@ -6894,7 +6894,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G225" t="n">
-        <v>1.8394467830658</v>
+        <v>1.83944690227509</v>
       </c>
       <c r="H225" t="n">
         <v>728977</v>
@@ -6952,7 +6952,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>1.81561994552612</v>
+        <v>1.81561982631683</v>
       </c>
       <c r="H227" t="n">
         <v>1092489</v>
@@ -6981,7 +6981,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H228" t="n">
         <v>443928</v>
@@ -7010,7 +7010,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>1.78130877017975</v>
+        <v>1.78130888938904</v>
       </c>
       <c r="H229" t="n">
         <v>921990</v>
@@ -7039,7 +7039,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G230" t="n">
-        <v>1.78512132167816</v>
+        <v>1.78512120246887</v>
       </c>
       <c r="H230" t="n">
         <v>640171</v>
@@ -7097,7 +7097,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G232" t="n">
-        <v>1.81847906112671</v>
+        <v>1.818479180336</v>
       </c>
       <c r="H232" t="n">
         <v>294423</v>
@@ -7126,7 +7126,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H233" t="n">
         <v>212483</v>
@@ -7155,7 +7155,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.71554625034332</v>
+        <v>1.71554613113403</v>
       </c>
       <c r="H234" t="n">
         <v>705149</v>
@@ -7242,7 +7242,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509191513062</v>
+        <v>1.74509179592133</v>
       </c>
       <c r="H237" t="n">
         <v>547803</v>
@@ -7416,7 +7416,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G243" t="n">
-        <v>1.84993076324463</v>
+        <v>1.84993088245392</v>
       </c>
       <c r="H243" t="n">
         <v>467341</v>
@@ -7445,7 +7445,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.87757015228271</v>
+        <v>1.87757003307343</v>
       </c>
       <c r="H244" t="n">
         <v>527721</v>
@@ -7503,7 +7503,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G246" t="n">
-        <v>1.91378700733185</v>
+        <v>1.91378712654114</v>
       </c>
       <c r="H246" t="n">
         <v>567797</v>
@@ -7532,7 +7532,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H247" t="n">
         <v>435355</v>
@@ -7590,7 +7590,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G249" t="n">
-        <v>1.95953512191772</v>
+        <v>1.95953500270844</v>
       </c>
       <c r="H249" t="n">
         <v>720423</v>
@@ -7619,7 +7619,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H250" t="n">
         <v>638755</v>
@@ -7677,7 +7677,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H252" t="n">
         <v>603474</v>
@@ -7706,7 +7706,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H253" t="n">
         <v>461640</v>
@@ -7735,7 +7735,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G254" t="n">
-        <v>1.97097218036652</v>
+        <v>1.97097206115723</v>
       </c>
       <c r="H254" t="n">
         <v>225821</v>
@@ -7764,7 +7764,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575233459473</v>
+        <v>1.99575245380402</v>
       </c>
       <c r="H255" t="n">
         <v>1478455</v>
@@ -7880,7 +7880,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G259" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H259" t="n">
         <v>1171318</v>
@@ -7909,7 +7909,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674958229065</v>
+        <v>2.05674934387207</v>
       </c>
       <c r="H260" t="n">
         <v>1146682</v>
@@ -7938,7 +7938,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G261" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H261" t="n">
         <v>1109093</v>
@@ -7967,7 +7967,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437397003174</v>
+        <v>2.06437420845032</v>
       </c>
       <c r="H262" t="n">
         <v>432968</v>
@@ -7996,7 +7996,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G263" t="n">
-        <v>2.00909519195557</v>
+        <v>2.00909543037415</v>
       </c>
       <c r="H263" t="n">
         <v>959315</v>
@@ -8112,7 +8112,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.09677863121033</v>
+        <v>2.09677886962891</v>
       </c>
       <c r="H267" t="n">
         <v>1644351</v>
@@ -8141,7 +8141,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G268" t="n">
-        <v>2.00718927383423</v>
+        <v>2.00718903541565</v>
       </c>
       <c r="H268" t="n">
         <v>1731581</v>
@@ -8199,7 +8199,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G270" t="n">
-        <v>1.91378700733185</v>
+        <v>1.91378712654114</v>
       </c>
       <c r="H270" t="n">
         <v>1352186</v>
@@ -8228,7 +8228,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334731578827</v>
+        <v>1.96334755420685</v>
       </c>
       <c r="H271" t="n">
         <v>1260265</v>
@@ -8257,7 +8257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.93475496768951</v>
+        <v>1.9347550868988</v>
       </c>
       <c r="H272" t="n">
         <v>1120465</v>
@@ -8286,7 +8286,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H273" t="n">
         <v>655413</v>
@@ -8315,7 +8315,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H274" t="n">
         <v>752887</v>
@@ -8344,7 +8344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H275" t="n">
         <v>590585</v>
@@ -8402,7 +8402,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H277" t="n">
         <v>1178960</v>
@@ -8431,7 +8431,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G278" t="n">
-        <v>1.94619190692902</v>
+        <v>1.94619202613831</v>
       </c>
       <c r="H278" t="n">
         <v>429988</v>
@@ -8460,7 +8460,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330326557159</v>
+        <v>1.90330338478088</v>
       </c>
       <c r="H279" t="n">
         <v>1004346</v>
@@ -8489,7 +8489,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G280" t="n">
-        <v>1.85946154594421</v>
+        <v>1.8594616651535</v>
       </c>
       <c r="H280" t="n">
         <v>1197568</v>
@@ -8547,7 +8547,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G282" t="n">
-        <v>1.8642270565033</v>
+        <v>1.86422693729401</v>
       </c>
       <c r="H282" t="n">
         <v>780479</v>
@@ -8576,7 +8576,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.81561994552612</v>
+        <v>1.81561982631683</v>
       </c>
       <c r="H283" t="n">
         <v>878438</v>
@@ -8692,7 +8692,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G287" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H287" t="n">
         <v>1598284</v>
@@ -8721,7 +8721,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G288" t="n">
-        <v>1.89472568035126</v>
+        <v>1.89472556114197</v>
       </c>
       <c r="H288" t="n">
         <v>588961</v>
@@ -8808,7 +8808,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G291" t="n">
-        <v>1.93666136264801</v>
+        <v>1.93666124343872</v>
       </c>
       <c r="H291" t="n">
         <v>660166</v>
@@ -8837,7 +8837,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G292" t="n">
-        <v>1.92713057994843</v>
+        <v>1.92713046073914</v>
       </c>
       <c r="H292" t="n">
         <v>475359</v>
@@ -8924,7 +8924,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G295" t="n">
-        <v>1.9195054769516</v>
+        <v>1.91950559616089</v>
       </c>
       <c r="H295" t="n">
         <v>317758</v>
@@ -8953,7 +8953,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G296" t="n">
-        <v>1.89091312885284</v>
+        <v>1.89091336727142</v>
       </c>
       <c r="H296" t="n">
         <v>272700</v>
@@ -9040,7 +9040,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H299" t="n">
         <v>494953</v>
@@ -9069,7 +9069,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478437423706</v>
+        <v>1.97478449344635</v>
       </c>
       <c r="H300" t="n">
         <v>1084282</v>
@@ -9098,7 +9098,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G301" t="n">
-        <v>1.95762884616852</v>
+        <v>1.95762872695923</v>
       </c>
       <c r="H301" t="n">
         <v>941040</v>
@@ -9127,7 +9127,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G302" t="n">
-        <v>1.87280488014221</v>
+        <v>1.87280476093292</v>
       </c>
       <c r="H302" t="n">
         <v>4452878</v>
@@ -9156,7 +9156,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471091747284</v>
+        <v>1.87471079826355</v>
       </c>
       <c r="H303" t="n">
         <v>726032</v>
@@ -9243,7 +9243,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G306" t="n">
-        <v>1.86994540691376</v>
+        <v>1.86994552612305</v>
       </c>
       <c r="H306" t="n">
         <v>388137</v>
@@ -9330,7 +9330,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H309" t="n">
         <v>821834</v>
@@ -9359,7 +9359,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G310" t="n">
-        <v>2.01481413841248</v>
+        <v>2.0148138999939</v>
       </c>
       <c r="H310" t="n">
         <v>1837811</v>
@@ -9388,7 +9388,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G311" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H311" t="n">
         <v>3113532</v>
@@ -9504,7 +9504,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H315" t="n">
         <v>682468</v>
@@ -9591,7 +9591,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>2.22067928314209</v>
+        <v>2.22067904472351</v>
       </c>
       <c r="H318" t="n">
         <v>2072704</v>
@@ -9620,7 +9620,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G319" t="n">
-        <v>2.3502984046936</v>
+        <v>2.35029864311218</v>
       </c>
       <c r="H319" t="n">
         <v>3123574</v>
@@ -9649,7 +9649,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>2.25880265235901</v>
+        <v>2.25880241394043</v>
       </c>
       <c r="H320" t="n">
         <v>1458698</v>
@@ -9678,7 +9678,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.25880265235901</v>
+        <v>2.25880241394043</v>
       </c>
       <c r="H321" t="n">
         <v>490380</v>
@@ -9707,7 +9707,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G322" t="n">
-        <v>2.24736571311951</v>
+        <v>2.24736595153809</v>
       </c>
       <c r="H322" t="n">
         <v>838718</v>
@@ -9736,7 +9736,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G323" t="n">
-        <v>2.28548884391785</v>
+        <v>2.28548908233643</v>
       </c>
       <c r="H323" t="n">
         <v>900752</v>
@@ -9765,7 +9765,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H324" t="n">
         <v>869705</v>
@@ -9823,7 +9823,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>2.22067928314209</v>
+        <v>2.22067904472351</v>
       </c>
       <c r="H326" t="n">
         <v>1037293</v>
@@ -9852,7 +9852,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H327" t="n">
         <v>791379</v>
@@ -9910,7 +9910,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G329" t="n">
-        <v>2.30836272239685</v>
+        <v>2.30836296081543</v>
       </c>
       <c r="H329" t="n">
         <v>1324811</v>
@@ -9939,7 +9939,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645656585693</v>
+        <v>2.30645704269409</v>
       </c>
       <c r="H330" t="n">
         <v>409387</v>
@@ -9997,7 +9997,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H332" t="n">
         <v>380492</v>
@@ -10026,7 +10026,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H333" t="n">
         <v>427893</v>
@@ -10113,7 +10113,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>2.39414000511169</v>
+        <v>2.39414024353027</v>
       </c>
       <c r="H336" t="n">
         <v>1849332</v>
@@ -10142,7 +10142,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G337" t="n">
-        <v>2.42463874816895</v>
+        <v>2.42463850975037</v>
       </c>
       <c r="H337" t="n">
         <v>563874</v>
@@ -10229,7 +10229,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36554789543152</v>
+        <v>2.36554765701294</v>
       </c>
       <c r="H340" t="n">
         <v>423860</v>
@@ -10316,7 +10316,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41129541397095</v>
+        <v>2.41129565238953</v>
       </c>
       <c r="H343" t="n">
         <v>830346</v>
@@ -10635,7 +10635,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G354" t="n">
-        <v>2.60572409629822</v>
+        <v>2.6057243347168</v>
       </c>
       <c r="H354" t="n">
         <v>907898</v>
@@ -10693,7 +10693,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058856010437</v>
+        <v>2.60058832168579</v>
       </c>
       <c r="H356" t="n">
         <v>605694</v>
@@ -10925,7 +10925,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806670188904</v>
+        <v>2.70806646347046</v>
       </c>
       <c r="H364" t="n">
         <v>849448</v>
@@ -10983,7 +10983,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715992927551</v>
+        <v>2.77715969085693</v>
       </c>
       <c r="H366" t="n">
         <v>1578655</v>
@@ -11128,7 +11128,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H371" t="n">
         <v>692586</v>
@@ -11157,7 +11157,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.72917866706848</v>
+        <v>2.7291784286499</v>
       </c>
       <c r="H372" t="n">
         <v>600785</v>
@@ -11331,7 +11331,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514119148254</v>
+        <v>2.82514095306396</v>
       </c>
       <c r="H378" t="n">
         <v>369015</v>
@@ -11447,7 +11447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H382" t="n">
         <v>194578</v>
@@ -11534,7 +11534,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H385" t="n">
         <v>512623</v>
@@ -11621,7 +11621,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.89807271957397</v>
+        <v>2.8980724811554</v>
       </c>
       <c r="H388" t="n">
         <v>1185420</v>
@@ -11766,7 +11766,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H393" t="n">
         <v>1082817</v>
@@ -11795,7 +11795,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H394" t="n">
         <v>382748</v>
@@ -11940,7 +11940,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363159179688</v>
+        <v>3.00363183021545</v>
       </c>
       <c r="H399" t="n">
         <v>217171</v>
@@ -11969,7 +11969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757537841797</v>
+        <v>3.14757561683655</v>
       </c>
       <c r="H400" t="n">
         <v>1320738</v>
@@ -12288,7 +12288,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343891143799</v>
+        <v>3.29343867301941</v>
       </c>
       <c r="H411" t="n">
         <v>758243</v>
@@ -12375,7 +12375,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H414" t="n">
         <v>480519</v>
@@ -12462,7 +12462,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818422317505</v>
+        <v>3.22818446159363</v>
       </c>
       <c r="H417" t="n">
         <v>285532</v>
@@ -12491,7 +12491,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H418" t="n">
         <v>195515</v>
@@ -12636,7 +12636,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596076965332</v>
+        <v>3.18596053123474</v>
       </c>
       <c r="H423" t="n">
         <v>127820</v>
@@ -12694,7 +12694,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040189743042</v>
+        <v>3.08040165901184</v>
       </c>
       <c r="H425" t="n">
         <v>401854</v>
@@ -12752,7 +12752,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H427" t="n">
         <v>748285</v>
@@ -12781,7 +12781,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707225799561</v>
+        <v>3.20707249641418</v>
       </c>
       <c r="H428" t="n">
         <v>535469</v>
@@ -12839,7 +12839,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020272254944</v>
+        <v>3.18020296096802</v>
       </c>
       <c r="H430" t="n">
         <v>159000</v>
@@ -13042,7 +13042,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H437" t="n">
         <v>851102</v>
@@ -13100,7 +13100,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H439" t="n">
         <v>269780</v>
@@ -13129,7 +13129,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H440" t="n">
         <v>183536</v>
@@ -13245,7 +13245,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H444" t="n">
         <v>548564</v>
@@ -13303,7 +13303,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647592544556</v>
+        <v>3.50647616386414</v>
       </c>
       <c r="H446" t="n">
         <v>1496771</v>
@@ -13361,7 +13361,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809101104736</v>
+        <v>3.46809077262878</v>
       </c>
       <c r="H448" t="n">
         <v>331930</v>
@@ -13622,7 +13622,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899778366089</v>
+        <v>3.39899802207947</v>
       </c>
       <c r="H457" t="n">
         <v>786922</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H458" t="n">
         <v>169837</v>
@@ -13680,7 +13680,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889855384827</v>
+        <v>3.44889831542969</v>
       </c>
       <c r="H459" t="n">
         <v>96243</v>
@@ -14028,7 +14028,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940745353699</v>
+        <v>3.57940769195557</v>
       </c>
       <c r="H471" t="n">
         <v>517225</v>
@@ -14086,7 +14086,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264364242554</v>
+        <v>3.69264340400696</v>
       </c>
       <c r="H473" t="n">
         <v>1575544</v>
@@ -14115,7 +14115,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122749328613</v>
+        <v>3.63122725486755</v>
       </c>
       <c r="H474" t="n">
         <v>392936</v>
@@ -14173,7 +14173,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223397254944</v>
+        <v>3.51223373413086</v>
       </c>
       <c r="H476" t="n">
         <v>1052005</v>
@@ -14289,7 +14289,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H480" t="n">
         <v>1897823</v>
@@ -14318,7 +14318,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H481" t="n">
         <v>1344877</v>
@@ -14376,7 +14376,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502944946289</v>
+        <v>2.49502921104431</v>
       </c>
       <c r="H483" t="n">
         <v>1113397</v>
@@ -14434,7 +14434,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736440658569</v>
+        <v>2.86736464500427</v>
       </c>
       <c r="H485" t="n">
         <v>2335973</v>
@@ -14637,7 +14637,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H492" t="n">
         <v>360031</v>
@@ -14840,7 +14840,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.8481719493866</v>
+        <v>2.84817218780518</v>
       </c>
       <c r="H499" t="n">
         <v>177776</v>
@@ -14956,7 +14956,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H503" t="n">
         <v>781804</v>
@@ -15014,7 +15014,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H505" t="n">
         <v>362332</v>
@@ -15043,7 +15043,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H506" t="n">
         <v>249155</v>
@@ -15072,7 +15072,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H507" t="n">
         <v>199788</v>
@@ -15101,7 +15101,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230865478516</v>
+        <v>2.70230889320374</v>
       </c>
       <c r="H508" t="n">
         <v>228947</v>
@@ -15130,7 +15130,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H509" t="n">
         <v>305291</v>
@@ -15275,7 +15275,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928391456604</v>
+        <v>2.86928367614746</v>
       </c>
       <c r="H514" t="n">
         <v>468533</v>
@@ -15420,7 +15420,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H519" t="n">
         <v>477584</v>
@@ -15478,7 +15478,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H521" t="n">
         <v>402806</v>
@@ -15565,7 +15565,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877453804016</v>
+        <v>2.73877477645874</v>
       </c>
       <c r="H524" t="n">
         <v>549359</v>
@@ -15594,7 +15594,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563805580139</v>
+        <v>2.57563829421997</v>
       </c>
       <c r="H525" t="n">
         <v>7158793</v>
@@ -15652,7 +15652,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614743232727</v>
+        <v>2.70614719390869</v>
       </c>
       <c r="H527" t="n">
         <v>1136471</v>
@@ -15739,7 +15739,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H530" t="n">
         <v>821537</v>
@@ -15797,7 +15797,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H532" t="n">
         <v>874097</v>
@@ -15942,7 +15942,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H537" t="n">
         <v>1383977</v>
@@ -16377,7 +16377,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685526847839</v>
+        <v>2.73685550689697</v>
       </c>
       <c r="H552" t="n">
         <v>1598171</v>
@@ -16406,7 +16406,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H553" t="n">
         <v>899641</v>
@@ -16435,7 +16435,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H554" t="n">
         <v>740489</v>
@@ -16464,7 +16464,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503570556641</v>
+        <v>2.68503546714783</v>
       </c>
       <c r="H555" t="n">
         <v>586866</v>
@@ -16522,7 +16522,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H557" t="n">
         <v>744218</v>
@@ -16638,7 +16638,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281779289246</v>
+        <v>2.83281803131104</v>
       </c>
       <c r="H561" t="n">
         <v>568824</v>
@@ -16667,7 +16667,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019068717957</v>
+        <v>2.80019092559814</v>
       </c>
       <c r="H562" t="n">
         <v>509608</v>
@@ -16783,7 +16783,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H566" t="n">
         <v>264829</v>
@@ -16812,7 +16812,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75028991699219</v>
+        <v>2.75029015541077</v>
       </c>
       <c r="H567" t="n">
         <v>219381</v>
@@ -16870,7 +16870,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H569" t="n">
         <v>328641</v>
@@ -16928,7 +16928,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978077888489</v>
+        <v>2.61978101730347</v>
       </c>
       <c r="H571" t="n">
         <v>581272</v>
@@ -17247,7 +17247,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H582" t="n">
         <v>328175</v>
@@ -17305,7 +17305,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H584" t="n">
         <v>285733</v>
@@ -17334,7 +17334,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H585" t="n">
         <v>250096</v>
@@ -17421,7 +17421,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H588" t="n">
         <v>505464</v>
@@ -17450,7 +17450,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301696777344</v>
+        <v>2.73301672935486</v>
       </c>
       <c r="H589" t="n">
         <v>256840</v>
@@ -17508,7 +17508,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H591" t="n">
         <v>1596803</v>
@@ -17595,7 +17595,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735838890076</v>
+        <v>2.67735862731934</v>
       </c>
       <c r="H594" t="n">
         <v>422850</v>
@@ -17624,7 +17624,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190500259399</v>
+        <v>2.71190524101257</v>
       </c>
       <c r="H595" t="n">
         <v>576828</v>
@@ -17682,7 +17682,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H597" t="n">
         <v>284034</v>
@@ -17711,7 +17711,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.70422792434692</v>
+        <v>2.7042281627655</v>
       </c>
       <c r="H598" t="n">
         <v>201687</v>
@@ -17827,7 +17827,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H602" t="n">
         <v>368932</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H603" t="n">
         <v>435948</v>
@@ -17972,7 +17972,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.37219715118408</v>
+        <v>2.3721969127655</v>
       </c>
       <c r="H607" t="n">
         <v>1221882</v>
@@ -79951,6 +79951,64 @@
         <v>237845</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.279000014066696</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.279000014066696</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.265500009059906</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.266999989748001</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.266999989748001</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>239560</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.266999989748001</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.271499991416931</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>406247</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599781036377</v>
+        <v>3.59599804878235</v>
       </c>
       <c r="H3" t="n">
         <v>611692</v>
@@ -485,7 +485,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62588667869568</v>
+        <v>3.62588691711426</v>
       </c>
       <c r="H4" t="n">
         <v>748185</v>
@@ -514,7 +514,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H5" t="n">
         <v>807816</v>
@@ -543,7 +543,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>3.41292905807495</v>
+        <v>3.41292929649353</v>
       </c>
       <c r="H6" t="n">
         <v>652737</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655394554138</v>
+        <v>3.44655418395996</v>
       </c>
       <c r="H8" t="n">
         <v>335339</v>
@@ -630,7 +630,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4932553768158</v>
+        <v>3.49325513839722</v>
       </c>
       <c r="H9" t="n">
         <v>197035</v>
@@ -659,7 +659,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>3.39798474311829</v>
+        <v>3.39798450469971</v>
       </c>
       <c r="H10" t="n">
         <v>829652</v>
@@ -688,7 +688,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G11" t="n">
-        <v>3.39985275268555</v>
+        <v>3.39985299110413</v>
       </c>
       <c r="H11" t="n">
         <v>1221987</v>
@@ -746,7 +746,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4278736114502</v>
+        <v>3.42787384986877</v>
       </c>
       <c r="H13" t="n">
         <v>410306</v>
@@ -804,7 +804,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.38864421844482</v>
+        <v>3.3886444568634</v>
       </c>
       <c r="H15" t="n">
         <v>742869</v>
@@ -891,7 +891,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127599716187</v>
+        <v>3.52127575874329</v>
       </c>
       <c r="H18" t="n">
         <v>372353</v>
@@ -920,7 +920,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H19" t="n">
         <v>400278</v>
@@ -949,7 +949,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062359809875</v>
+        <v>3.36062383651733</v>
       </c>
       <c r="H20" t="n">
         <v>463309</v>
@@ -978,7 +978,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G21" t="n">
-        <v>3.3269989490509</v>
+        <v>3.32699871063232</v>
       </c>
       <c r="H21" t="n">
         <v>602002</v>
@@ -1239,7 +1239,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636849403381</v>
+        <v>2.65636873245239</v>
       </c>
       <c r="H30" t="n">
         <v>718398</v>
@@ -1355,7 +1355,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45835494995117</v>
+        <v>2.45835518836975</v>
       </c>
       <c r="H34" t="n">
         <v>1399376</v>
@@ -1384,7 +1384,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.49198007583618</v>
+        <v>2.4919798374176</v>
       </c>
       <c r="H35" t="n">
         <v>844299</v>
@@ -1413,7 +1413,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>2.50318837165833</v>
+        <v>2.5031886100769</v>
       </c>
       <c r="H36" t="n">
         <v>421169</v>
@@ -1442,7 +1442,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604193687439</v>
+        <v>2.57604217529297</v>
       </c>
       <c r="H37" t="n">
         <v>886852</v>
@@ -1500,7 +1500,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395921707153</v>
+        <v>2.46395897865295</v>
       </c>
       <c r="H39" t="n">
         <v>414034</v>
@@ -1674,7 +1674,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G45" t="n">
-        <v>2.73856282234192</v>
+        <v>2.73856258392334</v>
       </c>
       <c r="H45" t="n">
         <v>644573</v>
@@ -1703,7 +1703,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988201141357</v>
+        <v>2.719881772995</v>
       </c>
       <c r="H46" t="n">
         <v>1083110</v>
@@ -1761,7 +1761,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61527109146118</v>
+        <v>2.61527132987976</v>
       </c>
       <c r="H48" t="n">
         <v>1729959</v>
@@ -1819,7 +1819,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526425361633</v>
+        <v>2.78526401519775</v>
       </c>
       <c r="H50" t="n">
         <v>3240146</v>
@@ -1848,7 +1848,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>2.78339576721191</v>
+        <v>2.78339600563049</v>
       </c>
       <c r="H51" t="n">
         <v>927105</v>
@@ -1935,7 +1935,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G54" t="n">
-        <v>2.73856282234192</v>
+        <v>2.73856258392334</v>
       </c>
       <c r="H54" t="n">
         <v>631029</v>
@@ -1964,7 +1964,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H55" t="n">
         <v>571416</v>
@@ -1993,7 +1993,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350689888</v>
+        <v>2.75350713729858</v>
       </c>
       <c r="H56" t="n">
         <v>617931</v>
@@ -2051,7 +2051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.71801424026489</v>
+        <v>2.71801400184631</v>
       </c>
       <c r="H58" t="n">
         <v>634534</v>
@@ -2080,7 +2080,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988201141357</v>
+        <v>2.719881772995</v>
       </c>
       <c r="H59" t="n">
         <v>486311</v>
@@ -2109,7 +2109,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G60" t="n">
-        <v>2.63768768310547</v>
+        <v>2.63768792152405</v>
       </c>
       <c r="H60" t="n">
         <v>807171</v>
@@ -2138,7 +2138,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65076446533203</v>
+        <v>2.65076422691345</v>
       </c>
       <c r="H61" t="n">
         <v>421361</v>
@@ -2225,7 +2225,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G64" t="n">
-        <v>2.58164620399475</v>
+        <v>2.58164644241333</v>
       </c>
       <c r="H64" t="n">
         <v>791010</v>
@@ -2283,7 +2283,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G66" t="n">
-        <v>2.50318837165833</v>
+        <v>2.5031886100769</v>
       </c>
       <c r="H66" t="n">
         <v>580199</v>
@@ -2370,7 +2370,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791042327881</v>
+        <v>2.57791018486023</v>
       </c>
       <c r="H69" t="n">
         <v>847648</v>
@@ -2544,7 +2544,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59285473823547</v>
+        <v>2.59285449981689</v>
       </c>
       <c r="H75" t="n">
         <v>375927</v>
@@ -2573,7 +2573,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.6264796257019</v>
+        <v>2.62647986412048</v>
       </c>
       <c r="H76" t="n">
         <v>520133</v>
@@ -2602,7 +2602,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395142555237</v>
       </c>
       <c r="H77" t="n">
         <v>329924</v>
@@ -2631,7 +2631,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.6264796257019</v>
+        <v>2.62647986412048</v>
       </c>
       <c r="H78" t="n">
         <v>392451</v>
@@ -2660,7 +2660,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384077072144</v>
+        <v>2.66384053230286</v>
       </c>
       <c r="H79" t="n">
         <v>306336</v>
@@ -2689,7 +2689,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H80" t="n">
         <v>263802</v>
@@ -2718,7 +2718,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>2.61527109146118</v>
+        <v>2.61527132987976</v>
       </c>
       <c r="H81" t="n">
         <v>515442</v>
@@ -2776,7 +2776,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395142555237</v>
       </c>
       <c r="H83" t="n">
         <v>139836</v>
@@ -2805,7 +2805,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G84" t="n">
-        <v>2.62834763526917</v>
+        <v>2.62834787368774</v>
       </c>
       <c r="H84" t="n">
         <v>97873</v>
@@ -2834,7 +2834,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263247489929</v>
+        <v>2.65263223648071</v>
       </c>
       <c r="H85" t="n">
         <v>83792</v>
@@ -2863,7 +2863,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208389282227</v>
+        <v>2.63208365440369</v>
       </c>
       <c r="H86" t="n">
         <v>115454</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066040992737</v>
+        <v>2.51066017150879</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3008,7 +3008,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.5517578125</v>
+        <v>2.55175757408142</v>
       </c>
       <c r="H91" t="n">
         <v>189126</v>
@@ -3037,7 +3037,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G92" t="n">
-        <v>2.52934074401855</v>
+        <v>2.52934098243713</v>
       </c>
       <c r="H92" t="n">
         <v>162932</v>
@@ -3124,7 +3124,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098672866821</v>
+        <v>2.59098649024963</v>
       </c>
       <c r="H95" t="n">
         <v>301461</v>
@@ -3269,7 +3269,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487400054932</v>
       </c>
       <c r="H100" t="n">
         <v>408349</v>
@@ -3298,7 +3298,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487400054932</v>
       </c>
       <c r="H101" t="n">
         <v>240708</v>
@@ -3704,7 +3704,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G115" t="n">
-        <v>2.82874536514282</v>
+        <v>2.82874512672424</v>
       </c>
       <c r="H115" t="n">
         <v>388875</v>
@@ -3849,7 +3849,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85352540016174</v>
+        <v>2.85352563858032</v>
       </c>
       <c r="H120" t="n">
         <v>374301</v>
@@ -3965,7 +3965,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>2.65909695625305</v>
+        <v>2.65909671783447</v>
       </c>
       <c r="H124" t="n">
         <v>451934</v>
@@ -3994,7 +3994,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760096549988</v>
+        <v>2.56760120391846</v>
       </c>
       <c r="H125" t="n">
         <v>525319</v>
@@ -4110,7 +4110,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72200012207031</v>
+        <v>2.72199988365173</v>
       </c>
       <c r="H129" t="n">
         <v>335865</v>
@@ -4139,7 +4139,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>2.59619355201721</v>
+        <v>2.59619331359863</v>
       </c>
       <c r="H130" t="n">
         <v>222114</v>
@@ -4197,7 +4197,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G132" t="n">
-        <v>2.46276211738586</v>
+        <v>2.46276235580444</v>
       </c>
       <c r="H132" t="n">
         <v>543169</v>
@@ -4255,7 +4255,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563623428345</v>
       </c>
       <c r="H134" t="n">
         <v>360643</v>
@@ -4284,7 +4284,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>2.55425786972046</v>
+        <v>2.55425763130188</v>
       </c>
       <c r="H135" t="n">
         <v>415438</v>
@@ -4313,7 +4313,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.57141351699829</v>
+        <v>2.57141327857971</v>
       </c>
       <c r="H136" t="n">
         <v>548868</v>
@@ -4429,7 +4429,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G140" t="n">
-        <v>2.6057243347168</v>
+        <v>2.60572409629822</v>
       </c>
       <c r="H140" t="n">
         <v>864905</v>
@@ -4458,7 +4458,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53329014778137</v>
+        <v>2.53328990936279</v>
       </c>
       <c r="H141" t="n">
         <v>619648</v>
@@ -4545,7 +4545,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.55425786972046</v>
+        <v>2.55425763130188</v>
       </c>
       <c r="H144" t="n">
         <v>360993</v>
@@ -4690,7 +4690,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.4551374912262</v>
+        <v>2.45513725280762</v>
       </c>
       <c r="H149" t="n">
         <v>1587031</v>
@@ -4719,7 +4719,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698459625244</v>
+        <v>2.37698483467102</v>
       </c>
       <c r="H150" t="n">
         <v>918463</v>
@@ -4777,7 +4777,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G152" t="n">
-        <v>2.24164700508118</v>
+        <v>2.24164724349976</v>
       </c>
       <c r="H152" t="n">
         <v>402686</v>
@@ -4806,7 +4806,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G153" t="n">
-        <v>2.24927163124084</v>
+        <v>2.24927186965942</v>
       </c>
       <c r="H153" t="n">
         <v>332222</v>
@@ -4864,7 +4864,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G155" t="n">
-        <v>2.32551860809326</v>
+        <v>2.32551836967468</v>
       </c>
       <c r="H155" t="n">
         <v>305944</v>
@@ -4893,7 +4893,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220456123352</v>
+        <v>2.35220432281494</v>
       </c>
       <c r="H156" t="n">
         <v>229323</v>
@@ -4951,7 +4951,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220456123352</v>
+        <v>2.35220432281494</v>
       </c>
       <c r="H158" t="n">
         <v>512824</v>
@@ -4980,7 +4980,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>2.33504939079285</v>
+        <v>2.33504915237427</v>
       </c>
       <c r="H159" t="n">
         <v>248797</v>
@@ -5096,7 +5096,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.17493152618408</v>
+        <v>2.17493176460266</v>
       </c>
       <c r="H163" t="n">
         <v>393671</v>
@@ -5125,7 +5125,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.17493152618408</v>
+        <v>2.17493176460266</v>
       </c>
       <c r="H164" t="n">
         <v>347934</v>
@@ -5212,7 +5212,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258543968201</v>
+        <v>2.22258567810059</v>
       </c>
       <c r="H167" t="n">
         <v>324769</v>
@@ -5270,7 +5270,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399309158325</v>
+        <v>2.19399333000183</v>
       </c>
       <c r="H169" t="n">
         <v>313201</v>
@@ -5299,7 +5299,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.17683744430542</v>
+        <v>2.176837682724</v>
       </c>
       <c r="H170" t="n">
         <v>631538</v>
@@ -5357,7 +5357,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.213054895401</v>
+        <v>2.21305465698242</v>
       </c>
       <c r="H172" t="n">
         <v>375938</v>
@@ -5415,7 +5415,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24164700508118</v>
+        <v>2.24164724349976</v>
       </c>
       <c r="H174" t="n">
         <v>233862</v>
@@ -5473,7 +5473,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H176" t="n">
         <v>181659</v>
@@ -5502,7 +5502,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H177" t="n">
         <v>239497</v>
@@ -5531,7 +5531,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H178" t="n">
         <v>189602</v>
@@ -5589,7 +5589,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G180" t="n">
-        <v>2.15396356582642</v>
+        <v>2.153963804245</v>
       </c>
       <c r="H180" t="n">
         <v>353939</v>
@@ -5734,7 +5734,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484318733215</v>
+        <v>2.05484294891357</v>
       </c>
       <c r="H185" t="n">
         <v>188205</v>
@@ -5763,7 +5763,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G186" t="n">
-        <v>2.05865550041199</v>
+        <v>2.05865573883057</v>
       </c>
       <c r="H186" t="n">
         <v>162410</v>
@@ -5792,7 +5792,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724808692932</v>
+        <v>2.08724784851074</v>
       </c>
       <c r="H187" t="n">
         <v>178971</v>
@@ -5850,7 +5850,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.0624680519104</v>
+        <v>2.06246781349182</v>
       </c>
       <c r="H189" t="n">
         <v>178603</v>
@@ -5879,7 +5879,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956452846527</v>
+        <v>1.99956464767456</v>
       </c>
       <c r="H190" t="n">
         <v>412606</v>
@@ -5908,7 +5908,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765813350677</v>
+        <v>1.99765849113464</v>
       </c>
       <c r="H191" t="n">
         <v>217002</v>
@@ -5995,7 +5995,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193978309631</v>
+        <v>1.99193966388702</v>
       </c>
       <c r="H194" t="n">
         <v>156156</v>
@@ -6053,7 +6053,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.99003386497498</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H196" t="n">
         <v>598584</v>
@@ -6082,7 +6082,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.99003386497498</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H197" t="n">
         <v>249799</v>
@@ -6111,7 +6111,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H198" t="n">
         <v>370597</v>
@@ -6169,7 +6169,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191061496735</v>
+        <v>1.95191049575806</v>
       </c>
       <c r="H200" t="n">
         <v>1432038</v>
@@ -6227,7 +6227,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G202" t="n">
-        <v>1.92903637886047</v>
+        <v>1.92903649806976</v>
       </c>
       <c r="H202" t="n">
         <v>442072</v>
@@ -6314,7 +6314,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G205" t="n">
-        <v>1.92903637886047</v>
+        <v>1.92903649806976</v>
       </c>
       <c r="H205" t="n">
         <v>687316</v>
@@ -6372,7 +6372,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616250038147</v>
+        <v>1.90616261959076</v>
       </c>
       <c r="H207" t="n">
         <v>580889</v>
@@ -6488,7 +6488,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803925037384</v>
+        <v>1.86803948879242</v>
       </c>
       <c r="H211" t="n">
         <v>545183</v>
@@ -6517,7 +6517,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186632633209</v>
+        <v>1.89186644554138</v>
       </c>
       <c r="H212" t="n">
         <v>467560</v>
@@ -6575,7 +6575,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185168266296</v>
+        <v>1.87185156345367</v>
       </c>
       <c r="H214" t="n">
         <v>537617</v>
@@ -6604,7 +6604,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803925037384</v>
+        <v>1.86803948879242</v>
       </c>
       <c r="H215" t="n">
         <v>225249</v>
@@ -6720,7 +6720,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038521766663</v>
+        <v>1.82038533687592</v>
       </c>
       <c r="H219" t="n">
         <v>227009</v>
@@ -6807,7 +6807,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95762872695923</v>
+        <v>1.95762884616852</v>
       </c>
       <c r="H222" t="n">
         <v>2654520</v>
@@ -6894,7 +6894,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G225" t="n">
-        <v>1.83944690227509</v>
+        <v>1.8394467830658</v>
       </c>
       <c r="H225" t="n">
         <v>728977</v>
@@ -6981,7 +6981,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179286956787</v>
+        <v>1.79179275035858</v>
       </c>
       <c r="H228" t="n">
         <v>443928</v>
@@ -7039,7 +7039,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G230" t="n">
-        <v>1.78512120246887</v>
+        <v>1.78512132167816</v>
       </c>
       <c r="H230" t="n">
         <v>640171</v>
@@ -7097,7 +7097,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G232" t="n">
-        <v>1.818479180336</v>
+        <v>1.81847906112671</v>
       </c>
       <c r="H232" t="n">
         <v>294423</v>
@@ -7126,7 +7126,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179286956787</v>
+        <v>1.79179275035858</v>
       </c>
       <c r="H233" t="n">
         <v>212483</v>
@@ -7155,7 +7155,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.71554613113403</v>
+        <v>1.71554625034332</v>
       </c>
       <c r="H234" t="n">
         <v>705149</v>
@@ -7242,7 +7242,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509179592133</v>
+        <v>1.74509191513062</v>
       </c>
       <c r="H237" t="n">
         <v>547803</v>
@@ -7300,7 +7300,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273118495941</v>
+        <v>1.7727313041687</v>
       </c>
       <c r="H239" t="n">
         <v>570721</v>
@@ -7358,7 +7358,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372831344604</v>
+        <v>1.83372843265533</v>
       </c>
       <c r="H241" t="n">
         <v>613856</v>
@@ -7387,7 +7387,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660231113434</v>
+        <v>1.85660243034363</v>
       </c>
       <c r="H242" t="n">
         <v>464622</v>
@@ -7416,7 +7416,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G243" t="n">
-        <v>1.84993088245392</v>
+        <v>1.84993076324463</v>
       </c>
       <c r="H243" t="n">
         <v>467341</v>
@@ -7503,7 +7503,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G246" t="n">
-        <v>1.91378712654114</v>
+        <v>1.91378700733185</v>
       </c>
       <c r="H246" t="n">
         <v>567797</v>
@@ -7532,7 +7532,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616250038147</v>
+        <v>1.90616261959076</v>
       </c>
       <c r="H247" t="n">
         <v>435355</v>
@@ -7561,7 +7561,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H248" t="n">
         <v>502927</v>
@@ -7619,7 +7619,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.95572292804718</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H250" t="n">
         <v>638755</v>
@@ -7677,7 +7677,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287821769714</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H252" t="n">
         <v>603474</v>
@@ -7706,7 +7706,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.95572292804718</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H253" t="n">
         <v>461640</v>
@@ -7735,7 +7735,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G254" t="n">
-        <v>1.97097206115723</v>
+        <v>1.97097218036652</v>
       </c>
       <c r="H254" t="n">
         <v>225821</v>
@@ -7764,7 +7764,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575245380402</v>
+        <v>1.99575257301331</v>
       </c>
       <c r="H255" t="n">
         <v>1478455</v>
@@ -7851,7 +7851,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252662658691</v>
+        <v>2.14252686500549</v>
       </c>
       <c r="H258" t="n">
         <v>1054327</v>
@@ -7909,7 +7909,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674934387207</v>
+        <v>2.05674958229065</v>
       </c>
       <c r="H260" t="n">
         <v>1146682</v>
@@ -7967,7 +7967,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437420845032</v>
+        <v>2.06437373161316</v>
       </c>
       <c r="H262" t="n">
         <v>432968</v>
@@ -8199,7 +8199,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G270" t="n">
-        <v>1.91378712654114</v>
+        <v>1.91378700733185</v>
       </c>
       <c r="H270" t="n">
         <v>1352186</v>
@@ -8228,7 +8228,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334755420685</v>
+        <v>1.96334743499756</v>
       </c>
       <c r="H271" t="n">
         <v>1260265</v>
@@ -8257,7 +8257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.9347550868988</v>
+        <v>1.93475496768951</v>
       </c>
       <c r="H272" t="n">
         <v>1120465</v>
@@ -8286,7 +8286,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287821769714</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H273" t="n">
         <v>655413</v>
@@ -8315,7 +8315,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193978309631</v>
+        <v>1.99193966388702</v>
       </c>
       <c r="H274" t="n">
         <v>752887</v>
@@ -8344,7 +8344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287821769714</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H275" t="n">
         <v>590585</v>
@@ -8402,7 +8402,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765813350677</v>
+        <v>1.99765849113464</v>
       </c>
       <c r="H277" t="n">
         <v>1178960</v>
@@ -8460,7 +8460,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330338478088</v>
+        <v>1.90330326557159</v>
       </c>
       <c r="H279" t="n">
         <v>1004346</v>
@@ -8489,7 +8489,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G280" t="n">
-        <v>1.8594616651535</v>
+        <v>1.85946154594421</v>
       </c>
       <c r="H280" t="n">
         <v>1197568</v>
@@ -8518,7 +8518,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>1.8689923286438</v>
+        <v>1.86899244785309</v>
       </c>
       <c r="H281" t="n">
         <v>1316326</v>
@@ -8634,7 +8634,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G285" t="n">
-        <v>1.81371366977692</v>
+        <v>1.81371355056763</v>
       </c>
       <c r="H285" t="n">
         <v>2245645</v>
@@ -8663,7 +8663,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H286" t="n">
         <v>1757407</v>
@@ -8721,7 +8721,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G288" t="n">
-        <v>1.89472556114197</v>
+        <v>1.89472568035126</v>
       </c>
       <c r="H288" t="n">
         <v>588961</v>
@@ -8779,7 +8779,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H290" t="n">
         <v>483668</v>
@@ -8866,7 +8866,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G293" t="n">
-        <v>1.90235030651093</v>
+        <v>1.90235018730164</v>
       </c>
       <c r="H293" t="n">
         <v>452383</v>
@@ -8895,7 +8895,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.9214118719101</v>
+        <v>1.92141199111938</v>
       </c>
       <c r="H294" t="n">
         <v>315857</v>
@@ -8953,7 +8953,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G296" t="n">
-        <v>1.89091336727142</v>
+        <v>1.89091312885284</v>
       </c>
       <c r="H296" t="n">
         <v>272700</v>
@@ -8982,7 +8982,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H297" t="n">
         <v>662717</v>
@@ -9011,7 +9011,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H298" t="n">
         <v>1498299</v>
@@ -9040,7 +9040,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.95572292804718</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H299" t="n">
         <v>494953</v>
@@ -9069,7 +9069,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478449344635</v>
+        <v>1.97478461265564</v>
       </c>
       <c r="H300" t="n">
         <v>1084282</v>
@@ -9098,7 +9098,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G301" t="n">
-        <v>1.95762872695923</v>
+        <v>1.95762884616852</v>
       </c>
       <c r="H301" t="n">
         <v>941040</v>
@@ -9156,7 +9156,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471079826355</v>
+        <v>1.87471091747284</v>
       </c>
       <c r="H303" t="n">
         <v>726032</v>
@@ -9185,7 +9185,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661707401276</v>
+        <v>1.87661695480347</v>
       </c>
       <c r="H304" t="n">
         <v>488529</v>
@@ -9214,7 +9214,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G305" t="n">
-        <v>1.8689923286438</v>
+        <v>1.86899244785309</v>
       </c>
       <c r="H305" t="n">
         <v>614151</v>
@@ -9330,7 +9330,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.99003386497498</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H309" t="n">
         <v>821834</v>
@@ -9446,7 +9446,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G313" t="n">
-        <v>2.10249757766724</v>
+        <v>2.10249733924866</v>
       </c>
       <c r="H313" t="n">
         <v>1169471</v>
@@ -9504,7 +9504,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.0624680519104</v>
+        <v>2.06246781349182</v>
       </c>
       <c r="H315" t="n">
         <v>682468</v>
@@ -9562,7 +9562,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730666160583</v>
+        <v>2.16730690002441</v>
       </c>
       <c r="H317" t="n">
         <v>2091344</v>
@@ -9591,7 +9591,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>2.22067904472351</v>
+        <v>2.22067928314209</v>
       </c>
       <c r="H318" t="n">
         <v>2072704</v>
@@ -9620,7 +9620,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35029864311218</v>
+        <v>2.3502984046936</v>
       </c>
       <c r="H319" t="n">
         <v>3123574</v>
@@ -9649,7 +9649,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>2.25880241394043</v>
+        <v>2.25880265235901</v>
       </c>
       <c r="H320" t="n">
         <v>1458698</v>
@@ -9678,7 +9678,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.25880241394043</v>
+        <v>2.25880265235901</v>
       </c>
       <c r="H321" t="n">
         <v>490380</v>
@@ -9736,7 +9736,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G323" t="n">
-        <v>2.28548908233643</v>
+        <v>2.28548884391785</v>
       </c>
       <c r="H323" t="n">
         <v>900752</v>
@@ -9765,7 +9765,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H324" t="n">
         <v>869705</v>
@@ -9823,7 +9823,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>2.22067904472351</v>
+        <v>2.22067928314209</v>
       </c>
       <c r="H326" t="n">
         <v>1037293</v>
@@ -9852,7 +9852,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H327" t="n">
         <v>791379</v>
@@ -9910,7 +9910,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G329" t="n">
-        <v>2.30836296081543</v>
+        <v>2.30836272239685</v>
       </c>
       <c r="H329" t="n">
         <v>1324811</v>
@@ -9939,7 +9939,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645704269409</v>
+        <v>2.30645680427551</v>
       </c>
       <c r="H330" t="n">
         <v>409387</v>
@@ -9997,7 +9997,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H332" t="n">
         <v>380492</v>
@@ -10026,7 +10026,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H333" t="n">
         <v>427893</v>
@@ -10142,7 +10142,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G337" t="n">
-        <v>2.42463850975037</v>
+        <v>2.42463874816895</v>
       </c>
       <c r="H337" t="n">
         <v>563874</v>
@@ -10200,7 +10200,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270330429077</v>
+        <v>2.38270306587219</v>
       </c>
       <c r="H339" t="n">
         <v>350392</v>
@@ -10229,7 +10229,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36554765701294</v>
+        <v>2.3655481338501</v>
       </c>
       <c r="H340" t="n">
         <v>423860</v>
@@ -10258,7 +10258,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938973426819</v>
+        <v>2.40938949584961</v>
       </c>
       <c r="H341" t="n">
         <v>1086286</v>
@@ -10316,7 +10316,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41129565238953</v>
+        <v>2.41129541397095</v>
       </c>
       <c r="H343" t="n">
         <v>830346</v>
@@ -10403,7 +10403,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563623428345</v>
       </c>
       <c r="H346" t="n">
         <v>1281154</v>
@@ -10635,7 +10635,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G354" t="n">
-        <v>2.6057243347168</v>
+        <v>2.60572409629822</v>
       </c>
       <c r="H354" t="n">
         <v>907898</v>
@@ -10693,7 +10693,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058832168579</v>
+        <v>2.60058856010437</v>
       </c>
       <c r="H356" t="n">
         <v>605694</v>
@@ -10925,7 +10925,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806646347046</v>
+        <v>2.70806670188904</v>
       </c>
       <c r="H364" t="n">
         <v>849448</v>
@@ -10983,7 +10983,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715969085693</v>
+        <v>2.77715992927551</v>
       </c>
       <c r="H366" t="n">
         <v>1578655</v>
@@ -11128,7 +11128,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H371" t="n">
         <v>692586</v>
@@ -11157,7 +11157,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.7291784286499</v>
+        <v>2.72917866706848</v>
       </c>
       <c r="H372" t="n">
         <v>600785</v>
@@ -11331,7 +11331,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514095306396</v>
+        <v>2.82514119148254</v>
       </c>
       <c r="H378" t="n">
         <v>369015</v>
@@ -11447,7 +11447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H382" t="n">
         <v>194578</v>
@@ -11534,7 +11534,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H385" t="n">
         <v>512623</v>
@@ -11621,7 +11621,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.8980724811554</v>
+        <v>2.89807271957397</v>
       </c>
       <c r="H388" t="n">
         <v>1185420</v>
@@ -11766,7 +11766,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H393" t="n">
         <v>1082817</v>
@@ -11795,7 +11795,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H394" t="n">
         <v>382748</v>
@@ -11940,7 +11940,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363183021545</v>
+        <v>3.00363159179688</v>
       </c>
       <c r="H399" t="n">
         <v>217171</v>
@@ -11969,7 +11969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757561683655</v>
+        <v>3.14757537841797</v>
       </c>
       <c r="H400" t="n">
         <v>1320738</v>
@@ -12288,7 +12288,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343867301941</v>
+        <v>3.29343891143799</v>
       </c>
       <c r="H411" t="n">
         <v>758243</v>
@@ -12375,7 +12375,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H414" t="n">
         <v>480519</v>
@@ -12462,7 +12462,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818446159363</v>
+        <v>3.22818422317505</v>
       </c>
       <c r="H417" t="n">
         <v>285532</v>
@@ -12491,7 +12491,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H418" t="n">
         <v>195515</v>
@@ -12636,7 +12636,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596053123474</v>
+        <v>3.18596076965332</v>
       </c>
       <c r="H423" t="n">
         <v>127820</v>
@@ -12694,7 +12694,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040165901184</v>
+        <v>3.08040189743042</v>
       </c>
       <c r="H425" t="n">
         <v>401854</v>
@@ -12752,7 +12752,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H427" t="n">
         <v>748285</v>
@@ -12781,7 +12781,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707249641418</v>
+        <v>3.20707225799561</v>
       </c>
       <c r="H428" t="n">
         <v>535469</v>
@@ -12839,7 +12839,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020296096802</v>
+        <v>3.18020272254944</v>
       </c>
       <c r="H430" t="n">
         <v>159000</v>
@@ -13042,7 +13042,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H437" t="n">
         <v>851102</v>
@@ -13100,7 +13100,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H439" t="n">
         <v>269780</v>
@@ -13129,7 +13129,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H440" t="n">
         <v>183536</v>
@@ -13245,7 +13245,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H444" t="n">
         <v>548564</v>
@@ -13303,7 +13303,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647616386414</v>
+        <v>3.50647592544556</v>
       </c>
       <c r="H446" t="n">
         <v>1496771</v>
@@ -13361,7 +13361,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809077262878</v>
+        <v>3.46809101104736</v>
       </c>
       <c r="H448" t="n">
         <v>331930</v>
@@ -13622,7 +13622,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899802207947</v>
+        <v>3.39899778366089</v>
       </c>
       <c r="H457" t="n">
         <v>786922</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H458" t="n">
         <v>169837</v>
@@ -13680,7 +13680,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889831542969</v>
+        <v>3.44889855384827</v>
       </c>
       <c r="H459" t="n">
         <v>96243</v>
@@ -14028,7 +14028,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940769195557</v>
+        <v>3.57940745353699</v>
       </c>
       <c r="H471" t="n">
         <v>517225</v>
@@ -14086,7 +14086,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264340400696</v>
+        <v>3.69264364242554</v>
       </c>
       <c r="H473" t="n">
         <v>1575544</v>
@@ -14115,7 +14115,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122725486755</v>
+        <v>3.63122749328613</v>
       </c>
       <c r="H474" t="n">
         <v>392936</v>
@@ -14173,7 +14173,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223373413086</v>
+        <v>3.51223397254944</v>
       </c>
       <c r="H476" t="n">
         <v>1052005</v>
@@ -14289,7 +14289,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H480" t="n">
         <v>1897823</v>
@@ -14318,7 +14318,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H481" t="n">
         <v>1344877</v>
@@ -14376,7 +14376,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502921104431</v>
+        <v>2.49502944946289</v>
       </c>
       <c r="H483" t="n">
         <v>1113397</v>
@@ -14434,7 +14434,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736464500427</v>
+        <v>2.86736440658569</v>
       </c>
       <c r="H485" t="n">
         <v>2335973</v>
@@ -14637,7 +14637,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H492" t="n">
         <v>360031</v>
@@ -14840,7 +14840,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.84817218780518</v>
+        <v>2.8481719493866</v>
       </c>
       <c r="H499" t="n">
         <v>177776</v>
@@ -14956,7 +14956,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H503" t="n">
         <v>781804</v>
@@ -15014,7 +15014,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H505" t="n">
         <v>362332</v>
@@ -15043,7 +15043,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H506" t="n">
         <v>249155</v>
@@ -15072,7 +15072,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H507" t="n">
         <v>199788</v>
@@ -15101,7 +15101,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230889320374</v>
+        <v>2.70230865478516</v>
       </c>
       <c r="H508" t="n">
         <v>228947</v>
@@ -15130,7 +15130,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H509" t="n">
         <v>305291</v>
@@ -15275,7 +15275,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928367614746</v>
+        <v>2.86928391456604</v>
       </c>
       <c r="H514" t="n">
         <v>468533</v>
@@ -15420,7 +15420,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H519" t="n">
         <v>477584</v>
@@ -15478,7 +15478,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H521" t="n">
         <v>402806</v>
@@ -15565,7 +15565,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877477645874</v>
+        <v>2.73877453804016</v>
       </c>
       <c r="H524" t="n">
         <v>549359</v>
@@ -15594,7 +15594,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563829421997</v>
+        <v>2.57563805580139</v>
       </c>
       <c r="H525" t="n">
         <v>7158793</v>
@@ -15652,7 +15652,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614719390869</v>
+        <v>2.70614743232727</v>
       </c>
       <c r="H527" t="n">
         <v>1136471</v>
@@ -15739,7 +15739,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H530" t="n">
         <v>821537</v>
@@ -15797,7 +15797,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H532" t="n">
         <v>874097</v>
@@ -15942,7 +15942,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H537" t="n">
         <v>1383977</v>
@@ -16377,7 +16377,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685550689697</v>
+        <v>2.73685526847839</v>
       </c>
       <c r="H552" t="n">
         <v>1598171</v>
@@ -16406,7 +16406,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H553" t="n">
         <v>899641</v>
@@ -16435,7 +16435,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H554" t="n">
         <v>740489</v>
@@ -16464,7 +16464,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503546714783</v>
+        <v>2.68503570556641</v>
       </c>
       <c r="H555" t="n">
         <v>586866</v>
@@ -16522,7 +16522,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H557" t="n">
         <v>744218</v>
@@ -16638,7 +16638,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281803131104</v>
+        <v>2.83281779289246</v>
       </c>
       <c r="H561" t="n">
         <v>568824</v>
@@ -16667,7 +16667,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019092559814</v>
+        <v>2.80019068717957</v>
       </c>
       <c r="H562" t="n">
         <v>509608</v>
@@ -16783,7 +16783,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H566" t="n">
         <v>264829</v>
@@ -16812,7 +16812,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75029015541077</v>
+        <v>2.75028991699219</v>
       </c>
       <c r="H567" t="n">
         <v>219381</v>
@@ -16870,7 +16870,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H569" t="n">
         <v>328641</v>
@@ -16928,7 +16928,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978101730347</v>
+        <v>2.61978077888489</v>
       </c>
       <c r="H571" t="n">
         <v>581272</v>
@@ -17247,7 +17247,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H582" t="n">
         <v>328175</v>
@@ -17305,7 +17305,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H584" t="n">
         <v>285733</v>
@@ -17334,7 +17334,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H585" t="n">
         <v>250096</v>
@@ -17421,7 +17421,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H588" t="n">
         <v>505464</v>
@@ -17450,7 +17450,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301672935486</v>
+        <v>2.73301696777344</v>
       </c>
       <c r="H589" t="n">
         <v>256840</v>
@@ -17508,7 +17508,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H591" t="n">
         <v>1596803</v>
@@ -17595,7 +17595,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735862731934</v>
+        <v>2.67735838890076</v>
       </c>
       <c r="H594" t="n">
         <v>422850</v>
@@ -17624,7 +17624,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190524101257</v>
+        <v>2.71190500259399</v>
       </c>
       <c r="H595" t="n">
         <v>576828</v>
@@ -17682,7 +17682,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H597" t="n">
         <v>284034</v>
@@ -17711,7 +17711,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.7042281627655</v>
+        <v>2.70422792434692</v>
       </c>
       <c r="H598" t="n">
         <v>201687</v>
@@ -17827,7 +17827,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H602" t="n">
         <v>368932</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H603" t="n">
         <v>435948</v>
@@ -17972,7 +17972,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.3721969127655</v>
+        <v>2.37219715118408</v>
       </c>
       <c r="H607" t="n">
         <v>1221882</v>
@@ -80009,6 +80009,35 @@
         <v>406247</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.268500000238419</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>231440</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599804878235</v>
+        <v>3.59599781036377</v>
       </c>
       <c r="H3" t="n">
         <v>611692</v>
@@ -514,7 +514,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H5" t="n">
         <v>807816</v>
@@ -572,7 +572,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930417060852</v>
+        <v>3.37930393218994</v>
       </c>
       <c r="H7" t="n">
         <v>489296</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655418395996</v>
+        <v>3.44655394554138</v>
       </c>
       <c r="H8" t="n">
         <v>335339</v>
@@ -630,7 +630,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.49325513839722</v>
+        <v>3.4932553768158</v>
       </c>
       <c r="H9" t="n">
         <v>197035</v>
@@ -717,7 +717,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G12" t="n">
-        <v>3.32886648178101</v>
+        <v>3.32886672019958</v>
       </c>
       <c r="H12" t="n">
         <v>597600</v>
@@ -746,7 +746,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.42787384986877</v>
+        <v>3.42787337303162</v>
       </c>
       <c r="H13" t="n">
         <v>410306</v>
@@ -804,7 +804,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3886444568634</v>
+        <v>3.38864421844482</v>
       </c>
       <c r="H15" t="n">
         <v>742869</v>
@@ -862,7 +862,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4316098690033</v>
+        <v>3.43160939216614</v>
       </c>
       <c r="H17" t="n">
         <v>415584</v>
@@ -920,7 +920,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391485214233</v>
+        <v>3.48391509056091</v>
       </c>
       <c r="H19" t="n">
         <v>400278</v>
@@ -949,7 +949,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062383651733</v>
+        <v>3.36062359809875</v>
       </c>
       <c r="H20" t="n">
         <v>463309</v>
@@ -1007,7 +1007,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G22" t="n">
-        <v>3.31579041481018</v>
+        <v>3.31579065322876</v>
       </c>
       <c r="H22" t="n">
         <v>1122003</v>
@@ -1065,7 +1065,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G24" t="n">
-        <v>3.22425580024719</v>
+        <v>3.22425556182861</v>
       </c>
       <c r="H24" t="n">
         <v>860294</v>
@@ -1181,7 +1181,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>2.64329195022583</v>
+        <v>2.64329218864441</v>
       </c>
       <c r="H28" t="n">
         <v>888507</v>
@@ -1210,7 +1210,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405548095703</v>
+        <v>2.77405571937561</v>
       </c>
       <c r="H29" t="n">
         <v>784919</v>
@@ -1239,7 +1239,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636873245239</v>
+        <v>2.65636825561523</v>
       </c>
       <c r="H30" t="n">
         <v>718398</v>
@@ -1297,7 +1297,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72922229766846</v>
+        <v>2.72922253608704</v>
       </c>
       <c r="H32" t="n">
         <v>485309</v>
@@ -1355,7 +1355,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45835518836975</v>
+        <v>2.45835494995117</v>
       </c>
       <c r="H34" t="n">
         <v>1399376</v>
@@ -1413,7 +1413,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5031886100769</v>
+        <v>2.50318837165833</v>
       </c>
       <c r="H36" t="n">
         <v>421169</v>
@@ -1442,7 +1442,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604217529297</v>
+        <v>2.57604193687439</v>
       </c>
       <c r="H37" t="n">
         <v>886852</v>
@@ -1471,7 +1471,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52747297286987</v>
+        <v>2.52747273445129</v>
       </c>
       <c r="H38" t="n">
         <v>913911</v>
@@ -1500,7 +1500,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395897865295</v>
+        <v>2.46395945549011</v>
       </c>
       <c r="H39" t="n">
         <v>414034</v>
@@ -1529,7 +1529,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120923042297</v>
+        <v>2.53120899200439</v>
       </c>
       <c r="H40" t="n">
         <v>622697</v>
@@ -1703,7 +1703,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.719881772995</v>
+        <v>2.71988224983215</v>
       </c>
       <c r="H46" t="n">
         <v>1083110</v>
@@ -1732,7 +1732,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G47" t="n">
-        <v>2.67318081855774</v>
+        <v>2.67318058013916</v>
       </c>
       <c r="H47" t="n">
         <v>714309</v>
@@ -1761,7 +1761,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61527132987976</v>
+        <v>2.61527109146118</v>
       </c>
       <c r="H48" t="n">
         <v>1729959</v>
@@ -1877,7 +1877,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8058123588562</v>
+        <v>2.80581259727478</v>
       </c>
       <c r="H52" t="n">
         <v>881692</v>
@@ -1964,7 +1964,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065285682678</v>
+        <v>2.68065309524536</v>
       </c>
       <c r="H55" t="n">
         <v>571416</v>
@@ -1993,7 +1993,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350713729858</v>
+        <v>2.75350689888</v>
       </c>
       <c r="H56" t="n">
         <v>617931</v>
@@ -2022,7 +2022,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603486061096</v>
+        <v>2.74603509902954</v>
       </c>
       <c r="H57" t="n">
         <v>468215</v>
@@ -2080,7 +2080,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.719881772995</v>
+        <v>2.71988224983215</v>
       </c>
       <c r="H59" t="n">
         <v>486311</v>
@@ -2109,7 +2109,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G60" t="n">
-        <v>2.63768792152405</v>
+        <v>2.63768768310547</v>
       </c>
       <c r="H60" t="n">
         <v>807171</v>
@@ -2283,7 +2283,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G66" t="n">
-        <v>2.5031886100769</v>
+        <v>2.50318837165833</v>
       </c>
       <c r="H66" t="n">
         <v>580199</v>
@@ -2370,7 +2370,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791018486023</v>
+        <v>2.57791042327881</v>
       </c>
       <c r="H69" t="n">
         <v>847648</v>
@@ -2399,7 +2399,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G70" t="n">
-        <v>2.56296586990356</v>
+        <v>2.56296563148499</v>
       </c>
       <c r="H70" t="n">
         <v>616769</v>
@@ -2486,7 +2486,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911895751953</v>
+        <v>2.58911848068237</v>
       </c>
       <c r="H73" t="n">
         <v>526922</v>
@@ -2515,7 +2515,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>2.60219502449036</v>
+        <v>2.60219478607178</v>
       </c>
       <c r="H74" t="n">
         <v>119380</v>
@@ -2544,7 +2544,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59285449981689</v>
+        <v>2.59285497665405</v>
       </c>
       <c r="H75" t="n">
         <v>375927</v>
@@ -2602,7 +2602,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395142555237</v>
+        <v>2.63395166397095</v>
       </c>
       <c r="H77" t="n">
         <v>329924</v>
@@ -2660,7 +2660,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384053230286</v>
+        <v>2.66384077072144</v>
       </c>
       <c r="H79" t="n">
         <v>306336</v>
@@ -2689,7 +2689,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065285682678</v>
+        <v>2.68065309524536</v>
       </c>
       <c r="H80" t="n">
         <v>263802</v>
@@ -2718,7 +2718,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>2.61527132987976</v>
+        <v>2.61527109146118</v>
       </c>
       <c r="H81" t="n">
         <v>515442</v>
@@ -2776,7 +2776,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395142555237</v>
+        <v>2.63395166397095</v>
       </c>
       <c r="H83" t="n">
         <v>139836</v>
@@ -2805,7 +2805,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G84" t="n">
-        <v>2.62834787368774</v>
+        <v>2.62834763526917</v>
       </c>
       <c r="H84" t="n">
         <v>97873</v>
@@ -2863,7 +2863,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208365440369</v>
+        <v>2.63208389282227</v>
       </c>
       <c r="H86" t="n">
         <v>115454</v>
@@ -2921,7 +2921,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>2.62461161613464</v>
+        <v>2.62461137771606</v>
       </c>
       <c r="H88" t="n">
         <v>90442</v>
@@ -2950,7 +2950,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911895751953</v>
+        <v>2.58911848068237</v>
       </c>
       <c r="H89" t="n">
         <v>154887</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066017150879</v>
+        <v>2.51066040992737</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3008,7 +3008,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55175757408142</v>
+        <v>2.5517578125</v>
       </c>
       <c r="H91" t="n">
         <v>189126</v>
@@ -3066,7 +3066,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538246154785</v>
+        <v>2.58538222312927</v>
       </c>
       <c r="H93" t="n">
         <v>366421</v>
@@ -3095,7 +3095,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56483387947083</v>
+        <v>2.5648341178894</v>
       </c>
       <c r="H94" t="n">
         <v>359206</v>
@@ -3124,7 +3124,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098649024963</v>
+        <v>2.59098672866821</v>
       </c>
       <c r="H95" t="n">
         <v>301461</v>
@@ -3153,7 +3153,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>2.65450024604797</v>
+        <v>2.65450048446655</v>
       </c>
       <c r="H96" t="n">
         <v>228387</v>
@@ -3269,7 +3269,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.74487400054932</v>
+        <v>2.74487447738647</v>
       </c>
       <c r="H100" t="n">
         <v>408349</v>
@@ -3298,7 +3298,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.74487400054932</v>
+        <v>2.74487447738647</v>
       </c>
       <c r="H101" t="n">
         <v>240708</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G104" t="n">
-        <v>2.84971284866333</v>
+        <v>2.84971308708191</v>
       </c>
       <c r="H104" t="n">
         <v>323531</v>
@@ -3443,7 +3443,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G106" t="n">
-        <v>2.93358421325684</v>
+        <v>2.93358445167542</v>
       </c>
       <c r="H106" t="n">
         <v>403679</v>
@@ -3530,7 +3530,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>2.870680809021</v>
+        <v>2.87068104743958</v>
       </c>
       <c r="H109" t="n">
         <v>377852</v>
@@ -3646,7 +3646,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G113" t="n">
-        <v>2.97170734405518</v>
+        <v>2.97170758247375</v>
       </c>
       <c r="H113" t="n">
         <v>368199</v>
@@ -3849,7 +3849,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85352563858032</v>
+        <v>2.85352540016174</v>
       </c>
       <c r="H120" t="n">
         <v>374301</v>
@@ -3878,7 +3878,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G121" t="n">
-        <v>2.8954610824585</v>
+        <v>2.89546084403992</v>
       </c>
       <c r="H121" t="n">
         <v>241175</v>
@@ -3907,7 +3907,7 @@
         <v>3</v>
       </c>
       <c r="G122" t="n">
-        <v>2.85924386978149</v>
+        <v>2.85924363136292</v>
       </c>
       <c r="H122" t="n">
         <v>166984</v>
@@ -3994,7 +3994,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760120391846</v>
+        <v>2.56760096549988</v>
       </c>
       <c r="H125" t="n">
         <v>525319</v>
@@ -4081,7 +4081,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>2.65719079971313</v>
+        <v>2.65719056129456</v>
       </c>
       <c r="H128" t="n">
         <v>191013</v>
@@ -4110,7 +4110,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72199988365173</v>
+        <v>2.72200012207031</v>
       </c>
       <c r="H129" t="n">
         <v>335865</v>
@@ -4226,7 +4226,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.47801113128662</v>
+        <v>2.4780113697052</v>
       </c>
       <c r="H133" t="n">
         <v>352159</v>
@@ -4255,7 +4255,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563623428345</v>
+        <v>2.48563599586487</v>
       </c>
       <c r="H134" t="n">
         <v>360643</v>
@@ -4284,7 +4284,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>2.55425763130188</v>
+        <v>2.55425786972046</v>
       </c>
       <c r="H135" t="n">
         <v>415438</v>
@@ -4458,7 +4458,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53328990936279</v>
+        <v>2.53329014778137</v>
       </c>
       <c r="H141" t="n">
         <v>619648</v>
@@ -4516,7 +4516,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G143" t="n">
-        <v>2.60381817817688</v>
+        <v>2.60381841659546</v>
       </c>
       <c r="H143" t="n">
         <v>581370</v>
@@ -4545,7 +4545,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.55425763130188</v>
+        <v>2.55425786972046</v>
       </c>
       <c r="H144" t="n">
         <v>360993</v>
@@ -4574,7 +4574,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>2.6400351524353</v>
+        <v>2.64003491401672</v>
       </c>
       <c r="H145" t="n">
         <v>342261</v>
@@ -4632,7 +4632,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G147" t="n">
-        <v>2.65719079971313</v>
+        <v>2.65719056129456</v>
       </c>
       <c r="H147" t="n">
         <v>531605</v>
@@ -4690,7 +4690,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.45513725280762</v>
+        <v>2.4551374912262</v>
       </c>
       <c r="H149" t="n">
         <v>1587031</v>
@@ -4719,7 +4719,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698483467102</v>
+        <v>2.37698459625244</v>
       </c>
       <c r="H150" t="n">
         <v>918463</v>
@@ -4835,7 +4835,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G154" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H154" t="n">
         <v>314927</v>
@@ -4893,7 +4893,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H156" t="n">
         <v>229323</v>
@@ -4951,7 +4951,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H158" t="n">
         <v>512824</v>
@@ -5096,7 +5096,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.17493176460266</v>
+        <v>2.1749312877655</v>
       </c>
       <c r="H163" t="n">
         <v>393671</v>
@@ -5125,7 +5125,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.17493176460266</v>
+        <v>2.1749312877655</v>
       </c>
       <c r="H164" t="n">
         <v>347934</v>
@@ -5154,7 +5154,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.19208693504333</v>
+        <v>2.19208669662476</v>
       </c>
       <c r="H165" t="n">
         <v>340810</v>
@@ -5212,7 +5212,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258567810059</v>
+        <v>2.22258543968201</v>
       </c>
       <c r="H167" t="n">
         <v>324769</v>
@@ -5241,7 +5241,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G168" t="n">
-        <v>2.24736595153809</v>
+        <v>2.24736571311951</v>
       </c>
       <c r="H168" t="n">
         <v>197676</v>
@@ -5270,7 +5270,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399333000183</v>
+        <v>2.19399309158325</v>
       </c>
       <c r="H169" t="n">
         <v>313201</v>
@@ -5299,7 +5299,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.176837682724</v>
+        <v>2.17683744430542</v>
       </c>
       <c r="H170" t="n">
         <v>631538</v>
@@ -5357,7 +5357,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.21305465698242</v>
+        <v>2.213054895401</v>
       </c>
       <c r="H172" t="n">
         <v>375938</v>
@@ -5473,7 +5473,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H176" t="n">
         <v>181659</v>
@@ -5502,7 +5502,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H177" t="n">
         <v>239497</v>
@@ -5531,7 +5531,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H178" t="n">
         <v>189602</v>
@@ -5647,7 +5647,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G182" t="n">
-        <v>2.12727761268616</v>
+        <v>2.12727737426758</v>
       </c>
       <c r="H182" t="n">
         <v>624125</v>
@@ -5734,7 +5734,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484294891357</v>
+        <v>2.05484318733215</v>
       </c>
       <c r="H185" t="n">
         <v>188205</v>
@@ -5792,7 +5792,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724784851074</v>
+        <v>2.08724808692932</v>
       </c>
       <c r="H187" t="n">
         <v>178971</v>
@@ -5821,7 +5821,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G188" t="n">
-        <v>2.08534169197083</v>
+        <v>2.0853419303894</v>
       </c>
       <c r="H188" t="n">
         <v>141186</v>
@@ -5850,7 +5850,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H189" t="n">
         <v>178603</v>
@@ -5879,7 +5879,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956464767456</v>
+        <v>1.99956452846527</v>
       </c>
       <c r="H190" t="n">
         <v>412606</v>
@@ -5908,7 +5908,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765837192535</v>
       </c>
       <c r="H191" t="n">
         <v>217002</v>
@@ -5937,7 +5937,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G192" t="n">
-        <v>1.98812747001648</v>
+        <v>1.98812758922577</v>
       </c>
       <c r="H192" t="n">
         <v>240368</v>
@@ -5995,7 +5995,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H194" t="n">
         <v>156156</v>
@@ -6053,7 +6053,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.99003374576569</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H196" t="n">
         <v>598584</v>
@@ -6082,7 +6082,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.99003374576569</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H197" t="n">
         <v>249799</v>
@@ -6111,7 +6111,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000433921814</v>
       </c>
       <c r="H198" t="n">
         <v>370597</v>
@@ -6169,7 +6169,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191049575806</v>
+        <v>1.95191061496735</v>
       </c>
       <c r="H200" t="n">
         <v>1432038</v>
@@ -6198,7 +6198,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G201" t="n">
-        <v>1.90425646305084</v>
+        <v>1.90425634384155</v>
       </c>
       <c r="H201" t="n">
         <v>949601</v>
@@ -6227,7 +6227,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G202" t="n">
-        <v>1.92903649806976</v>
+        <v>1.92903637886047</v>
       </c>
       <c r="H202" t="n">
         <v>442072</v>
@@ -6256,7 +6256,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G203" t="n">
-        <v>1.94619202613831</v>
+        <v>1.94619190692902</v>
       </c>
       <c r="H203" t="n">
         <v>236649</v>
@@ -6285,7 +6285,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96144139766693</v>
+        <v>1.96144151687622</v>
       </c>
       <c r="H204" t="n">
         <v>352781</v>
@@ -6314,7 +6314,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G205" t="n">
-        <v>1.92903649806976</v>
+        <v>1.92903637886047</v>
       </c>
       <c r="H205" t="n">
         <v>687316</v>
@@ -6343,7 +6343,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G206" t="n">
-        <v>1.90425646305084</v>
+        <v>1.90425634384155</v>
       </c>
       <c r="H206" t="n">
         <v>789726</v>
@@ -6372,7 +6372,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H207" t="n">
         <v>580889</v>
@@ -6401,7 +6401,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G208" t="n">
-        <v>1.90806877613068</v>
+        <v>1.90806889533997</v>
       </c>
       <c r="H208" t="n">
         <v>711737</v>
@@ -6430,7 +6430,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>1.91759967803955</v>
+        <v>1.91759955883026</v>
       </c>
       <c r="H209" t="n">
         <v>998577</v>
@@ -6488,7 +6488,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803936958313</v>
       </c>
       <c r="H211" t="n">
         <v>545183</v>
@@ -6517,7 +6517,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186644554138</v>
+        <v>1.89186632633209</v>
       </c>
       <c r="H212" t="n">
         <v>467560</v>
@@ -6546,7 +6546,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G213" t="n">
-        <v>1.86422693729401</v>
+        <v>1.8642270565033</v>
       </c>
       <c r="H213" t="n">
         <v>633127</v>
@@ -6575,7 +6575,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185156345367</v>
+        <v>1.87185168266296</v>
       </c>
       <c r="H214" t="n">
         <v>537617</v>
@@ -6604,7 +6604,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803936958313</v>
       </c>
       <c r="H215" t="n">
         <v>225249</v>
@@ -6662,7 +6662,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G217" t="n">
-        <v>1.85469615459442</v>
+        <v>1.85469627380371</v>
       </c>
       <c r="H217" t="n">
         <v>275371</v>
@@ -6720,7 +6720,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038533687592</v>
+        <v>1.82038521766663</v>
       </c>
       <c r="H219" t="n">
         <v>227009</v>
@@ -6778,7 +6778,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G221" t="n">
-        <v>1.80227673053741</v>
+        <v>1.8022768497467</v>
       </c>
       <c r="H221" t="n">
         <v>462867</v>
@@ -6981,7 +6981,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H228" t="n">
         <v>443928</v>
@@ -7010,7 +7010,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>1.78130888938904</v>
+        <v>1.78130877017975</v>
       </c>
       <c r="H229" t="n">
         <v>921990</v>
@@ -7126,7 +7126,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H233" t="n">
         <v>212483</v>
@@ -7184,7 +7184,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G235" t="n">
-        <v>1.75081038475037</v>
+        <v>1.75081026554108</v>
       </c>
       <c r="H235" t="n">
         <v>480374</v>
@@ -7213,7 +7213,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G236" t="n">
-        <v>1.77559041976929</v>
+        <v>1.77559053897858</v>
       </c>
       <c r="H236" t="n">
         <v>499172</v>
@@ -7242,7 +7242,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509191513062</v>
+        <v>1.74509179592133</v>
       </c>
       <c r="H237" t="n">
         <v>547803</v>
@@ -7271,7 +7271,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G238" t="n">
-        <v>1.77082502841949</v>
+        <v>1.77082514762878</v>
       </c>
       <c r="H238" t="n">
         <v>468353</v>
@@ -7300,7 +7300,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.7727313041687</v>
+        <v>1.77273106575012</v>
       </c>
       <c r="H239" t="n">
         <v>570721</v>
@@ -7387,7 +7387,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660243034363</v>
+        <v>1.85660231113434</v>
       </c>
       <c r="H242" t="n">
         <v>464622</v>
@@ -7445,7 +7445,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.87757003307343</v>
+        <v>1.877570271492</v>
       </c>
       <c r="H244" t="n">
         <v>527721</v>
@@ -7532,7 +7532,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H247" t="n">
         <v>435355</v>
@@ -7561,7 +7561,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H248" t="n">
         <v>502927</v>
@@ -7590,7 +7590,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G249" t="n">
-        <v>1.95953500270844</v>
+        <v>1.95953512191772</v>
       </c>
       <c r="H249" t="n">
         <v>720423</v>
@@ -7619,7 +7619,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.95572280883789</v>
+        <v>1.9557226896286</v>
       </c>
       <c r="H250" t="n">
         <v>638755</v>
@@ -7648,7 +7648,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G251" t="n">
-        <v>1.96144139766693</v>
+        <v>1.96144151687622</v>
       </c>
       <c r="H251" t="n">
         <v>332742</v>
@@ -7677,7 +7677,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H252" t="n">
         <v>603474</v>
@@ -7706,7 +7706,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.95572280883789</v>
+        <v>1.9557226896286</v>
       </c>
       <c r="H253" t="n">
         <v>461640</v>
@@ -7764,7 +7764,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575257301331</v>
+        <v>1.99575233459473</v>
       </c>
       <c r="H255" t="n">
         <v>1478455</v>
@@ -7851,7 +7851,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252686500549</v>
+        <v>2.14252662658691</v>
       </c>
       <c r="H258" t="n">
         <v>1054327</v>
@@ -7880,7 +7880,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G259" t="n">
-        <v>2.08534169197083</v>
+        <v>2.0853419303894</v>
       </c>
       <c r="H259" t="n">
         <v>1171318</v>
@@ -7909,7 +7909,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674958229065</v>
+        <v>2.05674934387207</v>
       </c>
       <c r="H260" t="n">
         <v>1146682</v>
@@ -7938,7 +7938,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G261" t="n">
-        <v>2.08534169197083</v>
+        <v>2.0853419303894</v>
       </c>
       <c r="H261" t="n">
         <v>1109093</v>
@@ -8054,7 +8054,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="n">
-        <v>2.12727761268616</v>
+        <v>2.12727737426758</v>
       </c>
       <c r="H265" t="n">
         <v>1746792</v>
@@ -8083,7 +8083,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G266" t="n">
-        <v>2.13108992576599</v>
+        <v>2.13108968734741</v>
       </c>
       <c r="H266" t="n">
         <v>1244280</v>
@@ -8112,7 +8112,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.09677886962891</v>
+        <v>2.09677863121033</v>
       </c>
       <c r="H267" t="n">
         <v>1644351</v>
@@ -8141,7 +8141,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G268" t="n">
-        <v>2.00718903541565</v>
+        <v>2.00718927383423</v>
       </c>
       <c r="H268" t="n">
         <v>1731581</v>
@@ -8228,7 +8228,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334743499756</v>
+        <v>1.96334719657898</v>
       </c>
       <c r="H271" t="n">
         <v>1260265</v>
@@ -8257,7 +8257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.93475496768951</v>
+        <v>1.9347550868988</v>
       </c>
       <c r="H272" t="n">
         <v>1120465</v>
@@ -8286,7 +8286,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H273" t="n">
         <v>655413</v>
@@ -8315,7 +8315,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H274" t="n">
         <v>752887</v>
@@ -8344,7 +8344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H275" t="n">
         <v>590585</v>
@@ -8402,7 +8402,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765837192535</v>
       </c>
       <c r="H277" t="n">
         <v>1178960</v>
@@ -8431,7 +8431,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G278" t="n">
-        <v>1.94619202613831</v>
+        <v>1.94619190692902</v>
       </c>
       <c r="H278" t="n">
         <v>429988</v>
@@ -8460,7 +8460,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330326557159</v>
+        <v>1.90330338478088</v>
       </c>
       <c r="H279" t="n">
         <v>1004346</v>
@@ -8518,7 +8518,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>1.86899244785309</v>
+        <v>1.8689923286438</v>
       </c>
       <c r="H281" t="n">
         <v>1316326</v>
@@ -8547,7 +8547,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G282" t="n">
-        <v>1.86422693729401</v>
+        <v>1.8642270565033</v>
       </c>
       <c r="H282" t="n">
         <v>780479</v>
@@ -8634,7 +8634,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G285" t="n">
-        <v>1.81371355056763</v>
+        <v>1.81371366977692</v>
       </c>
       <c r="H285" t="n">
         <v>2245645</v>
@@ -8663,7 +8663,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H286" t="n">
         <v>1757407</v>
@@ -8692,7 +8692,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G287" t="n">
-        <v>1.90425646305084</v>
+        <v>1.90425634384155</v>
       </c>
       <c r="H287" t="n">
         <v>1598284</v>
@@ -8779,7 +8779,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H290" t="n">
         <v>483668</v>
@@ -8808,7 +8808,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G291" t="n">
-        <v>1.93666124343872</v>
+        <v>1.93666136264801</v>
       </c>
       <c r="H291" t="n">
         <v>660166</v>
@@ -8866,7 +8866,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G293" t="n">
-        <v>1.90235018730164</v>
+        <v>1.90235030651093</v>
       </c>
       <c r="H293" t="n">
         <v>452383</v>
@@ -8895,7 +8895,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.92141199111938</v>
+        <v>1.92141175270081</v>
       </c>
       <c r="H294" t="n">
         <v>315857</v>
@@ -8982,7 +8982,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H297" t="n">
         <v>662717</v>
@@ -9011,7 +9011,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000433921814</v>
       </c>
       <c r="H298" t="n">
         <v>1498299</v>
@@ -9040,7 +9040,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.95572280883789</v>
+        <v>1.9557226896286</v>
       </c>
       <c r="H299" t="n">
         <v>494953</v>
@@ -9069,7 +9069,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478461265564</v>
+        <v>1.97478437423706</v>
       </c>
       <c r="H300" t="n">
         <v>1084282</v>
@@ -9156,7 +9156,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471091747284</v>
+        <v>1.87471079826355</v>
       </c>
       <c r="H303" t="n">
         <v>726032</v>
@@ -9185,7 +9185,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661695480347</v>
+        <v>1.87661707401276</v>
       </c>
       <c r="H304" t="n">
         <v>488529</v>
@@ -9214,7 +9214,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G305" t="n">
-        <v>1.86899244785309</v>
+        <v>1.8689923286438</v>
       </c>
       <c r="H305" t="n">
         <v>614151</v>
@@ -9330,7 +9330,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.99003374576569</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H309" t="n">
         <v>821834</v>
@@ -9359,7 +9359,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G310" t="n">
-        <v>2.0148138999939</v>
+        <v>2.01481413841248</v>
       </c>
       <c r="H310" t="n">
         <v>1837811</v>
@@ -9388,7 +9388,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G311" t="n">
-        <v>2.08534169197083</v>
+        <v>2.0853419303894</v>
       </c>
       <c r="H311" t="n">
         <v>3113532</v>
@@ -9446,7 +9446,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G313" t="n">
-        <v>2.10249733924866</v>
+        <v>2.10249757766724</v>
       </c>
       <c r="H313" t="n">
         <v>1169471</v>
@@ -9475,7 +9475,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.04912495613098</v>
+        <v>2.0491247177124</v>
       </c>
       <c r="H314" t="n">
         <v>1011370</v>
@@ -9504,7 +9504,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H315" t="n">
         <v>682468</v>
@@ -9562,7 +9562,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730690002441</v>
+        <v>2.16730666160583</v>
       </c>
       <c r="H317" t="n">
         <v>2091344</v>
@@ -9707,7 +9707,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G322" t="n">
-        <v>2.24736595153809</v>
+        <v>2.24736571311951</v>
       </c>
       <c r="H322" t="n">
         <v>838718</v>
@@ -9765,7 +9765,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H324" t="n">
         <v>869705</v>
@@ -9852,7 +9852,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H327" t="n">
         <v>791379</v>
@@ -9997,7 +9997,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H332" t="n">
         <v>380492</v>
@@ -10026,7 +10026,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H333" t="n">
         <v>427893</v>
@@ -10055,7 +10055,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G334" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H334" t="n">
         <v>425667</v>
@@ -10084,7 +10084,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G335" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H335" t="n">
         <v>541475</v>
@@ -10113,7 +10113,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>2.39414024353027</v>
+        <v>2.39414000511169</v>
       </c>
       <c r="H336" t="n">
         <v>1849332</v>
@@ -10200,7 +10200,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270306587219</v>
+        <v>2.38270330429077</v>
       </c>
       <c r="H339" t="n">
         <v>350392</v>
@@ -10229,7 +10229,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.3655481338501</v>
+        <v>2.36554789543152</v>
       </c>
       <c r="H340" t="n">
         <v>423860</v>
@@ -10403,7 +10403,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563623428345</v>
+        <v>2.48563599586487</v>
       </c>
       <c r="H346" t="n">
         <v>1281154</v>
@@ -10577,7 +10577,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>2.57331943511963</v>
+        <v>2.57331967353821</v>
       </c>
       <c r="H352" t="n">
         <v>1478509</v>
@@ -10693,7 +10693,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058856010437</v>
+        <v>2.60058832168579</v>
       </c>
       <c r="H356" t="n">
         <v>605694</v>
@@ -10925,7 +10925,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806670188904</v>
+        <v>2.70806646347046</v>
       </c>
       <c r="H364" t="n">
         <v>849448</v>
@@ -10983,7 +10983,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715992927551</v>
+        <v>2.77715969085693</v>
       </c>
       <c r="H366" t="n">
         <v>1578655</v>
@@ -11128,7 +11128,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H371" t="n">
         <v>692586</v>
@@ -11157,7 +11157,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.72917866706848</v>
+        <v>2.7291784286499</v>
       </c>
       <c r="H372" t="n">
         <v>600785</v>
@@ -11331,7 +11331,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514119148254</v>
+        <v>2.82514095306396</v>
       </c>
       <c r="H378" t="n">
         <v>369015</v>
@@ -11447,7 +11447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H382" t="n">
         <v>194578</v>
@@ -11534,7 +11534,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H385" t="n">
         <v>512623</v>
@@ -11621,7 +11621,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.89807271957397</v>
+        <v>2.8980724811554</v>
       </c>
       <c r="H388" t="n">
         <v>1185420</v>
@@ -11766,7 +11766,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H393" t="n">
         <v>1082817</v>
@@ -11795,7 +11795,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H394" t="n">
         <v>382748</v>
@@ -11940,7 +11940,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363159179688</v>
+        <v>3.00363183021545</v>
       </c>
       <c r="H399" t="n">
         <v>217171</v>
@@ -11969,7 +11969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757537841797</v>
+        <v>3.14757561683655</v>
       </c>
       <c r="H400" t="n">
         <v>1320738</v>
@@ -12288,7 +12288,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343891143799</v>
+        <v>3.29343867301941</v>
       </c>
       <c r="H411" t="n">
         <v>758243</v>
@@ -12375,7 +12375,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H414" t="n">
         <v>480519</v>
@@ -12462,7 +12462,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818422317505</v>
+        <v>3.22818446159363</v>
       </c>
       <c r="H417" t="n">
         <v>285532</v>
@@ -12491,7 +12491,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H418" t="n">
         <v>195515</v>
@@ -12636,7 +12636,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596076965332</v>
+        <v>3.18596053123474</v>
       </c>
       <c r="H423" t="n">
         <v>127820</v>
@@ -12694,7 +12694,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040189743042</v>
+        <v>3.08040165901184</v>
       </c>
       <c r="H425" t="n">
         <v>401854</v>
@@ -12752,7 +12752,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H427" t="n">
         <v>748285</v>
@@ -12781,7 +12781,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707225799561</v>
+        <v>3.20707249641418</v>
       </c>
       <c r="H428" t="n">
         <v>535469</v>
@@ -12839,7 +12839,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020272254944</v>
+        <v>3.18020296096802</v>
       </c>
       <c r="H430" t="n">
         <v>159000</v>
@@ -13042,7 +13042,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H437" t="n">
         <v>851102</v>
@@ -13100,7 +13100,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H439" t="n">
         <v>269780</v>
@@ -13129,7 +13129,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H440" t="n">
         <v>183536</v>
@@ -13245,7 +13245,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H444" t="n">
         <v>548564</v>
@@ -13303,7 +13303,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647592544556</v>
+        <v>3.50647616386414</v>
       </c>
       <c r="H446" t="n">
         <v>1496771</v>
@@ -13361,7 +13361,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809101104736</v>
+        <v>3.46809077262878</v>
       </c>
       <c r="H448" t="n">
         <v>331930</v>
@@ -13622,7 +13622,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899778366089</v>
+        <v>3.39899802207947</v>
       </c>
       <c r="H457" t="n">
         <v>786922</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H458" t="n">
         <v>169837</v>
@@ -13680,7 +13680,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889855384827</v>
+        <v>3.44889831542969</v>
       </c>
       <c r="H459" t="n">
         <v>96243</v>
@@ -14028,7 +14028,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940745353699</v>
+        <v>3.57940769195557</v>
       </c>
       <c r="H471" t="n">
         <v>517225</v>
@@ -14086,7 +14086,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264364242554</v>
+        <v>3.69264340400696</v>
       </c>
       <c r="H473" t="n">
         <v>1575544</v>
@@ -14115,7 +14115,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122749328613</v>
+        <v>3.63122725486755</v>
       </c>
       <c r="H474" t="n">
         <v>392936</v>
@@ -14173,7 +14173,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223397254944</v>
+        <v>3.51223373413086</v>
       </c>
       <c r="H476" t="n">
         <v>1052005</v>
@@ -14289,7 +14289,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H480" t="n">
         <v>1897823</v>
@@ -14318,7 +14318,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H481" t="n">
         <v>1344877</v>
@@ -14376,7 +14376,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502944946289</v>
+        <v>2.49502921104431</v>
       </c>
       <c r="H483" t="n">
         <v>1113397</v>
@@ -14434,7 +14434,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736440658569</v>
+        <v>2.86736464500427</v>
       </c>
       <c r="H485" t="n">
         <v>2335973</v>
@@ -14637,7 +14637,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H492" t="n">
         <v>360031</v>
@@ -14840,7 +14840,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.8481719493866</v>
+        <v>2.84817218780518</v>
       </c>
       <c r="H499" t="n">
         <v>177776</v>
@@ -14956,7 +14956,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H503" t="n">
         <v>781804</v>
@@ -15014,7 +15014,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H505" t="n">
         <v>362332</v>
@@ -15043,7 +15043,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H506" t="n">
         <v>249155</v>
@@ -15072,7 +15072,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H507" t="n">
         <v>199788</v>
@@ -15101,7 +15101,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230865478516</v>
+        <v>2.70230889320374</v>
       </c>
       <c r="H508" t="n">
         <v>228947</v>
@@ -15130,7 +15130,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H509" t="n">
         <v>305291</v>
@@ -15275,7 +15275,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928391456604</v>
+        <v>2.86928367614746</v>
       </c>
       <c r="H514" t="n">
         <v>468533</v>
@@ -15420,7 +15420,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H519" t="n">
         <v>477584</v>
@@ -15478,7 +15478,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H521" t="n">
         <v>402806</v>
@@ -15565,7 +15565,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877453804016</v>
+        <v>2.73877477645874</v>
       </c>
       <c r="H524" t="n">
         <v>549359</v>
@@ -15594,7 +15594,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563805580139</v>
+        <v>2.57563829421997</v>
       </c>
       <c r="H525" t="n">
         <v>7158793</v>
@@ -15652,7 +15652,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614743232727</v>
+        <v>2.70614719390869</v>
       </c>
       <c r="H527" t="n">
         <v>1136471</v>
@@ -15739,7 +15739,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H530" t="n">
         <v>821537</v>
@@ -15797,7 +15797,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H532" t="n">
         <v>874097</v>
@@ -15942,7 +15942,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H537" t="n">
         <v>1383977</v>
@@ -16377,7 +16377,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685526847839</v>
+        <v>2.73685550689697</v>
       </c>
       <c r="H552" t="n">
         <v>1598171</v>
@@ -16406,7 +16406,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H553" t="n">
         <v>899641</v>
@@ -16435,7 +16435,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H554" t="n">
         <v>740489</v>
@@ -16464,7 +16464,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503570556641</v>
+        <v>2.68503546714783</v>
       </c>
       <c r="H555" t="n">
         <v>586866</v>
@@ -16522,7 +16522,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H557" t="n">
         <v>744218</v>
@@ -16638,7 +16638,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281779289246</v>
+        <v>2.83281803131104</v>
       </c>
       <c r="H561" t="n">
         <v>568824</v>
@@ -16667,7 +16667,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019068717957</v>
+        <v>2.80019092559814</v>
       </c>
       <c r="H562" t="n">
         <v>509608</v>
@@ -16783,7 +16783,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H566" t="n">
         <v>264829</v>
@@ -16812,7 +16812,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75028991699219</v>
+        <v>2.75029015541077</v>
       </c>
       <c r="H567" t="n">
         <v>219381</v>
@@ -16870,7 +16870,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H569" t="n">
         <v>328641</v>
@@ -16928,7 +16928,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978077888489</v>
+        <v>2.61978101730347</v>
       </c>
       <c r="H571" t="n">
         <v>581272</v>
@@ -17247,7 +17247,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H582" t="n">
         <v>328175</v>
@@ -17305,7 +17305,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H584" t="n">
         <v>285733</v>
@@ -17334,7 +17334,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H585" t="n">
         <v>250096</v>
@@ -17421,7 +17421,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H588" t="n">
         <v>505464</v>
@@ -17450,7 +17450,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301696777344</v>
+        <v>2.73301672935486</v>
       </c>
       <c r="H589" t="n">
         <v>256840</v>
@@ -17508,7 +17508,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H591" t="n">
         <v>1596803</v>
@@ -17595,7 +17595,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735838890076</v>
+        <v>2.67735862731934</v>
       </c>
       <c r="H594" t="n">
         <v>422850</v>
@@ -17624,7 +17624,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190500259399</v>
+        <v>2.71190524101257</v>
       </c>
       <c r="H595" t="n">
         <v>576828</v>
@@ -17682,7 +17682,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H597" t="n">
         <v>284034</v>
@@ -17711,7 +17711,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.70422792434692</v>
+        <v>2.7042281627655</v>
       </c>
       <c r="H598" t="n">
         <v>201687</v>
@@ -17827,7 +17827,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H602" t="n">
         <v>368932</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H603" t="n">
         <v>435948</v>
@@ -17972,7 +17972,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.37219715118408</v>
+        <v>2.3721969127655</v>
       </c>
       <c r="H607" t="n">
         <v>1221882</v>
@@ -80026,7 +80026,7 @@
         <v>0.268500000238419</v>
       </c>
       <c r="E2747" t="n">
-        <v>0.261999994516373</v>
+        <v>0.261000007390976</v>
       </c>
       <c r="F2747" t="n">
         <v>0.261000007390976</v>
@@ -80038,6 +80038,35 @@
         <v>231440</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>161341</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67819237709045</v>
+        <v>3.67819261550903</v>
       </c>
       <c r="H2" t="n">
         <v>809052</v>
@@ -456,7 +456,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599781036377</v>
+        <v>3.59599804878235</v>
       </c>
       <c r="H3" t="n">
         <v>611692</v>
@@ -514,7 +514,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H5" t="n">
         <v>807816</v>
@@ -572,7 +572,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930393218994</v>
+        <v>3.37930417060852</v>
       </c>
       <c r="H7" t="n">
         <v>489296</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655394554138</v>
+        <v>3.44655418395996</v>
       </c>
       <c r="H8" t="n">
         <v>335339</v>
@@ -630,7 +630,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4932553768158</v>
+        <v>3.49325513839722</v>
       </c>
       <c r="H9" t="n">
         <v>197035</v>
@@ -717,7 +717,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G12" t="n">
-        <v>3.32886672019958</v>
+        <v>3.32886648178101</v>
       </c>
       <c r="H12" t="n">
         <v>597600</v>
@@ -746,7 +746,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.42787337303162</v>
+        <v>3.42787384986877</v>
       </c>
       <c r="H13" t="n">
         <v>410306</v>
@@ -804,7 +804,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.38864421844482</v>
+        <v>3.3886444568634</v>
       </c>
       <c r="H15" t="n">
         <v>742869</v>
@@ -862,7 +862,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.43160939216614</v>
+        <v>3.43160963058472</v>
       </c>
       <c r="H17" t="n">
         <v>415584</v>
@@ -920,7 +920,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>3.48391509056091</v>
+        <v>3.48391485214233</v>
       </c>
       <c r="H19" t="n">
         <v>400278</v>
@@ -949,7 +949,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062359809875</v>
+        <v>3.36062383651733</v>
       </c>
       <c r="H20" t="n">
         <v>463309</v>
@@ -1007,7 +1007,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G22" t="n">
-        <v>3.31579065322876</v>
+        <v>3.31579041481018</v>
       </c>
       <c r="H22" t="n">
         <v>1122003</v>
@@ -1065,7 +1065,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G24" t="n">
-        <v>3.22425556182861</v>
+        <v>3.22425580024719</v>
       </c>
       <c r="H24" t="n">
         <v>860294</v>
@@ -1094,7 +1094,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2578809261322</v>
+        <v>3.25788068771362</v>
       </c>
       <c r="H25" t="n">
         <v>832589</v>
@@ -1210,7 +1210,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405571937561</v>
+        <v>2.77405548095703</v>
       </c>
       <c r="H29" t="n">
         <v>784919</v>
@@ -1239,7 +1239,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636825561523</v>
+        <v>2.65636849403381</v>
       </c>
       <c r="H30" t="n">
         <v>718398</v>
@@ -1355,7 +1355,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45835494995117</v>
+        <v>2.45835518836975</v>
       </c>
       <c r="H34" t="n">
         <v>1399376</v>
@@ -1384,7 +1384,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.4919798374176</v>
+        <v>2.49198007583618</v>
       </c>
       <c r="H35" t="n">
         <v>844299</v>
@@ -1442,7 +1442,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604193687439</v>
+        <v>2.57604217529297</v>
       </c>
       <c r="H37" t="n">
         <v>886852</v>
@@ -1471,7 +1471,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52747273445129</v>
+        <v>2.52747297286987</v>
       </c>
       <c r="H38" t="n">
         <v>913911</v>
@@ -1500,7 +1500,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395945549011</v>
+        <v>2.46395921707153</v>
       </c>
       <c r="H39" t="n">
         <v>414034</v>
@@ -1558,7 +1558,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G41" t="n">
-        <v>2.79460430145264</v>
+        <v>2.79460406303406</v>
       </c>
       <c r="H41" t="n">
         <v>2765448</v>
@@ -1674,7 +1674,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G45" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H45" t="n">
         <v>644573</v>
@@ -1703,7 +1703,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H46" t="n">
         <v>1083110</v>
@@ -1732,7 +1732,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G47" t="n">
-        <v>2.67318058013916</v>
+        <v>2.67318081855774</v>
       </c>
       <c r="H47" t="n">
         <v>714309</v>
@@ -1761,7 +1761,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G48" t="n">
-        <v>2.61527109146118</v>
+        <v>2.61527132987976</v>
       </c>
       <c r="H48" t="n">
         <v>1729959</v>
@@ -1819,7 +1819,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526401519775</v>
+        <v>2.78526377677917</v>
       </c>
       <c r="H50" t="n">
         <v>3240146</v>
@@ -1935,7 +1935,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G54" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H54" t="n">
         <v>631029</v>
@@ -1964,7 +1964,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065333366394</v>
       </c>
       <c r="H55" t="n">
         <v>571416</v>
@@ -2022,7 +2022,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603509902954</v>
+        <v>2.74603486061096</v>
       </c>
       <c r="H57" t="n">
         <v>468215</v>
@@ -2080,7 +2080,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H59" t="n">
         <v>486311</v>
@@ -2109,7 +2109,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G60" t="n">
-        <v>2.63768768310547</v>
+        <v>2.63768792152405</v>
       </c>
       <c r="H60" t="n">
         <v>807171</v>
@@ -2225,7 +2225,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G64" t="n">
-        <v>2.58164644241333</v>
+        <v>2.58164620399475</v>
       </c>
       <c r="H64" t="n">
         <v>791010</v>
@@ -2254,7 +2254,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>2.64889621734619</v>
+        <v>2.64889597892761</v>
       </c>
       <c r="H65" t="n">
         <v>389941</v>
@@ -2312,7 +2312,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G67" t="n">
-        <v>2.4994523525238</v>
+        <v>2.49945259094238</v>
       </c>
       <c r="H67" t="n">
         <v>487491</v>
@@ -2515,7 +2515,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>2.60219478607178</v>
+        <v>2.60219502449036</v>
       </c>
       <c r="H74" t="n">
         <v>119380</v>
@@ -2544,7 +2544,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59285497665405</v>
+        <v>2.59285473823547</v>
       </c>
       <c r="H75" t="n">
         <v>375927</v>
@@ -2689,7 +2689,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065333366394</v>
       </c>
       <c r="H80" t="n">
         <v>263802</v>
@@ -2718,7 +2718,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>2.61527109146118</v>
+        <v>2.61527132987976</v>
       </c>
       <c r="H81" t="n">
         <v>515442</v>
@@ -2747,7 +2747,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702820777893</v>
+        <v>2.64702844619751</v>
       </c>
       <c r="H82" t="n">
         <v>202750</v>
@@ -2834,7 +2834,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263223648071</v>
+        <v>2.65263247489929</v>
       </c>
       <c r="H85" t="n">
         <v>83792</v>
@@ -2921,7 +2921,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>2.62461137771606</v>
+        <v>2.62461161613464</v>
       </c>
       <c r="H88" t="n">
         <v>90442</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066040992737</v>
+        <v>2.51066017150879</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3008,7 +3008,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.5517578125</v>
+        <v>2.55175757408142</v>
       </c>
       <c r="H91" t="n">
         <v>189126</v>
@@ -3066,7 +3066,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538222312927</v>
+        <v>2.58538269996643</v>
       </c>
       <c r="H93" t="n">
         <v>366421</v>
@@ -3124,7 +3124,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098672866821</v>
+        <v>2.59098649024963</v>
       </c>
       <c r="H95" t="n">
         <v>301461</v>
@@ -3182,7 +3182,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702820777893</v>
+        <v>2.64702844619751</v>
       </c>
       <c r="H97" t="n">
         <v>251024</v>
@@ -3269,7 +3269,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.74487447738647</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H100" t="n">
         <v>408349</v>
@@ -3298,7 +3298,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.74487447738647</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H101" t="n">
         <v>240708</v>
@@ -3327,7 +3327,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G102" t="n">
-        <v>2.80777764320374</v>
+        <v>2.80777740478516</v>
       </c>
       <c r="H102" t="n">
         <v>317585</v>
@@ -3443,7 +3443,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G106" t="n">
-        <v>2.93358445167542</v>
+        <v>2.93358421325684</v>
       </c>
       <c r="H106" t="n">
         <v>403679</v>
@@ -3472,7 +3472,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92595958709717</v>
+        <v>2.92595934867859</v>
       </c>
       <c r="H107" t="n">
         <v>323008</v>
@@ -3530,7 +3530,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>2.87068104743958</v>
+        <v>2.870680809021</v>
       </c>
       <c r="H109" t="n">
         <v>377852</v>
@@ -3675,7 +3675,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91071009635925</v>
+        <v>2.91071033477783</v>
       </c>
       <c r="H114" t="n">
         <v>1063201</v>
@@ -3878,7 +3878,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G121" t="n">
-        <v>2.89546084403992</v>
+        <v>2.8954610824585</v>
       </c>
       <c r="H121" t="n">
         <v>241175</v>
@@ -3994,7 +3994,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760096549988</v>
+        <v>2.56760120391846</v>
       </c>
       <c r="H125" t="n">
         <v>525319</v>
@@ -4226,7 +4226,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.4780113697052</v>
+        <v>2.47801113128662</v>
       </c>
       <c r="H133" t="n">
         <v>352159</v>
@@ -4516,7 +4516,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G143" t="n">
-        <v>2.60381841659546</v>
+        <v>2.60381817817688</v>
       </c>
       <c r="H143" t="n">
         <v>581370</v>
@@ -4574,7 +4574,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64003491401672</v>
+        <v>2.6400351524353</v>
       </c>
       <c r="H145" t="n">
         <v>342261</v>
@@ -4835,7 +4835,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G154" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H154" t="n">
         <v>314927</v>
@@ -4893,7 +4893,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220456123352</v>
+        <v>2.35220432281494</v>
       </c>
       <c r="H156" t="n">
         <v>229323</v>
@@ -4951,7 +4951,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220456123352</v>
+        <v>2.35220432281494</v>
       </c>
       <c r="H158" t="n">
         <v>512824</v>
@@ -5096,7 +5096,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.1749312877655</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H163" t="n">
         <v>393671</v>
@@ -5125,7 +5125,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.1749312877655</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H164" t="n">
         <v>347934</v>
@@ -5270,7 +5270,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399309158325</v>
+        <v>2.19399333000183</v>
       </c>
       <c r="H169" t="n">
         <v>313201</v>
@@ -5357,7 +5357,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.213054895401</v>
+        <v>2.21305465698242</v>
       </c>
       <c r="H172" t="n">
         <v>375938</v>
@@ -5473,7 +5473,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H176" t="n">
         <v>181659</v>
@@ -5647,7 +5647,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G182" t="n">
-        <v>2.12727737426758</v>
+        <v>2.12727761268616</v>
       </c>
       <c r="H182" t="n">
         <v>624125</v>
@@ -5734,7 +5734,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484318733215</v>
+        <v>2.05484294891357</v>
       </c>
       <c r="H185" t="n">
         <v>188205</v>
@@ -5792,7 +5792,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724808692932</v>
+        <v>2.08724784851074</v>
       </c>
       <c r="H187" t="n">
         <v>178971</v>
@@ -5850,7 +5850,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.0624680519104</v>
+        <v>2.06246781349182</v>
       </c>
       <c r="H189" t="n">
         <v>178603</v>
@@ -5879,7 +5879,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956452846527</v>
+        <v>1.99956440925598</v>
       </c>
       <c r="H190" t="n">
         <v>412606</v>
@@ -5908,7 +5908,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765849113464</v>
       </c>
       <c r="H191" t="n">
         <v>217002</v>
@@ -5937,7 +5937,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G192" t="n">
-        <v>1.98812758922577</v>
+        <v>1.98812747001648</v>
       </c>
       <c r="H192" t="n">
         <v>240368</v>
@@ -5995,7 +5995,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193978309631</v>
+        <v>1.99193966388702</v>
       </c>
       <c r="H194" t="n">
         <v>156156</v>
@@ -6053,7 +6053,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H196" t="n">
         <v>598584</v>
@@ -6082,7 +6082,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H197" t="n">
         <v>249799</v>
@@ -6140,7 +6140,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G199" t="n">
-        <v>1.92713046073914</v>
+        <v>1.92713057994843</v>
       </c>
       <c r="H199" t="n">
         <v>354166</v>
@@ -6285,7 +6285,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96144151687622</v>
+        <v>1.96144139766693</v>
       </c>
       <c r="H204" t="n">
         <v>352781</v>
@@ -6372,7 +6372,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616250038147</v>
+        <v>1.90616261959076</v>
       </c>
       <c r="H207" t="n">
         <v>580889</v>
@@ -6488,7 +6488,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803936958313</v>
+        <v>1.86803948879242</v>
       </c>
       <c r="H211" t="n">
         <v>545183</v>
@@ -6575,7 +6575,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185168266296</v>
+        <v>1.87185156345367</v>
       </c>
       <c r="H214" t="n">
         <v>537617</v>
@@ -6604,7 +6604,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803936958313</v>
+        <v>1.86803948879242</v>
       </c>
       <c r="H215" t="n">
         <v>225249</v>
@@ -6662,7 +6662,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G217" t="n">
-        <v>1.85469627380371</v>
+        <v>1.85469615459442</v>
       </c>
       <c r="H217" t="n">
         <v>275371</v>
@@ -6720,7 +6720,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038521766663</v>
+        <v>1.82038533687592</v>
       </c>
       <c r="H219" t="n">
         <v>227009</v>
@@ -6778,7 +6778,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G221" t="n">
-        <v>1.8022768497467</v>
+        <v>1.80227673053741</v>
       </c>
       <c r="H221" t="n">
         <v>462867</v>
@@ -6952,7 +6952,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>1.81561982631683</v>
+        <v>1.81561994552612</v>
       </c>
       <c r="H227" t="n">
         <v>1092489</v>
@@ -6981,7 +6981,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179286956787</v>
+        <v>1.79179275035858</v>
       </c>
       <c r="H228" t="n">
         <v>443928</v>
@@ -7126,7 +7126,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179286956787</v>
+        <v>1.79179275035858</v>
       </c>
       <c r="H233" t="n">
         <v>212483</v>
@@ -7184,7 +7184,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G235" t="n">
-        <v>1.75081026554108</v>
+        <v>1.75081038475037</v>
       </c>
       <c r="H235" t="n">
         <v>480374</v>
@@ -7213,7 +7213,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G236" t="n">
-        <v>1.77559053897858</v>
+        <v>1.77559041976929</v>
       </c>
       <c r="H236" t="n">
         <v>499172</v>
@@ -7242,7 +7242,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509179592133</v>
+        <v>1.74509191513062</v>
       </c>
       <c r="H237" t="n">
         <v>547803</v>
@@ -7271,7 +7271,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G238" t="n">
-        <v>1.77082514762878</v>
+        <v>1.77082502841949</v>
       </c>
       <c r="H238" t="n">
         <v>468353</v>
@@ -7300,7 +7300,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273106575012</v>
+        <v>1.77273118495941</v>
       </c>
       <c r="H239" t="n">
         <v>570721</v>
@@ -7358,7 +7358,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372843265533</v>
+        <v>1.83372831344604</v>
       </c>
       <c r="H241" t="n">
         <v>613856</v>
@@ -7445,7 +7445,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.877570271492</v>
+        <v>1.87757015228271</v>
       </c>
       <c r="H244" t="n">
         <v>527721</v>
@@ -7532,7 +7532,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616250038147</v>
+        <v>1.90616261959076</v>
       </c>
       <c r="H247" t="n">
         <v>435355</v>
@@ -7648,7 +7648,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G251" t="n">
-        <v>1.96144151687622</v>
+        <v>1.96144139766693</v>
       </c>
       <c r="H251" t="n">
         <v>332742</v>
@@ -7909,7 +7909,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674934387207</v>
+        <v>2.05674958229065</v>
       </c>
       <c r="H260" t="n">
         <v>1146682</v>
@@ -7967,7 +7967,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437373161316</v>
+        <v>2.06437397003174</v>
       </c>
       <c r="H262" t="n">
         <v>432968</v>
@@ -7996,7 +7996,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G263" t="n">
-        <v>2.00909543037415</v>
+        <v>2.00909519195557</v>
       </c>
       <c r="H263" t="n">
         <v>959315</v>
@@ -8054,7 +8054,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="n">
-        <v>2.12727737426758</v>
+        <v>2.12727761268616</v>
       </c>
       <c r="H265" t="n">
         <v>1746792</v>
@@ -8083,7 +8083,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G266" t="n">
-        <v>2.13108968734741</v>
+        <v>2.13108992576599</v>
       </c>
       <c r="H266" t="n">
         <v>1244280</v>
@@ -8228,7 +8228,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334719657898</v>
+        <v>1.96334731578827</v>
       </c>
       <c r="H271" t="n">
         <v>1260265</v>
@@ -8257,7 +8257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.9347550868988</v>
+        <v>1.93475496768951</v>
       </c>
       <c r="H272" t="n">
         <v>1120465</v>
@@ -8315,7 +8315,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193978309631</v>
+        <v>1.99193966388702</v>
       </c>
       <c r="H274" t="n">
         <v>752887</v>
@@ -8402,7 +8402,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765849113464</v>
       </c>
       <c r="H277" t="n">
         <v>1178960</v>
@@ -8460,7 +8460,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330338478088</v>
+        <v>1.90330326557159</v>
       </c>
       <c r="H279" t="n">
         <v>1004346</v>
@@ -8576,7 +8576,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.81561982631683</v>
+        <v>1.81561994552612</v>
       </c>
       <c r="H283" t="n">
         <v>878438</v>
@@ -8837,7 +8837,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G292" t="n">
-        <v>1.92713046073914</v>
+        <v>1.92713057994843</v>
       </c>
       <c r="H292" t="n">
         <v>475359</v>
@@ -8895,7 +8895,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.92141175270081</v>
+        <v>1.9214118719101</v>
       </c>
       <c r="H294" t="n">
         <v>315857</v>
@@ -8924,7 +8924,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G295" t="n">
-        <v>1.91950559616089</v>
+        <v>1.9195054769516</v>
       </c>
       <c r="H295" t="n">
         <v>317758</v>
@@ -9127,7 +9127,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G302" t="n">
-        <v>1.87280476093292</v>
+        <v>1.87280488014221</v>
       </c>
       <c r="H302" t="n">
         <v>4452878</v>
@@ -9156,7 +9156,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471079826355</v>
+        <v>1.87471091747284</v>
       </c>
       <c r="H303" t="n">
         <v>726032</v>
@@ -9243,7 +9243,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G306" t="n">
-        <v>1.86994552612305</v>
+        <v>1.86994540691376</v>
       </c>
       <c r="H306" t="n">
         <v>388137</v>
@@ -9330,7 +9330,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003374576569</v>
       </c>
       <c r="H309" t="n">
         <v>821834</v>
@@ -9475,7 +9475,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.0491247177124</v>
+        <v>2.04912495613098</v>
       </c>
       <c r="H314" t="n">
         <v>1011370</v>
@@ -9504,7 +9504,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.0624680519104</v>
+        <v>2.06246781349182</v>
       </c>
       <c r="H315" t="n">
         <v>682468</v>
@@ -9765,7 +9765,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H324" t="n">
         <v>869705</v>
@@ -9852,7 +9852,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H327" t="n">
         <v>791379</v>
@@ -9939,7 +9939,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645680427551</v>
+        <v>2.30645656585693</v>
       </c>
       <c r="H330" t="n">
         <v>409387</v>
@@ -9997,7 +9997,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H332" t="n">
         <v>380492</v>
@@ -10026,7 +10026,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833343505859</v>
+        <v>2.26833367347717</v>
       </c>
       <c r="H333" t="n">
         <v>427893</v>
@@ -10055,7 +10055,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G334" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H334" t="n">
         <v>425667</v>
@@ -10084,7 +10084,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G335" t="n">
-        <v>2.31598734855652</v>
+        <v>2.3159875869751</v>
       </c>
       <c r="H335" t="n">
         <v>541475</v>
@@ -10258,7 +10258,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938949584961</v>
+        <v>2.40938973426819</v>
       </c>
       <c r="H341" t="n">
         <v>1086286</v>
@@ -10577,7 +10577,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>2.57331967353821</v>
+        <v>2.57331943511963</v>
       </c>
       <c r="H352" t="n">
         <v>1478509</v>
@@ -10693,7 +10693,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058832168579</v>
+        <v>2.60058856010437</v>
       </c>
       <c r="H356" t="n">
         <v>605694</v>
@@ -10925,7 +10925,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806646347046</v>
+        <v>2.70806670188904</v>
       </c>
       <c r="H364" t="n">
         <v>849448</v>
@@ -10983,7 +10983,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715969085693</v>
+        <v>2.77715992927551</v>
       </c>
       <c r="H366" t="n">
         <v>1578655</v>
@@ -11128,7 +11128,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H371" t="n">
         <v>692586</v>
@@ -11157,7 +11157,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.7291784286499</v>
+        <v>2.72917866706848</v>
       </c>
       <c r="H372" t="n">
         <v>600785</v>
@@ -11331,7 +11331,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514095306396</v>
+        <v>2.82514119148254</v>
       </c>
       <c r="H378" t="n">
         <v>369015</v>
@@ -11447,7 +11447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H382" t="n">
         <v>194578</v>
@@ -11534,7 +11534,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H385" t="n">
         <v>512623</v>
@@ -11621,7 +11621,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.8980724811554</v>
+        <v>2.89807271957397</v>
       </c>
       <c r="H388" t="n">
         <v>1185420</v>
@@ -11766,7 +11766,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H393" t="n">
         <v>1082817</v>
@@ -11795,7 +11795,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H394" t="n">
         <v>382748</v>
@@ -11940,7 +11940,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363183021545</v>
+        <v>3.00363159179688</v>
       </c>
       <c r="H399" t="n">
         <v>217171</v>
@@ -11969,7 +11969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757561683655</v>
+        <v>3.14757537841797</v>
       </c>
       <c r="H400" t="n">
         <v>1320738</v>
@@ -12288,7 +12288,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343867301941</v>
+        <v>3.29343891143799</v>
       </c>
       <c r="H411" t="n">
         <v>758243</v>
@@ -12375,7 +12375,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H414" t="n">
         <v>480519</v>
@@ -12462,7 +12462,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818446159363</v>
+        <v>3.22818422317505</v>
       </c>
       <c r="H417" t="n">
         <v>285532</v>
@@ -12491,7 +12491,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H418" t="n">
         <v>195515</v>
@@ -12636,7 +12636,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596053123474</v>
+        <v>3.18596076965332</v>
       </c>
       <c r="H423" t="n">
         <v>127820</v>
@@ -12694,7 +12694,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040165901184</v>
+        <v>3.08040189743042</v>
       </c>
       <c r="H425" t="n">
         <v>401854</v>
@@ -12752,7 +12752,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H427" t="n">
         <v>748285</v>
@@ -12781,7 +12781,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707249641418</v>
+        <v>3.20707225799561</v>
       </c>
       <c r="H428" t="n">
         <v>535469</v>
@@ -12839,7 +12839,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020296096802</v>
+        <v>3.18020272254944</v>
       </c>
       <c r="H430" t="n">
         <v>159000</v>
@@ -13042,7 +13042,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H437" t="n">
         <v>851102</v>
@@ -13100,7 +13100,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H439" t="n">
         <v>269780</v>
@@ -13129,7 +13129,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H440" t="n">
         <v>183536</v>
@@ -13245,7 +13245,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H444" t="n">
         <v>548564</v>
@@ -13303,7 +13303,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647616386414</v>
+        <v>3.50647592544556</v>
       </c>
       <c r="H446" t="n">
         <v>1496771</v>
@@ -13361,7 +13361,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809077262878</v>
+        <v>3.46809101104736</v>
       </c>
       <c r="H448" t="n">
         <v>331930</v>
@@ -13622,7 +13622,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899802207947</v>
+        <v>3.39899778366089</v>
       </c>
       <c r="H457" t="n">
         <v>786922</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H458" t="n">
         <v>169837</v>
@@ -13680,7 +13680,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889831542969</v>
+        <v>3.44889855384827</v>
       </c>
       <c r="H459" t="n">
         <v>96243</v>
@@ -14028,7 +14028,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940769195557</v>
+        <v>3.57940745353699</v>
       </c>
       <c r="H471" t="n">
         <v>517225</v>
@@ -14086,7 +14086,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264340400696</v>
+        <v>3.69264364242554</v>
       </c>
       <c r="H473" t="n">
         <v>1575544</v>
@@ -14115,7 +14115,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122725486755</v>
+        <v>3.63122749328613</v>
       </c>
       <c r="H474" t="n">
         <v>392936</v>
@@ -14173,7 +14173,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223373413086</v>
+        <v>3.51223397254944</v>
       </c>
       <c r="H476" t="n">
         <v>1052005</v>
@@ -14289,7 +14289,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H480" t="n">
         <v>1897823</v>
@@ -14318,7 +14318,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H481" t="n">
         <v>1344877</v>
@@ -14376,7 +14376,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502921104431</v>
+        <v>2.49502944946289</v>
       </c>
       <c r="H483" t="n">
         <v>1113397</v>
@@ -14434,7 +14434,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736464500427</v>
+        <v>2.86736440658569</v>
       </c>
       <c r="H485" t="n">
         <v>2335973</v>
@@ -14637,7 +14637,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H492" t="n">
         <v>360031</v>
@@ -14840,7 +14840,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.84817218780518</v>
+        <v>2.8481719493866</v>
       </c>
       <c r="H499" t="n">
         <v>177776</v>
@@ -14956,7 +14956,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H503" t="n">
         <v>781804</v>
@@ -15014,7 +15014,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H505" t="n">
         <v>362332</v>
@@ -15043,7 +15043,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H506" t="n">
         <v>249155</v>
@@ -15072,7 +15072,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H507" t="n">
         <v>199788</v>
@@ -15101,7 +15101,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230889320374</v>
+        <v>2.70230865478516</v>
       </c>
       <c r="H508" t="n">
         <v>228947</v>
@@ -15130,7 +15130,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H509" t="n">
         <v>305291</v>
@@ -15275,7 +15275,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928367614746</v>
+        <v>2.86928391456604</v>
       </c>
       <c r="H514" t="n">
         <v>468533</v>
@@ -15420,7 +15420,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H519" t="n">
         <v>477584</v>
@@ -15478,7 +15478,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H521" t="n">
         <v>402806</v>
@@ -15565,7 +15565,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877477645874</v>
+        <v>2.73877453804016</v>
       </c>
       <c r="H524" t="n">
         <v>549359</v>
@@ -15594,7 +15594,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563829421997</v>
+        <v>2.57563805580139</v>
       </c>
       <c r="H525" t="n">
         <v>7158793</v>
@@ -15652,7 +15652,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614719390869</v>
+        <v>2.70614743232727</v>
       </c>
       <c r="H527" t="n">
         <v>1136471</v>
@@ -15739,7 +15739,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H530" t="n">
         <v>821537</v>
@@ -15797,7 +15797,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H532" t="n">
         <v>874097</v>
@@ -15942,7 +15942,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H537" t="n">
         <v>1383977</v>
@@ -16377,7 +16377,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685550689697</v>
+        <v>2.73685526847839</v>
       </c>
       <c r="H552" t="n">
         <v>1598171</v>
@@ -16406,7 +16406,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H553" t="n">
         <v>899641</v>
@@ -16435,7 +16435,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H554" t="n">
         <v>740489</v>
@@ -16464,7 +16464,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503546714783</v>
+        <v>2.68503570556641</v>
       </c>
       <c r="H555" t="n">
         <v>586866</v>
@@ -16522,7 +16522,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H557" t="n">
         <v>744218</v>
@@ -16638,7 +16638,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281803131104</v>
+        <v>2.83281779289246</v>
       </c>
       <c r="H561" t="n">
         <v>568824</v>
@@ -16667,7 +16667,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019092559814</v>
+        <v>2.80019068717957</v>
       </c>
       <c r="H562" t="n">
         <v>509608</v>
@@ -16783,7 +16783,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H566" t="n">
         <v>264829</v>
@@ -16812,7 +16812,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75029015541077</v>
+        <v>2.75028991699219</v>
       </c>
       <c r="H567" t="n">
         <v>219381</v>
@@ -16870,7 +16870,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H569" t="n">
         <v>328641</v>
@@ -16928,7 +16928,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978101730347</v>
+        <v>2.61978077888489</v>
       </c>
       <c r="H571" t="n">
         <v>581272</v>
@@ -17247,7 +17247,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H582" t="n">
         <v>328175</v>
@@ -17305,7 +17305,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H584" t="n">
         <v>285733</v>
@@ -17334,7 +17334,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H585" t="n">
         <v>250096</v>
@@ -17421,7 +17421,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H588" t="n">
         <v>505464</v>
@@ -17450,7 +17450,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301672935486</v>
+        <v>2.73301696777344</v>
       </c>
       <c r="H589" t="n">
         <v>256840</v>
@@ -17508,7 +17508,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H591" t="n">
         <v>1596803</v>
@@ -17595,7 +17595,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735862731934</v>
+        <v>2.67735838890076</v>
       </c>
       <c r="H594" t="n">
         <v>422850</v>
@@ -17624,7 +17624,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190524101257</v>
+        <v>2.71190500259399</v>
       </c>
       <c r="H595" t="n">
         <v>576828</v>
@@ -17682,7 +17682,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H597" t="n">
         <v>284034</v>
@@ -17711,7 +17711,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.7042281627655</v>
+        <v>2.70422792434692</v>
       </c>
       <c r="H598" t="n">
         <v>201687</v>
@@ -17827,7 +17827,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H602" t="n">
         <v>368932</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H603" t="n">
         <v>435948</v>
@@ -17972,7 +17972,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.3721969127655</v>
+        <v>2.37219715118408</v>
       </c>
       <c r="H607" t="n">
         <v>1221882</v>
@@ -80067,6 +80067,35 @@
         <v>161341</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.26350000500679</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.261500000953674</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.266499996185303</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.266499996185303</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>313284</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2" t="n">
-        <v>3.67819261550903</v>
+        <v>3.67819237709045</v>
       </c>
       <c r="H2" t="n">
         <v>809052</v>
@@ -543,7 +543,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>3.41292929649353</v>
+        <v>3.41292905807495</v>
       </c>
       <c r="H6" t="n">
         <v>652737</v>
@@ -659,7 +659,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>3.39798450469971</v>
+        <v>3.39798474311829</v>
       </c>
       <c r="H10" t="n">
         <v>829652</v>
@@ -775,7 +775,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G14" t="n">
-        <v>3.36622786521912</v>
+        <v>3.36622762680054</v>
       </c>
       <c r="H14" t="n">
         <v>614286</v>
@@ -891,7 +891,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127575874329</v>
+        <v>3.52127599716187</v>
       </c>
       <c r="H18" t="n">
         <v>372353</v>
@@ -1036,7 +1036,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2541446685791</v>
+        <v>3.25414490699768</v>
       </c>
       <c r="H23" t="n">
         <v>614542</v>
@@ -1181,7 +1181,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>2.64329218864441</v>
+        <v>2.64329195022583</v>
       </c>
       <c r="H28" t="n">
         <v>888507</v>
@@ -1210,7 +1210,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405548095703</v>
+        <v>2.77405571937561</v>
       </c>
       <c r="H29" t="n">
         <v>784919</v>
@@ -1239,7 +1239,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636849403381</v>
+        <v>2.65636873245239</v>
       </c>
       <c r="H30" t="n">
         <v>718398</v>
@@ -1326,7 +1326,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>2.40978574752808</v>
+        <v>2.4097855091095</v>
       </c>
       <c r="H33" t="n">
         <v>2581770</v>
@@ -1384,7 +1384,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.49198007583618</v>
+        <v>2.4919798374176</v>
       </c>
       <c r="H35" t="n">
         <v>844299</v>
@@ -1413,7 +1413,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>2.50318837165833</v>
+        <v>2.50318813323975</v>
       </c>
       <c r="H36" t="n">
         <v>421169</v>
@@ -1819,7 +1819,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526377677917</v>
+        <v>2.78526401519775</v>
       </c>
       <c r="H50" t="n">
         <v>3240146</v>
@@ -1848,7 +1848,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>2.78339600563049</v>
+        <v>2.78339576721191</v>
       </c>
       <c r="H51" t="n">
         <v>927105</v>
@@ -1993,7 +1993,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350689888</v>
+        <v>2.75350713729858</v>
       </c>
       <c r="H56" t="n">
         <v>617931</v>
@@ -2022,7 +2022,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603486061096</v>
+        <v>2.74603462219238</v>
       </c>
       <c r="H57" t="n">
         <v>468215</v>
@@ -2283,7 +2283,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G66" t="n">
-        <v>2.50318837165833</v>
+        <v>2.50318813323975</v>
       </c>
       <c r="H66" t="n">
         <v>580199</v>
@@ -2312,7 +2312,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G67" t="n">
-        <v>2.49945259094238</v>
+        <v>2.4994523525238</v>
       </c>
       <c r="H67" t="n">
         <v>487491</v>
@@ -2370,7 +2370,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791042327881</v>
+        <v>2.57791018486023</v>
       </c>
       <c r="H69" t="n">
         <v>847648</v>
@@ -2399,7 +2399,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G70" t="n">
-        <v>2.56296563148499</v>
+        <v>2.56296586990356</v>
       </c>
       <c r="H70" t="n">
         <v>616769</v>
@@ -2428,7 +2428,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G71" t="n">
-        <v>2.52373671531677</v>
+        <v>2.52373647689819</v>
       </c>
       <c r="H71" t="n">
         <v>480652</v>
@@ -2486,7 +2486,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911848068237</v>
+        <v>2.58911871910095</v>
       </c>
       <c r="H73" t="n">
         <v>526922</v>
@@ -2515,7 +2515,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>2.60219502449036</v>
+        <v>2.60219478607178</v>
       </c>
       <c r="H74" t="n">
         <v>119380</v>
@@ -2573,7 +2573,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.62647986412048</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H76" t="n">
         <v>520133</v>
@@ -2602,7 +2602,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395190238953</v>
       </c>
       <c r="H77" t="n">
         <v>329924</v>
@@ -2631,7 +2631,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.62647986412048</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H78" t="n">
         <v>392451</v>
@@ -2660,7 +2660,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384077072144</v>
+        <v>2.66384053230286</v>
       </c>
       <c r="H79" t="n">
         <v>306336</v>
@@ -2747,7 +2747,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702820777893</v>
       </c>
       <c r="H82" t="n">
         <v>202750</v>
@@ -2776,7 +2776,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395166397095</v>
+        <v>2.63395190238953</v>
       </c>
       <c r="H83" t="n">
         <v>139836</v>
@@ -2892,7 +2892,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G87" t="n">
-        <v>2.62087535858154</v>
+        <v>2.62087512016296</v>
       </c>
       <c r="H87" t="n">
         <v>251095</v>
@@ -2950,7 +2950,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911848068237</v>
+        <v>2.58911871910095</v>
       </c>
       <c r="H89" t="n">
         <v>154887</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066017150879</v>
+        <v>2.51066040992737</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3066,7 +3066,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538269996643</v>
+        <v>2.58538246154785</v>
       </c>
       <c r="H93" t="n">
         <v>366421</v>
@@ -3182,7 +3182,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702820777893</v>
       </c>
       <c r="H97" t="n">
         <v>251024</v>
@@ -3240,7 +3240,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G99" t="n">
-        <v>2.6134033203125</v>
+        <v>2.61340355873108</v>
       </c>
       <c r="H99" t="n">
         <v>231020</v>
@@ -3269,7 +3269,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487400054932</v>
       </c>
       <c r="H100" t="n">
         <v>408349</v>
@@ -3298,7 +3298,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7448742389679</v>
+        <v>2.74487400054932</v>
       </c>
       <c r="H101" t="n">
         <v>240708</v>
@@ -3327,7 +3327,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G102" t="n">
-        <v>2.80777740478516</v>
+        <v>2.80777764320374</v>
       </c>
       <c r="H102" t="n">
         <v>317585</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G104" t="n">
-        <v>2.84971308708191</v>
+        <v>2.84971284866333</v>
       </c>
       <c r="H104" t="n">
         <v>323531</v>
@@ -3472,7 +3472,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92595934867859</v>
+        <v>2.92595958709717</v>
       </c>
       <c r="H107" t="n">
         <v>323008</v>
@@ -3646,7 +3646,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G113" t="n">
-        <v>2.97170758247375</v>
+        <v>2.97170734405518</v>
       </c>
       <c r="H113" t="n">
         <v>368199</v>
@@ -3675,7 +3675,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91071033477783</v>
+        <v>2.91071009635925</v>
       </c>
       <c r="H114" t="n">
         <v>1063201</v>
@@ -3849,7 +3849,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85352540016174</v>
+        <v>2.85352563858032</v>
       </c>
       <c r="H120" t="n">
         <v>374301</v>
@@ -3907,7 +3907,7 @@
         <v>3</v>
       </c>
       <c r="G122" t="n">
-        <v>2.85924363136292</v>
+        <v>2.85924386978149</v>
       </c>
       <c r="H122" t="n">
         <v>166984</v>
@@ -4081,7 +4081,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>2.65719056129456</v>
+        <v>2.65719079971313</v>
       </c>
       <c r="H128" t="n">
         <v>191013</v>
@@ -4110,7 +4110,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72200012207031</v>
+        <v>2.72199988365173</v>
       </c>
       <c r="H129" t="n">
         <v>335865</v>
@@ -4255,7 +4255,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563623428345</v>
       </c>
       <c r="H134" t="n">
         <v>360643</v>
@@ -4284,7 +4284,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>2.55425786972046</v>
+        <v>2.55425763130188</v>
       </c>
       <c r="H135" t="n">
         <v>415438</v>
@@ -4458,7 +4458,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53329014778137</v>
+        <v>2.53328990936279</v>
       </c>
       <c r="H141" t="n">
         <v>619648</v>
@@ -4545,7 +4545,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.55425786972046</v>
+        <v>2.55425763130188</v>
       </c>
       <c r="H144" t="n">
         <v>360993</v>
@@ -4632,7 +4632,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G147" t="n">
-        <v>2.65719056129456</v>
+        <v>2.65719079971313</v>
       </c>
       <c r="H147" t="n">
         <v>531605</v>
@@ -4690,7 +4690,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.4551374912262</v>
+        <v>2.45513725280762</v>
       </c>
       <c r="H149" t="n">
         <v>1587031</v>
@@ -4719,7 +4719,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698459625244</v>
+        <v>2.37698483467102</v>
       </c>
       <c r="H150" t="n">
         <v>918463</v>
@@ -5096,7 +5096,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.17493152618408</v>
+        <v>2.17493176460266</v>
       </c>
       <c r="H163" t="n">
         <v>393671</v>
@@ -5125,7 +5125,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.17493152618408</v>
+        <v>2.17493176460266</v>
       </c>
       <c r="H164" t="n">
         <v>347934</v>
@@ -5154,7 +5154,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>2.19208669662476</v>
+        <v>2.19208693504333</v>
       </c>
       <c r="H165" t="n">
         <v>340810</v>
@@ -5212,7 +5212,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258543968201</v>
+        <v>2.22258567810059</v>
       </c>
       <c r="H167" t="n">
         <v>324769</v>
@@ -5241,7 +5241,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G168" t="n">
-        <v>2.24736571311951</v>
+        <v>2.24736595153809</v>
       </c>
       <c r="H168" t="n">
         <v>197676</v>
@@ -5299,7 +5299,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.17683744430542</v>
+        <v>2.176837682724</v>
       </c>
       <c r="H170" t="n">
         <v>631538</v>
@@ -5502,7 +5502,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H177" t="n">
         <v>239497</v>
@@ -5531,7 +5531,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H178" t="n">
         <v>189602</v>
@@ -5821,7 +5821,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G188" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H188" t="n">
         <v>141186</v>
@@ -5879,7 +5879,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956440925598</v>
+        <v>1.99956464767456</v>
       </c>
       <c r="H190" t="n">
         <v>412606</v>
@@ -6111,7 +6111,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H198" t="n">
         <v>370597</v>
@@ -6140,7 +6140,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G199" t="n">
-        <v>1.92713057994843</v>
+        <v>1.92713046073914</v>
       </c>
       <c r="H199" t="n">
         <v>354166</v>
@@ -6169,7 +6169,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191061496735</v>
+        <v>1.95191049575806</v>
       </c>
       <c r="H200" t="n">
         <v>1432038</v>
@@ -6198,7 +6198,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G201" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H201" t="n">
         <v>949601</v>
@@ -6227,7 +6227,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G202" t="n">
-        <v>1.92903637886047</v>
+        <v>1.92903649806976</v>
       </c>
       <c r="H202" t="n">
         <v>442072</v>
@@ -6256,7 +6256,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G203" t="n">
-        <v>1.94619190692902</v>
+        <v>1.94619202613831</v>
       </c>
       <c r="H203" t="n">
         <v>236649</v>
@@ -6314,7 +6314,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G205" t="n">
-        <v>1.92903637886047</v>
+        <v>1.92903649806976</v>
       </c>
       <c r="H205" t="n">
         <v>687316</v>
@@ -6343,7 +6343,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G206" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H206" t="n">
         <v>789726</v>
@@ -6401,7 +6401,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G208" t="n">
-        <v>1.90806889533997</v>
+        <v>1.90806877613068</v>
       </c>
       <c r="H208" t="n">
         <v>711737</v>
@@ -6430,7 +6430,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>1.91759955883026</v>
+        <v>1.91759967803955</v>
       </c>
       <c r="H209" t="n">
         <v>998577</v>
@@ -6517,7 +6517,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186632633209</v>
+        <v>1.89186644554138</v>
       </c>
       <c r="H212" t="n">
         <v>467560</v>
@@ -6546,7 +6546,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G213" t="n">
-        <v>1.8642270565033</v>
+        <v>1.86422693729401</v>
       </c>
       <c r="H213" t="n">
         <v>633127</v>
@@ -6952,7 +6952,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>1.81561994552612</v>
+        <v>1.81561982631683</v>
       </c>
       <c r="H227" t="n">
         <v>1092489</v>
@@ -7010,7 +7010,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>1.78130877017975</v>
+        <v>1.78130888938904</v>
       </c>
       <c r="H229" t="n">
         <v>921990</v>
@@ -7300,7 +7300,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273118495941</v>
+        <v>1.7727313041687</v>
       </c>
       <c r="H239" t="n">
         <v>570721</v>
@@ -7358,7 +7358,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372831344604</v>
+        <v>1.83372843265533</v>
       </c>
       <c r="H241" t="n">
         <v>613856</v>
@@ -7387,7 +7387,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660231113434</v>
+        <v>1.85660243034363</v>
       </c>
       <c r="H242" t="n">
         <v>464622</v>
@@ -7445,7 +7445,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.87757015228271</v>
+        <v>1.87757003307343</v>
       </c>
       <c r="H244" t="n">
         <v>527721</v>
@@ -7561,7 +7561,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H248" t="n">
         <v>502927</v>
@@ -7590,7 +7590,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G249" t="n">
-        <v>1.95953512191772</v>
+        <v>1.95953500270844</v>
       </c>
       <c r="H249" t="n">
         <v>720423</v>
@@ -7619,7 +7619,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H250" t="n">
         <v>638755</v>
@@ -7677,7 +7677,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H252" t="n">
         <v>603474</v>
@@ -7706,7 +7706,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H253" t="n">
         <v>461640</v>
@@ -7764,7 +7764,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575233459473</v>
+        <v>1.99575257301331</v>
       </c>
       <c r="H255" t="n">
         <v>1478455</v>
@@ -7851,7 +7851,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252662658691</v>
+        <v>2.14252686500549</v>
       </c>
       <c r="H258" t="n">
         <v>1054327</v>
@@ -7880,7 +7880,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G259" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H259" t="n">
         <v>1171318</v>
@@ -7938,7 +7938,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G261" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H261" t="n">
         <v>1109093</v>
@@ -7967,7 +7967,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437397003174</v>
+        <v>2.06437373161316</v>
       </c>
       <c r="H262" t="n">
         <v>432968</v>
@@ -7996,7 +7996,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G263" t="n">
-        <v>2.00909519195557</v>
+        <v>2.00909543037415</v>
       </c>
       <c r="H263" t="n">
         <v>959315</v>
@@ -8112,7 +8112,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.09677863121033</v>
+        <v>2.09677886962891</v>
       </c>
       <c r="H267" t="n">
         <v>1644351</v>
@@ -8141,7 +8141,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G268" t="n">
-        <v>2.00718927383423</v>
+        <v>2.00718903541565</v>
       </c>
       <c r="H268" t="n">
         <v>1731581</v>
@@ -8228,7 +8228,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334731578827</v>
+        <v>1.96334743499756</v>
       </c>
       <c r="H271" t="n">
         <v>1260265</v>
@@ -8286,7 +8286,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H273" t="n">
         <v>655413</v>
@@ -8344,7 +8344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287809848785</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H275" t="n">
         <v>590585</v>
@@ -8431,7 +8431,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G278" t="n">
-        <v>1.94619190692902</v>
+        <v>1.94619202613831</v>
       </c>
       <c r="H278" t="n">
         <v>429988</v>
@@ -8518,7 +8518,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>1.8689923286438</v>
+        <v>1.86899244785309</v>
       </c>
       <c r="H281" t="n">
         <v>1316326</v>
@@ -8547,7 +8547,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G282" t="n">
-        <v>1.8642270565033</v>
+        <v>1.86422693729401</v>
       </c>
       <c r="H282" t="n">
         <v>780479</v>
@@ -8576,7 +8576,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.81561994552612</v>
+        <v>1.81561982631683</v>
       </c>
       <c r="H283" t="n">
         <v>878438</v>
@@ -8634,7 +8634,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G285" t="n">
-        <v>1.81371366977692</v>
+        <v>1.81371355056763</v>
       </c>
       <c r="H285" t="n">
         <v>2245645</v>
@@ -8663,7 +8663,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H286" t="n">
         <v>1757407</v>
@@ -8692,7 +8692,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G287" t="n">
-        <v>1.90425634384155</v>
+        <v>1.90425646305084</v>
       </c>
       <c r="H287" t="n">
         <v>1598284</v>
@@ -8779,7 +8779,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H290" t="n">
         <v>483668</v>
@@ -8808,7 +8808,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G291" t="n">
-        <v>1.93666136264801</v>
+        <v>1.93666124343872</v>
       </c>
       <c r="H291" t="n">
         <v>660166</v>
@@ -8837,7 +8837,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G292" t="n">
-        <v>1.92713057994843</v>
+        <v>1.92713046073914</v>
       </c>
       <c r="H292" t="n">
         <v>475359</v>
@@ -8866,7 +8866,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G293" t="n">
-        <v>1.90235030651093</v>
+        <v>1.90235018730164</v>
       </c>
       <c r="H293" t="n">
         <v>452383</v>
@@ -8895,7 +8895,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.9214118719101</v>
+        <v>1.92141199111938</v>
       </c>
       <c r="H294" t="n">
         <v>315857</v>
@@ -8924,7 +8924,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G295" t="n">
-        <v>1.9195054769516</v>
+        <v>1.91950559616089</v>
       </c>
       <c r="H295" t="n">
         <v>317758</v>
@@ -8982,7 +8982,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>1.92522418498993</v>
+        <v>1.92522406578064</v>
       </c>
       <c r="H297" t="n">
         <v>662717</v>
@@ -9011,7 +9011,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H298" t="n">
         <v>1498299</v>
@@ -9040,7 +9040,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.9557226896286</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H299" t="n">
         <v>494953</v>
@@ -9069,7 +9069,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478437423706</v>
+        <v>1.97478461265564</v>
       </c>
       <c r="H300" t="n">
         <v>1084282</v>
@@ -9127,7 +9127,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G302" t="n">
-        <v>1.87280488014221</v>
+        <v>1.87280476093292</v>
       </c>
       <c r="H302" t="n">
         <v>4452878</v>
@@ -9185,7 +9185,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661707401276</v>
+        <v>1.87661695480347</v>
       </c>
       <c r="H304" t="n">
         <v>488529</v>
@@ -9214,7 +9214,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G305" t="n">
-        <v>1.8689923286438</v>
+        <v>1.86899244785309</v>
       </c>
       <c r="H305" t="n">
         <v>614151</v>
@@ -9243,7 +9243,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G306" t="n">
-        <v>1.86994540691376</v>
+        <v>1.86994552612305</v>
       </c>
       <c r="H306" t="n">
         <v>388137</v>
@@ -9359,7 +9359,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G310" t="n">
-        <v>2.01481413841248</v>
+        <v>2.0148138999939</v>
       </c>
       <c r="H310" t="n">
         <v>1837811</v>
@@ -9388,7 +9388,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G311" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H311" t="n">
         <v>3113532</v>
@@ -9446,7 +9446,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G313" t="n">
-        <v>2.10249757766724</v>
+        <v>2.10249733924866</v>
       </c>
       <c r="H313" t="n">
         <v>1169471</v>
@@ -9562,7 +9562,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730666160583</v>
+        <v>2.16730690002441</v>
       </c>
       <c r="H317" t="n">
         <v>2091344</v>
@@ -9707,7 +9707,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G322" t="n">
-        <v>2.24736571311951</v>
+        <v>2.24736595153809</v>
       </c>
       <c r="H322" t="n">
         <v>838718</v>
@@ -9939,7 +9939,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645656585693</v>
+        <v>2.30645680427551</v>
       </c>
       <c r="H330" t="n">
         <v>409387</v>
@@ -10113,7 +10113,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>2.39414000511169</v>
+        <v>2.39414024353027</v>
       </c>
       <c r="H336" t="n">
         <v>1849332</v>
@@ -10200,7 +10200,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270330429077</v>
+        <v>2.38270306587219</v>
       </c>
       <c r="H339" t="n">
         <v>350392</v>
@@ -10229,7 +10229,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36554789543152</v>
+        <v>2.3655481338501</v>
       </c>
       <c r="H340" t="n">
         <v>423860</v>
@@ -10258,7 +10258,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938973426819</v>
+        <v>2.40938949584961</v>
       </c>
       <c r="H341" t="n">
         <v>1086286</v>
@@ -10403,7 +10403,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563623428345</v>
       </c>
       <c r="H346" t="n">
         <v>1281154</v>
@@ -80096,6 +80096,35 @@
         <v>313284</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.272000014781952</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.264499992132187</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>198867</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -572,7 +572,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930417060852</v>
+        <v>3.37930393218994</v>
       </c>
       <c r="H7" t="n">
         <v>489296</v>
@@ -659,7 +659,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>3.39798474311829</v>
+        <v>3.39798450469971</v>
       </c>
       <c r="H10" t="n">
         <v>829652</v>
@@ -775,7 +775,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G14" t="n">
-        <v>3.36622762680054</v>
+        <v>3.36622786521912</v>
       </c>
       <c r="H14" t="n">
         <v>614286</v>
@@ -804,7 +804,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3886444568634</v>
+        <v>3.38864421844482</v>
       </c>
       <c r="H15" t="n">
         <v>742869</v>
@@ -1036,7 +1036,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G23" t="n">
-        <v>3.25414490699768</v>
+        <v>3.2541446685791</v>
       </c>
       <c r="H23" t="n">
         <v>614542</v>
@@ -1297,7 +1297,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72922253608704</v>
+        <v>2.72922229766846</v>
       </c>
       <c r="H32" t="n">
         <v>485309</v>
@@ -1413,7 +1413,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>2.50318813323975</v>
+        <v>2.50318837165833</v>
       </c>
       <c r="H36" t="n">
         <v>421169</v>
@@ -1500,7 +1500,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395921707153</v>
+        <v>2.46395897865295</v>
       </c>
       <c r="H39" t="n">
         <v>414034</v>
@@ -1529,7 +1529,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120899200439</v>
+        <v>2.53120923042297</v>
       </c>
       <c r="H40" t="n">
         <v>622697</v>
@@ -1558,7 +1558,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G41" t="n">
-        <v>2.79460406303406</v>
+        <v>2.79460430145264</v>
       </c>
       <c r="H41" t="n">
         <v>2765448</v>
@@ -1674,7 +1674,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G45" t="n">
-        <v>2.73856282234192</v>
+        <v>2.73856258392334</v>
       </c>
       <c r="H45" t="n">
         <v>644573</v>
@@ -1877,7 +1877,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80581259727478</v>
+        <v>2.8058123588562</v>
       </c>
       <c r="H52" t="n">
         <v>881692</v>
@@ -1935,7 +1935,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G54" t="n">
-        <v>2.73856282234192</v>
+        <v>2.73856258392334</v>
       </c>
       <c r="H54" t="n">
         <v>631029</v>
@@ -1964,7 +1964,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065333366394</v>
+        <v>2.68065309524536</v>
       </c>
       <c r="H55" t="n">
         <v>571416</v>
@@ -2022,7 +2022,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603462219238</v>
+        <v>2.74603486061096</v>
       </c>
       <c r="H57" t="n">
         <v>468215</v>
@@ -2051,7 +2051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.71801400184631</v>
+        <v>2.71801424026489</v>
       </c>
       <c r="H58" t="n">
         <v>634534</v>
@@ -2254,7 +2254,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>2.64889597892761</v>
+        <v>2.64889621734619</v>
       </c>
       <c r="H65" t="n">
         <v>389941</v>
@@ -2283,7 +2283,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G66" t="n">
-        <v>2.50318813323975</v>
+        <v>2.50318837165833</v>
       </c>
       <c r="H66" t="n">
         <v>580199</v>
@@ -2341,7 +2341,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>2.44714665412903</v>
+        <v>2.44714689254761</v>
       </c>
       <c r="H68" t="n">
         <v>346515</v>
@@ -2428,7 +2428,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G71" t="n">
-        <v>2.52373647689819</v>
+        <v>2.52373671531677</v>
       </c>
       <c r="H71" t="n">
         <v>480652</v>
@@ -2515,7 +2515,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>2.60219478607178</v>
+        <v>2.60219502449036</v>
       </c>
       <c r="H74" t="n">
         <v>119380</v>
@@ -2573,7 +2573,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.6264796257019</v>
+        <v>2.62647986412048</v>
       </c>
       <c r="H76" t="n">
         <v>520133</v>
@@ -2602,7 +2602,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G77" t="n">
-        <v>2.63395190238953</v>
+        <v>2.63395166397095</v>
       </c>
       <c r="H77" t="n">
         <v>329924</v>
@@ -2631,7 +2631,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.6264796257019</v>
+        <v>2.62647986412048</v>
       </c>
       <c r="H78" t="n">
         <v>392451</v>
@@ -2660,7 +2660,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384053230286</v>
+        <v>2.66384029388428</v>
       </c>
       <c r="H79" t="n">
         <v>306336</v>
@@ -2689,7 +2689,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065333366394</v>
+        <v>2.68065309524536</v>
       </c>
       <c r="H80" t="n">
         <v>263802</v>
@@ -2747,7 +2747,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702820777893</v>
+        <v>2.64702844619751</v>
       </c>
       <c r="H82" t="n">
         <v>202750</v>
@@ -2776,7 +2776,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.63395190238953</v>
+        <v>2.63395166397095</v>
       </c>
       <c r="H83" t="n">
         <v>139836</v>
@@ -2834,7 +2834,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263247489929</v>
+        <v>2.65263223648071</v>
       </c>
       <c r="H85" t="n">
         <v>83792</v>
@@ -2863,7 +2863,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208389282227</v>
+        <v>2.63208365440369</v>
       </c>
       <c r="H86" t="n">
         <v>115454</v>
@@ -2892,7 +2892,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G87" t="n">
-        <v>2.62087512016296</v>
+        <v>2.62087535858154</v>
       </c>
       <c r="H87" t="n">
         <v>251095</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066040992737</v>
+        <v>2.51066017150879</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3008,7 +3008,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G91" t="n">
-        <v>2.55175757408142</v>
+        <v>2.5517578125</v>
       </c>
       <c r="H91" t="n">
         <v>189126</v>
@@ -3066,7 +3066,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538246154785</v>
+        <v>2.58538222312927</v>
       </c>
       <c r="H93" t="n">
         <v>366421</v>
@@ -3095,7 +3095,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G94" t="n">
-        <v>2.5648341178894</v>
+        <v>2.56483387947083</v>
       </c>
       <c r="H94" t="n">
         <v>359206</v>
@@ -3124,7 +3124,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G95" t="n">
-        <v>2.59098649024963</v>
+        <v>2.59098672866821</v>
       </c>
       <c r="H95" t="n">
         <v>301461</v>
@@ -3153,7 +3153,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>2.65450048446655</v>
+        <v>2.65450024604797</v>
       </c>
       <c r="H96" t="n">
         <v>228387</v>
@@ -3182,7 +3182,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702820777893</v>
+        <v>2.64702844619751</v>
       </c>
       <c r="H97" t="n">
         <v>251024</v>
@@ -3240,7 +3240,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G99" t="n">
-        <v>2.61340355873108</v>
+        <v>2.6134033203125</v>
       </c>
       <c r="H99" t="n">
         <v>231020</v>
@@ -80125,6 +80125,35 @@
         <v>198867</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.272000014781952</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>197770</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599804878235</v>
+        <v>3.59599781036377</v>
       </c>
       <c r="H3" t="n">
         <v>611692</v>
@@ -485,7 +485,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62588691711426</v>
+        <v>3.62588667869568</v>
       </c>
       <c r="H4" t="n">
         <v>748185</v>
@@ -572,7 +572,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930393218994</v>
+        <v>3.37930417060852</v>
       </c>
       <c r="H7" t="n">
         <v>489296</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655418395996</v>
+        <v>3.44655394554138</v>
       </c>
       <c r="H8" t="n">
         <v>335339</v>
@@ -630,7 +630,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>3.49325513839722</v>
+        <v>3.4932553768158</v>
       </c>
       <c r="H9" t="n">
         <v>197035</v>
@@ -659,7 +659,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>3.39798450469971</v>
+        <v>3.39798474311829</v>
       </c>
       <c r="H10" t="n">
         <v>829652</v>
@@ -688,7 +688,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G11" t="n">
-        <v>3.39985299110413</v>
+        <v>3.39985275268555</v>
       </c>
       <c r="H11" t="n">
         <v>1221987</v>
@@ -746,7 +746,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G13" t="n">
-        <v>3.42787384986877</v>
+        <v>3.4278736114502</v>
       </c>
       <c r="H13" t="n">
         <v>410306</v>
@@ -804,7 +804,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.38864421844482</v>
+        <v>3.3886444568634</v>
       </c>
       <c r="H15" t="n">
         <v>742869</v>
@@ -862,7 +862,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.43160963058472</v>
+        <v>3.4316098690033</v>
       </c>
       <c r="H17" t="n">
         <v>415584</v>
@@ -891,7 +891,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127599716187</v>
+        <v>3.52127623558044</v>
       </c>
       <c r="H18" t="n">
         <v>372353</v>
@@ -949,7 +949,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062383651733</v>
+        <v>3.36062359809875</v>
       </c>
       <c r="H20" t="n">
         <v>463309</v>
@@ -1094,7 +1094,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.25788068771362</v>
+        <v>3.2578809261322</v>
       </c>
       <c r="H25" t="n">
         <v>832589</v>
@@ -1210,7 +1210,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405571937561</v>
+        <v>2.77405548095703</v>
       </c>
       <c r="H29" t="n">
         <v>784919</v>
@@ -1239,7 +1239,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G30" t="n">
-        <v>2.65636873245239</v>
+        <v>2.65636849403381</v>
       </c>
       <c r="H30" t="n">
         <v>718398</v>
@@ -1326,7 +1326,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4097855091095</v>
+        <v>2.40978574752808</v>
       </c>
       <c r="H33" t="n">
         <v>2581770</v>
@@ -1355,7 +1355,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45835518836975</v>
+        <v>2.45835494995117</v>
       </c>
       <c r="H34" t="n">
         <v>1399376</v>
@@ -1500,7 +1500,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395897865295</v>
+        <v>2.46395921707153</v>
       </c>
       <c r="H39" t="n">
         <v>414034</v>
@@ -1529,7 +1529,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120923042297</v>
+        <v>2.53120899200439</v>
       </c>
       <c r="H40" t="n">
         <v>622697</v>
@@ -1703,7 +1703,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988201141357</v>
+        <v>2.71988224983215</v>
       </c>
       <c r="H46" t="n">
         <v>1083110</v>
@@ -1877,7 +1877,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8058123588562</v>
+        <v>2.80581259727478</v>
       </c>
       <c r="H52" t="n">
         <v>881692</v>
@@ -1993,7 +1993,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350713729858</v>
+        <v>2.75350689888</v>
       </c>
       <c r="H56" t="n">
         <v>617931</v>
@@ -2080,7 +2080,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988201141357</v>
+        <v>2.71988224983215</v>
       </c>
       <c r="H59" t="n">
         <v>486311</v>
@@ -2109,7 +2109,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G60" t="n">
-        <v>2.63768792152405</v>
+        <v>2.63768768310547</v>
       </c>
       <c r="H60" t="n">
         <v>807171</v>
@@ -2138,7 +2138,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65076422691345</v>
+        <v>2.65076446533203</v>
       </c>
       <c r="H61" t="n">
         <v>421361</v>
@@ -2225,7 +2225,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G64" t="n">
-        <v>2.58164620399475</v>
+        <v>2.58164644241333</v>
       </c>
       <c r="H64" t="n">
         <v>791010</v>
@@ -2254,7 +2254,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>2.64889621734619</v>
+        <v>2.64889645576477</v>
       </c>
       <c r="H65" t="n">
         <v>389941</v>
@@ -2341,7 +2341,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>2.44714689254761</v>
+        <v>2.44714641571045</v>
       </c>
       <c r="H68" t="n">
         <v>346515</v>
@@ -2370,7 +2370,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791018486023</v>
+        <v>2.57791042327881</v>
       </c>
       <c r="H69" t="n">
         <v>847648</v>
@@ -2486,7 +2486,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911871910095</v>
+        <v>2.58911895751953</v>
       </c>
       <c r="H73" t="n">
         <v>526922</v>
@@ -2573,7 +2573,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.62647986412048</v>
+        <v>2.62647938728333</v>
       </c>
       <c r="H76" t="n">
         <v>520133</v>
@@ -2631,7 +2631,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.62647986412048</v>
+        <v>2.62647938728333</v>
       </c>
       <c r="H78" t="n">
         <v>392451</v>
@@ -2660,7 +2660,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384029388428</v>
+        <v>2.66384077072144</v>
       </c>
       <c r="H79" t="n">
         <v>306336</v>
@@ -2747,7 +2747,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G82" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702820777893</v>
       </c>
       <c r="H82" t="n">
         <v>202750</v>
@@ -2805,7 +2805,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G84" t="n">
-        <v>2.62834763526917</v>
+        <v>2.62834787368774</v>
       </c>
       <c r="H84" t="n">
         <v>97873</v>
@@ -2863,7 +2863,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208365440369</v>
+        <v>2.63208389282227</v>
       </c>
       <c r="H86" t="n">
         <v>115454</v>
@@ -2950,7 +2950,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911871910095</v>
+        <v>2.58911895751953</v>
       </c>
       <c r="H89" t="n">
         <v>154887</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066017150879</v>
+        <v>2.51066040992737</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3066,7 +3066,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538222312927</v>
+        <v>2.58538246154785</v>
       </c>
       <c r="H93" t="n">
         <v>366421</v>
@@ -3182,7 +3182,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G97" t="n">
-        <v>2.64702844619751</v>
+        <v>2.64702820777893</v>
       </c>
       <c r="H97" t="n">
         <v>251024</v>
@@ -3269,7 +3269,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>2.74487400054932</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H100" t="n">
         <v>408349</v>
@@ -3298,7 +3298,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>2.74487400054932</v>
+        <v>2.7448742389679</v>
       </c>
       <c r="H101" t="n">
         <v>240708</v>
@@ -3704,7 +3704,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G115" t="n">
-        <v>2.82874512672424</v>
+        <v>2.82874536514282</v>
       </c>
       <c r="H115" t="n">
         <v>388875</v>
@@ -3849,7 +3849,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85352563858032</v>
+        <v>2.85352540016174</v>
       </c>
       <c r="H120" t="n">
         <v>374301</v>
@@ -3965,7 +3965,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>2.65909671783447</v>
+        <v>2.65909695625305</v>
       </c>
       <c r="H124" t="n">
         <v>451934</v>
@@ -3994,7 +3994,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.56760120391846</v>
+        <v>2.56760096549988</v>
       </c>
       <c r="H125" t="n">
         <v>525319</v>
@@ -4110,7 +4110,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72199988365173</v>
+        <v>2.72200012207031</v>
       </c>
       <c r="H129" t="n">
         <v>335865</v>
@@ -4139,7 +4139,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>2.59619331359863</v>
+        <v>2.59619355201721</v>
       </c>
       <c r="H130" t="n">
         <v>222114</v>
@@ -4197,7 +4197,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G132" t="n">
-        <v>2.46276235580444</v>
+        <v>2.46276211738586</v>
       </c>
       <c r="H132" t="n">
         <v>543169</v>
@@ -4255,7 +4255,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563623428345</v>
+        <v>2.48563599586487</v>
       </c>
       <c r="H134" t="n">
         <v>360643</v>
@@ -4284,7 +4284,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>2.55425763130188</v>
+        <v>2.55425786972046</v>
       </c>
       <c r="H135" t="n">
         <v>415438</v>
@@ -4313,7 +4313,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.57141327857971</v>
+        <v>2.57141351699829</v>
       </c>
       <c r="H136" t="n">
         <v>548868</v>
@@ -4429,7 +4429,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G140" t="n">
-        <v>2.60572409629822</v>
+        <v>2.6057243347168</v>
       </c>
       <c r="H140" t="n">
         <v>864905</v>
@@ -4458,7 +4458,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53328990936279</v>
+        <v>2.53329014778137</v>
       </c>
       <c r="H141" t="n">
         <v>619648</v>
@@ -4545,7 +4545,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G144" t="n">
-        <v>2.55425763130188</v>
+        <v>2.55425786972046</v>
       </c>
       <c r="H144" t="n">
         <v>360993</v>
@@ -4690,7 +4690,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.45513725280762</v>
+        <v>2.4551374912262</v>
       </c>
       <c r="H149" t="n">
         <v>1587031</v>
@@ -4719,7 +4719,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698483467102</v>
+        <v>2.37698459625244</v>
       </c>
       <c r="H150" t="n">
         <v>918463</v>
@@ -4777,7 +4777,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G152" t="n">
-        <v>2.24164724349976</v>
+        <v>2.24164700508118</v>
       </c>
       <c r="H152" t="n">
         <v>402686</v>
@@ -4806,7 +4806,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G153" t="n">
-        <v>2.24927186965942</v>
+        <v>2.24927163124084</v>
       </c>
       <c r="H153" t="n">
         <v>332222</v>
@@ -4864,7 +4864,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G155" t="n">
-        <v>2.32551836967468</v>
+        <v>2.32551860809326</v>
       </c>
       <c r="H155" t="n">
         <v>305944</v>
@@ -4893,7 +4893,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H156" t="n">
         <v>229323</v>
@@ -4951,7 +4951,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G158" t="n">
-        <v>2.35220432281494</v>
+        <v>2.35220456123352</v>
       </c>
       <c r="H158" t="n">
         <v>512824</v>
@@ -4980,7 +4980,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>2.33504915237427</v>
+        <v>2.33504939079285</v>
       </c>
       <c r="H159" t="n">
         <v>248797</v>
@@ -5096,7 +5096,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G163" t="n">
-        <v>2.17493176460266</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H163" t="n">
         <v>393671</v>
@@ -5125,7 +5125,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>2.17493176460266</v>
+        <v>2.17493152618408</v>
       </c>
       <c r="H164" t="n">
         <v>347934</v>
@@ -5212,7 +5212,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258567810059</v>
+        <v>2.22258543968201</v>
       </c>
       <c r="H167" t="n">
         <v>324769</v>
@@ -5270,7 +5270,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G169" t="n">
-        <v>2.19399333000183</v>
+        <v>2.19399309158325</v>
       </c>
       <c r="H169" t="n">
         <v>313201</v>
@@ -5299,7 +5299,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.176837682724</v>
+        <v>2.17683744430542</v>
       </c>
       <c r="H170" t="n">
         <v>631538</v>
@@ -5357,7 +5357,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>2.21305465698242</v>
+        <v>2.213054895401</v>
       </c>
       <c r="H172" t="n">
         <v>375938</v>
@@ -5415,7 +5415,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24164724349976</v>
+        <v>2.24164700508118</v>
       </c>
       <c r="H174" t="n">
         <v>233862</v>
@@ -5473,7 +5473,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H176" t="n">
         <v>181659</v>
@@ -5502,7 +5502,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H177" t="n">
         <v>239497</v>
@@ -5531,7 +5531,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H178" t="n">
         <v>189602</v>
@@ -5589,7 +5589,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G180" t="n">
-        <v>2.153963804245</v>
+        <v>2.15396356582642</v>
       </c>
       <c r="H180" t="n">
         <v>353939</v>
@@ -5734,7 +5734,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484294891357</v>
+        <v>2.05484318733215</v>
       </c>
       <c r="H185" t="n">
         <v>188205</v>
@@ -5763,7 +5763,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G186" t="n">
-        <v>2.05865573883057</v>
+        <v>2.05865550041199</v>
       </c>
       <c r="H186" t="n">
         <v>162410</v>
@@ -5792,7 +5792,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>2.08724784851074</v>
+        <v>2.08724808692932</v>
       </c>
       <c r="H187" t="n">
         <v>178971</v>
@@ -5850,7 +5850,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H189" t="n">
         <v>178603</v>
@@ -5879,7 +5879,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G190" t="n">
-        <v>1.99956464767456</v>
+        <v>1.99956452846527</v>
       </c>
       <c r="H190" t="n">
         <v>412606</v>
@@ -5908,7 +5908,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H191" t="n">
         <v>217002</v>
@@ -5995,7 +5995,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G194" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H194" t="n">
         <v>156156</v>
@@ -6053,7 +6053,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H196" t="n">
         <v>598584</v>
@@ -6082,7 +6082,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H197" t="n">
         <v>249799</v>
@@ -6111,7 +6111,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000433921814</v>
       </c>
       <c r="H198" t="n">
         <v>370597</v>
@@ -6169,7 +6169,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191049575806</v>
+        <v>1.95191061496735</v>
       </c>
       <c r="H200" t="n">
         <v>1432038</v>
@@ -6227,7 +6227,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G202" t="n">
-        <v>1.92903649806976</v>
+        <v>1.92903637886047</v>
       </c>
       <c r="H202" t="n">
         <v>442072</v>
@@ -6314,7 +6314,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G205" t="n">
-        <v>1.92903649806976</v>
+        <v>1.92903637886047</v>
       </c>
       <c r="H205" t="n">
         <v>687316</v>
@@ -6372,7 +6372,7 @@
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H207" t="n">
         <v>580889</v>
@@ -6488,7 +6488,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803925037384</v>
       </c>
       <c r="H211" t="n">
         <v>545183</v>
@@ -6517,7 +6517,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186644554138</v>
+        <v>1.89186632633209</v>
       </c>
       <c r="H212" t="n">
         <v>467560</v>
@@ -6575,7 +6575,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>1.87185156345367</v>
+        <v>1.87185168266296</v>
       </c>
       <c r="H214" t="n">
         <v>537617</v>
@@ -6604,7 +6604,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803948879242</v>
+        <v>1.86803925037384</v>
       </c>
       <c r="H215" t="n">
         <v>225249</v>
@@ -6720,7 +6720,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038533687592</v>
+        <v>1.82038521766663</v>
       </c>
       <c r="H219" t="n">
         <v>227009</v>
@@ -6807,7 +6807,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95762884616852</v>
+        <v>1.95762872695923</v>
       </c>
       <c r="H222" t="n">
         <v>2654520</v>
@@ -6894,7 +6894,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G225" t="n">
-        <v>1.8394467830658</v>
+        <v>1.83944690227509</v>
       </c>
       <c r="H225" t="n">
         <v>728977</v>
@@ -6981,7 +6981,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H228" t="n">
         <v>443928</v>
@@ -7039,7 +7039,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G230" t="n">
-        <v>1.78512132167816</v>
+        <v>1.78512120246887</v>
       </c>
       <c r="H230" t="n">
         <v>640171</v>
@@ -7097,7 +7097,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G232" t="n">
-        <v>1.81847906112671</v>
+        <v>1.818479180336</v>
       </c>
       <c r="H232" t="n">
         <v>294423</v>
@@ -7126,7 +7126,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G233" t="n">
-        <v>1.79179275035858</v>
+        <v>1.79179286956787</v>
       </c>
       <c r="H233" t="n">
         <v>212483</v>
@@ -7155,7 +7155,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.71554625034332</v>
+        <v>1.71554613113403</v>
       </c>
       <c r="H234" t="n">
         <v>705149</v>
@@ -7242,7 +7242,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509191513062</v>
+        <v>1.74509179592133</v>
       </c>
       <c r="H237" t="n">
         <v>547803</v>
@@ -7300,7 +7300,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.7727313041687</v>
+        <v>1.77273118495941</v>
       </c>
       <c r="H239" t="n">
         <v>570721</v>
@@ -7358,7 +7358,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372843265533</v>
+        <v>1.83372831344604</v>
       </c>
       <c r="H241" t="n">
         <v>613856</v>
@@ -7387,7 +7387,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660243034363</v>
+        <v>1.85660231113434</v>
       </c>
       <c r="H242" t="n">
         <v>464622</v>
@@ -7416,7 +7416,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G243" t="n">
-        <v>1.84993076324463</v>
+        <v>1.84993088245392</v>
       </c>
       <c r="H243" t="n">
         <v>467341</v>
@@ -7503,7 +7503,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G246" t="n">
-        <v>1.91378700733185</v>
+        <v>1.91378712654114</v>
       </c>
       <c r="H246" t="n">
         <v>567797</v>
@@ -7532,7 +7532,7 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>1.90616261959076</v>
+        <v>1.90616250038147</v>
       </c>
       <c r="H247" t="n">
         <v>435355</v>
@@ -7561,7 +7561,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G248" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H248" t="n">
         <v>502927</v>
@@ -7619,7 +7619,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H250" t="n">
         <v>638755</v>
@@ -7677,7 +7677,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H252" t="n">
         <v>603474</v>
@@ -7706,7 +7706,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H253" t="n">
         <v>461640</v>
@@ -7735,7 +7735,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G254" t="n">
-        <v>1.97097218036652</v>
+        <v>1.97097206115723</v>
       </c>
       <c r="H254" t="n">
         <v>225821</v>
@@ -7764,7 +7764,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575257301331</v>
+        <v>1.99575245380402</v>
       </c>
       <c r="H255" t="n">
         <v>1478455</v>
@@ -7851,7 +7851,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252686500549</v>
+        <v>2.14252662658691</v>
       </c>
       <c r="H258" t="n">
         <v>1054327</v>
@@ -7909,7 +7909,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674958229065</v>
+        <v>2.05674934387207</v>
       </c>
       <c r="H260" t="n">
         <v>1146682</v>
@@ -7967,7 +7967,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437373161316</v>
+        <v>2.06437420845032</v>
       </c>
       <c r="H262" t="n">
         <v>432968</v>
@@ -8199,7 +8199,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G270" t="n">
-        <v>1.91378700733185</v>
+        <v>1.91378712654114</v>
       </c>
       <c r="H270" t="n">
         <v>1352186</v>
@@ -8228,7 +8228,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334743499756</v>
+        <v>1.96334755420685</v>
       </c>
       <c r="H271" t="n">
         <v>1260265</v>
@@ -8257,7 +8257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.93475496768951</v>
+        <v>1.9347550868988</v>
       </c>
       <c r="H272" t="n">
         <v>1120465</v>
@@ -8286,7 +8286,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H273" t="n">
         <v>655413</v>
@@ -8315,7 +8315,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G274" t="n">
-        <v>1.99193966388702</v>
+        <v>1.99193978309631</v>
       </c>
       <c r="H274" t="n">
         <v>752887</v>
@@ -8344,7 +8344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287821769714</v>
       </c>
       <c r="H275" t="n">
         <v>590585</v>
@@ -8402,7 +8402,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765849113464</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H277" t="n">
         <v>1178960</v>
@@ -8460,7 +8460,7 @@
         <v>1.99699997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>1.90330326557159</v>
+        <v>1.90330338478088</v>
       </c>
       <c r="H279" t="n">
         <v>1004346</v>
@@ -8489,7 +8489,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G280" t="n">
-        <v>1.85946154594421</v>
+        <v>1.8594616651535</v>
       </c>
       <c r="H280" t="n">
         <v>1197568</v>
@@ -8518,7 +8518,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>1.86899244785309</v>
+        <v>1.8689923286438</v>
       </c>
       <c r="H281" t="n">
         <v>1316326</v>
@@ -8634,7 +8634,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G285" t="n">
-        <v>1.81371355056763</v>
+        <v>1.81371366977692</v>
       </c>
       <c r="H285" t="n">
         <v>2245645</v>
@@ -8663,7 +8663,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H286" t="n">
         <v>1757407</v>
@@ -8721,7 +8721,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G288" t="n">
-        <v>1.89472568035126</v>
+        <v>1.89472556114197</v>
       </c>
       <c r="H288" t="n">
         <v>588961</v>
@@ -8779,7 +8779,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H290" t="n">
         <v>483668</v>
@@ -8866,7 +8866,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G293" t="n">
-        <v>1.90235018730164</v>
+        <v>1.90235030651093</v>
       </c>
       <c r="H293" t="n">
         <v>452383</v>
@@ -8895,7 +8895,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.92141199111938</v>
+        <v>1.9214118719101</v>
       </c>
       <c r="H294" t="n">
         <v>315857</v>
@@ -8953,7 +8953,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G296" t="n">
-        <v>1.89091312885284</v>
+        <v>1.89091336727142</v>
       </c>
       <c r="H296" t="n">
         <v>272700</v>
@@ -8982,7 +8982,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>1.92522406578064</v>
+        <v>1.92522418498993</v>
       </c>
       <c r="H297" t="n">
         <v>662717</v>
@@ -9011,7 +9011,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000433921814</v>
       </c>
       <c r="H298" t="n">
         <v>1498299</v>
@@ -9040,7 +9040,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H299" t="n">
         <v>494953</v>
@@ -9069,7 +9069,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478461265564</v>
+        <v>1.97478449344635</v>
       </c>
       <c r="H300" t="n">
         <v>1084282</v>
@@ -9098,7 +9098,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G301" t="n">
-        <v>1.95762884616852</v>
+        <v>1.95762872695923</v>
       </c>
       <c r="H301" t="n">
         <v>941040</v>
@@ -9156,7 +9156,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471091747284</v>
+        <v>1.87471079826355</v>
       </c>
       <c r="H303" t="n">
         <v>726032</v>
@@ -9185,7 +9185,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661695480347</v>
+        <v>1.87661707401276</v>
       </c>
       <c r="H304" t="n">
         <v>488529</v>
@@ -9214,7 +9214,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G305" t="n">
-        <v>1.86899244785309</v>
+        <v>1.8689923286438</v>
       </c>
       <c r="H305" t="n">
         <v>614151</v>
@@ -9330,7 +9330,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.99003374576569</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H309" t="n">
         <v>821834</v>
@@ -9446,7 +9446,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G313" t="n">
-        <v>2.10249733924866</v>
+        <v>2.10249757766724</v>
       </c>
       <c r="H313" t="n">
         <v>1169471</v>
@@ -9504,7 +9504,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>2.06246781349182</v>
+        <v>2.0624680519104</v>
       </c>
       <c r="H315" t="n">
         <v>682468</v>
@@ -9562,7 +9562,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730690002441</v>
+        <v>2.16730666160583</v>
       </c>
       <c r="H317" t="n">
         <v>2091344</v>
@@ -9591,7 +9591,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>2.22067928314209</v>
+        <v>2.22067904472351</v>
       </c>
       <c r="H318" t="n">
         <v>2072704</v>
@@ -9620,7 +9620,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G319" t="n">
-        <v>2.3502984046936</v>
+        <v>2.35029864311218</v>
       </c>
       <c r="H319" t="n">
         <v>3123574</v>
@@ -9649,7 +9649,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>2.25880265235901</v>
+        <v>2.25880241394043</v>
       </c>
       <c r="H320" t="n">
         <v>1458698</v>
@@ -9678,7 +9678,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.25880265235901</v>
+        <v>2.25880241394043</v>
       </c>
       <c r="H321" t="n">
         <v>490380</v>
@@ -9736,7 +9736,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G323" t="n">
-        <v>2.28548884391785</v>
+        <v>2.28548908233643</v>
       </c>
       <c r="H323" t="n">
         <v>900752</v>
@@ -9765,7 +9765,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355340003967</v>
+        <v>2.24355363845825</v>
       </c>
       <c r="H324" t="n">
         <v>869705</v>
@@ -9823,7 +9823,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>2.22067928314209</v>
+        <v>2.22067904472351</v>
       </c>
       <c r="H326" t="n">
         <v>1037293</v>
@@ -9852,7 +9852,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H327" t="n">
         <v>791379</v>
@@ -9910,7 +9910,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G329" t="n">
-        <v>2.30836272239685</v>
+        <v>2.30836296081543</v>
       </c>
       <c r="H329" t="n">
         <v>1324811</v>
@@ -9939,7 +9939,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645680427551</v>
+        <v>2.30645704269409</v>
       </c>
       <c r="H330" t="n">
         <v>409387</v>
@@ -9997,7 +9997,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H332" t="n">
         <v>380492</v>
@@ -10026,7 +10026,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.26833367347717</v>
+        <v>2.26833343505859</v>
       </c>
       <c r="H333" t="n">
         <v>427893</v>
@@ -10142,7 +10142,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G337" t="n">
-        <v>2.42463874816895</v>
+        <v>2.42463850975037</v>
       </c>
       <c r="H337" t="n">
         <v>563874</v>
@@ -10200,7 +10200,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270306587219</v>
+        <v>2.38270330429077</v>
       </c>
       <c r="H339" t="n">
         <v>350392</v>
@@ -10229,7 +10229,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.3655481338501</v>
+        <v>2.36554765701294</v>
       </c>
       <c r="H340" t="n">
         <v>423860</v>
@@ -10258,7 +10258,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G341" t="n">
-        <v>2.40938949584961</v>
+        <v>2.40938973426819</v>
       </c>
       <c r="H341" t="n">
         <v>1086286</v>
@@ -10316,7 +10316,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41129541397095</v>
+        <v>2.41129565238953</v>
       </c>
       <c r="H343" t="n">
         <v>830346</v>
@@ -10403,7 +10403,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563623428345</v>
+        <v>2.48563599586487</v>
       </c>
       <c r="H346" t="n">
         <v>1281154</v>
@@ -10635,7 +10635,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G354" t="n">
-        <v>2.60572409629822</v>
+        <v>2.6057243347168</v>
       </c>
       <c r="H354" t="n">
         <v>907898</v>
@@ -10693,7 +10693,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058856010437</v>
+        <v>2.60058832168579</v>
       </c>
       <c r="H356" t="n">
         <v>605694</v>
@@ -10925,7 +10925,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806670188904</v>
+        <v>2.70806646347046</v>
       </c>
       <c r="H364" t="n">
         <v>849448</v>
@@ -10983,7 +10983,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715992927551</v>
+        <v>2.77715969085693</v>
       </c>
       <c r="H366" t="n">
         <v>1578655</v>
@@ -11128,7 +11128,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H371" t="n">
         <v>692586</v>
@@ -11157,7 +11157,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.72917866706848</v>
+        <v>2.7291784286499</v>
       </c>
       <c r="H372" t="n">
         <v>600785</v>
@@ -11331,7 +11331,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514119148254</v>
+        <v>2.82514095306396</v>
       </c>
       <c r="H378" t="n">
         <v>369015</v>
@@ -11447,7 +11447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H382" t="n">
         <v>194578</v>
@@ -11534,7 +11534,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H385" t="n">
         <v>512623</v>
@@ -11621,7 +11621,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.89807271957397</v>
+        <v>2.8980724811554</v>
       </c>
       <c r="H388" t="n">
         <v>1185420</v>
@@ -11766,7 +11766,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H393" t="n">
         <v>1082817</v>
@@ -11795,7 +11795,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H394" t="n">
         <v>382748</v>
@@ -11940,7 +11940,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363159179688</v>
+        <v>3.00363183021545</v>
       </c>
       <c r="H399" t="n">
         <v>217171</v>
@@ -11969,7 +11969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757537841797</v>
+        <v>3.14757561683655</v>
       </c>
       <c r="H400" t="n">
         <v>1320738</v>
@@ -12288,7 +12288,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343891143799</v>
+        <v>3.29343867301941</v>
       </c>
       <c r="H411" t="n">
         <v>758243</v>
@@ -12375,7 +12375,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H414" t="n">
         <v>480519</v>
@@ -12462,7 +12462,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818422317505</v>
+        <v>3.22818446159363</v>
       </c>
       <c r="H417" t="n">
         <v>285532</v>
@@ -12491,7 +12491,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H418" t="n">
         <v>195515</v>
@@ -12636,7 +12636,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596076965332</v>
+        <v>3.18596053123474</v>
       </c>
       <c r="H423" t="n">
         <v>127820</v>
@@ -12694,7 +12694,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040189743042</v>
+        <v>3.08040165901184</v>
       </c>
       <c r="H425" t="n">
         <v>401854</v>
@@ -12752,7 +12752,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H427" t="n">
         <v>748285</v>
@@ -12781,7 +12781,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707225799561</v>
+        <v>3.20707249641418</v>
       </c>
       <c r="H428" t="n">
         <v>535469</v>
@@ -12839,7 +12839,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020272254944</v>
+        <v>3.18020296096802</v>
       </c>
       <c r="H430" t="n">
         <v>159000</v>
@@ -13042,7 +13042,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H437" t="n">
         <v>851102</v>
@@ -13100,7 +13100,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H439" t="n">
         <v>269780</v>
@@ -13129,7 +13129,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H440" t="n">
         <v>183536</v>
@@ -13245,7 +13245,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H444" t="n">
         <v>548564</v>
@@ -13303,7 +13303,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647592544556</v>
+        <v>3.50647616386414</v>
       </c>
       <c r="H446" t="n">
         <v>1496771</v>
@@ -13361,7 +13361,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809101104736</v>
+        <v>3.46809077262878</v>
       </c>
       <c r="H448" t="n">
         <v>331930</v>
@@ -13622,7 +13622,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899778366089</v>
+        <v>3.39899802207947</v>
       </c>
       <c r="H457" t="n">
         <v>786922</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H458" t="n">
         <v>169837</v>
@@ -13680,7 +13680,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889855384827</v>
+        <v>3.44889831542969</v>
       </c>
       <c r="H459" t="n">
         <v>96243</v>
@@ -14028,7 +14028,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940745353699</v>
+        <v>3.57940769195557</v>
       </c>
       <c r="H471" t="n">
         <v>517225</v>
@@ -14086,7 +14086,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264364242554</v>
+        <v>3.69264340400696</v>
       </c>
       <c r="H473" t="n">
         <v>1575544</v>
@@ -14115,7 +14115,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122749328613</v>
+        <v>3.63122725486755</v>
       </c>
       <c r="H474" t="n">
         <v>392936</v>
@@ -14173,7 +14173,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223397254944</v>
+        <v>3.51223373413086</v>
       </c>
       <c r="H476" t="n">
         <v>1052005</v>
@@ -14289,7 +14289,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H480" t="n">
         <v>1897823</v>
@@ -14318,7 +14318,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H481" t="n">
         <v>1344877</v>
@@ -14376,7 +14376,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502944946289</v>
+        <v>2.49502921104431</v>
       </c>
       <c r="H483" t="n">
         <v>1113397</v>
@@ -14434,7 +14434,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736440658569</v>
+        <v>2.86736464500427</v>
       </c>
       <c r="H485" t="n">
         <v>2335973</v>
@@ -14637,7 +14637,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H492" t="n">
         <v>360031</v>
@@ -14840,7 +14840,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.8481719493866</v>
+        <v>2.84817218780518</v>
       </c>
       <c r="H499" t="n">
         <v>177776</v>
@@ -14956,7 +14956,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H503" t="n">
         <v>781804</v>
@@ -15014,7 +15014,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H505" t="n">
         <v>362332</v>
@@ -15043,7 +15043,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H506" t="n">
         <v>249155</v>
@@ -15072,7 +15072,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H507" t="n">
         <v>199788</v>
@@ -15101,7 +15101,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230865478516</v>
+        <v>2.70230889320374</v>
       </c>
       <c r="H508" t="n">
         <v>228947</v>
@@ -15130,7 +15130,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H509" t="n">
         <v>305291</v>
@@ -15275,7 +15275,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928391456604</v>
+        <v>2.86928367614746</v>
       </c>
       <c r="H514" t="n">
         <v>468533</v>
@@ -15420,7 +15420,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H519" t="n">
         <v>477584</v>
@@ -15478,7 +15478,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H521" t="n">
         <v>402806</v>
@@ -15565,7 +15565,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877453804016</v>
+        <v>2.73877477645874</v>
       </c>
       <c r="H524" t="n">
         <v>549359</v>
@@ -15594,7 +15594,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563805580139</v>
+        <v>2.57563829421997</v>
       </c>
       <c r="H525" t="n">
         <v>7158793</v>
@@ -15652,7 +15652,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614743232727</v>
+        <v>2.70614719390869</v>
       </c>
       <c r="H527" t="n">
         <v>1136471</v>
@@ -15739,7 +15739,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H530" t="n">
         <v>821537</v>
@@ -15797,7 +15797,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H532" t="n">
         <v>874097</v>
@@ -15942,7 +15942,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H537" t="n">
         <v>1383977</v>
@@ -16377,7 +16377,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685526847839</v>
+        <v>2.73685550689697</v>
       </c>
       <c r="H552" t="n">
         <v>1598171</v>
@@ -16406,7 +16406,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H553" t="n">
         <v>899641</v>
@@ -16435,7 +16435,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H554" t="n">
         <v>740489</v>
@@ -16464,7 +16464,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503570556641</v>
+        <v>2.68503546714783</v>
       </c>
       <c r="H555" t="n">
         <v>586866</v>
@@ -16522,7 +16522,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H557" t="n">
         <v>744218</v>
@@ -16638,7 +16638,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281779289246</v>
+        <v>2.83281803131104</v>
       </c>
       <c r="H561" t="n">
         <v>568824</v>
@@ -16667,7 +16667,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019068717957</v>
+        <v>2.80019092559814</v>
       </c>
       <c r="H562" t="n">
         <v>509608</v>
@@ -16783,7 +16783,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H566" t="n">
         <v>264829</v>
@@ -16812,7 +16812,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75028991699219</v>
+        <v>2.75029015541077</v>
       </c>
       <c r="H567" t="n">
         <v>219381</v>
@@ -16870,7 +16870,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H569" t="n">
         <v>328641</v>
@@ -16928,7 +16928,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978077888489</v>
+        <v>2.61978101730347</v>
       </c>
       <c r="H571" t="n">
         <v>581272</v>
@@ -17247,7 +17247,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H582" t="n">
         <v>328175</v>
@@ -17305,7 +17305,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H584" t="n">
         <v>285733</v>
@@ -17334,7 +17334,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H585" t="n">
         <v>250096</v>
@@ -17421,7 +17421,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H588" t="n">
         <v>505464</v>
@@ -17450,7 +17450,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301696777344</v>
+        <v>2.73301672935486</v>
       </c>
       <c r="H589" t="n">
         <v>256840</v>
@@ -17508,7 +17508,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H591" t="n">
         <v>1596803</v>
@@ -17595,7 +17595,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735838890076</v>
+        <v>2.67735862731934</v>
       </c>
       <c r="H594" t="n">
         <v>422850</v>
@@ -17624,7 +17624,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190500259399</v>
+        <v>2.71190524101257</v>
       </c>
       <c r="H595" t="n">
         <v>576828</v>
@@ -17682,7 +17682,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H597" t="n">
         <v>284034</v>
@@ -17711,7 +17711,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.70422792434692</v>
+        <v>2.7042281627655</v>
       </c>
       <c r="H598" t="n">
         <v>201687</v>
@@ -17827,7 +17827,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H602" t="n">
         <v>368932</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H603" t="n">
         <v>435948</v>
@@ -17972,7 +17972,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.37219715118408</v>
+        <v>2.3721969127655</v>
       </c>
       <c r="H607" t="n">
         <v>1221882</v>
@@ -80154,6 +80154,35 @@
         <v>197770</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.270999997854233</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.270999997854233</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.263000011444092</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>540856</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599781036377</v>
+        <v>3.59599804878235</v>
       </c>
       <c r="H3" t="n">
         <v>611692</v>
@@ -485,7 +485,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62588667869568</v>
+        <v>3.62588691711426</v>
       </c>
       <c r="H4" t="n">
         <v>748185</v>
@@ -572,7 +572,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930417060852</v>
+        <v>3.37930393218994</v>
       </c>
       <c r="H7" t="n">
         <v>489296</v>
@@ -717,7 +717,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G12" t="n">
-        <v>3.32886648178101</v>
+        <v>3.32886672019958</v>
       </c>
       <c r="H12" t="n">
         <v>597600</v>
@@ -804,7 +804,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3886444568634</v>
+        <v>3.38864421844482</v>
       </c>
       <c r="H15" t="n">
         <v>742869</v>
@@ -862,7 +862,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4316098690033</v>
+        <v>3.43160963058472</v>
       </c>
       <c r="H17" t="n">
         <v>415584</v>
@@ -1094,7 +1094,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2578809261322</v>
+        <v>3.25788068771362</v>
       </c>
       <c r="H25" t="n">
         <v>832589</v>
@@ -1210,7 +1210,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405548095703</v>
+        <v>2.77405571937561</v>
       </c>
       <c r="H29" t="n">
         <v>784919</v>
@@ -1297,7 +1297,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72922229766846</v>
+        <v>2.72922253608704</v>
       </c>
       <c r="H32" t="n">
         <v>485309</v>
@@ -1326,7 +1326,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>2.40978574752808</v>
+        <v>2.4097855091095</v>
       </c>
       <c r="H33" t="n">
         <v>2581770</v>
@@ -1384,7 +1384,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G35" t="n">
-        <v>2.4919798374176</v>
+        <v>2.49198007583618</v>
       </c>
       <c r="H35" t="n">
         <v>844299</v>
@@ -1471,7 +1471,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52747297286987</v>
+        <v>2.52747273445129</v>
       </c>
       <c r="H38" t="n">
         <v>913911</v>
@@ -1529,7 +1529,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120899200439</v>
+        <v>2.53120923042297</v>
       </c>
       <c r="H40" t="n">
         <v>622697</v>
@@ -1616,7 +1616,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>2.76471543312073</v>
+        <v>2.76471519470215</v>
       </c>
       <c r="H43" t="n">
         <v>1274763</v>
@@ -1645,7 +1645,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>2.76471543312073</v>
+        <v>2.76471519470215</v>
       </c>
       <c r="H44" t="n">
         <v>1144614</v>
@@ -1790,7 +1790,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G49" t="n">
-        <v>2.62274360656738</v>
+        <v>2.62274384498596</v>
       </c>
       <c r="H49" t="n">
         <v>618759</v>
@@ -1819,7 +1819,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526401519775</v>
+        <v>2.78526425361633</v>
       </c>
       <c r="H50" t="n">
         <v>3240146</v>
@@ -1877,7 +1877,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G52" t="n">
-        <v>2.80581259727478</v>
+        <v>2.8058123588562</v>
       </c>
       <c r="H52" t="n">
         <v>881692</v>
@@ -1906,7 +1906,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>2.76471543312073</v>
+        <v>2.76471519470215</v>
       </c>
       <c r="H53" t="n">
         <v>939951</v>
@@ -2022,7 +2022,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603486061096</v>
+        <v>2.74603509902954</v>
       </c>
       <c r="H57" t="n">
         <v>468215</v>
@@ -2051,7 +2051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.71801424026489</v>
+        <v>2.71801447868347</v>
       </c>
       <c r="H58" t="n">
         <v>634534</v>
@@ -2167,7 +2167,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G62" t="n">
-        <v>2.68625712394714</v>
+        <v>2.68625688552856</v>
       </c>
       <c r="H62" t="n">
         <v>751565</v>
@@ -2312,7 +2312,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G67" t="n">
-        <v>2.4994523525238</v>
+        <v>2.49945211410522</v>
       </c>
       <c r="H67" t="n">
         <v>487491</v>
@@ -2341,7 +2341,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>2.44714641571045</v>
+        <v>2.44714665412903</v>
       </c>
       <c r="H68" t="n">
         <v>346515</v>
@@ -2370,7 +2370,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791042327881</v>
+        <v>2.57791018486023</v>
       </c>
       <c r="H69" t="n">
         <v>847648</v>
@@ -2486,7 +2486,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911895751953</v>
+        <v>2.58911871910095</v>
       </c>
       <c r="H73" t="n">
         <v>526922</v>
@@ -2573,7 +2573,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G76" t="n">
-        <v>2.62647938728333</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H76" t="n">
         <v>520133</v>
@@ -2631,7 +2631,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G78" t="n">
-        <v>2.62647938728333</v>
+        <v>2.6264796257019</v>
       </c>
       <c r="H78" t="n">
         <v>392451</v>
@@ -2660,7 +2660,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66384077072144</v>
+        <v>2.66384053230286</v>
       </c>
       <c r="H79" t="n">
         <v>306336</v>
@@ -2805,7 +2805,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G84" t="n">
-        <v>2.62834787368774</v>
+        <v>2.62834763526917</v>
       </c>
       <c r="H84" t="n">
         <v>97873</v>
@@ -2863,7 +2863,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208389282227</v>
+        <v>2.63208365440369</v>
       </c>
       <c r="H86" t="n">
         <v>115454</v>
@@ -2892,7 +2892,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G87" t="n">
-        <v>2.62087535858154</v>
+        <v>2.62087559700012</v>
       </c>
       <c r="H87" t="n">
         <v>251095</v>
@@ -2950,7 +2950,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911895751953</v>
+        <v>2.58911871910095</v>
       </c>
       <c r="H89" t="n">
         <v>154887</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066040992737</v>
+        <v>2.51066017150879</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3066,7 +3066,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538246154785</v>
+        <v>2.58538222312927</v>
       </c>
       <c r="H93" t="n">
         <v>366421</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G104" t="n">
-        <v>2.84971284866333</v>
+        <v>2.84971308708191</v>
       </c>
       <c r="H104" t="n">
         <v>323531</v>
@@ -3588,7 +3588,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G111" t="n">
-        <v>2.96598887443542</v>
+        <v>2.965989112854</v>
       </c>
       <c r="H111" t="n">
         <v>727600</v>
@@ -3704,7 +3704,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G115" t="n">
-        <v>2.82874536514282</v>
+        <v>2.82874512672424</v>
       </c>
       <c r="H115" t="n">
         <v>388875</v>
@@ -3762,7 +3762,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7315309047699</v>
+        <v>2.73153066635132</v>
       </c>
       <c r="H117" t="n">
         <v>277740</v>
@@ -3878,7 +3878,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G121" t="n">
-        <v>2.8954610824585</v>
+        <v>2.89546084403992</v>
       </c>
       <c r="H121" t="n">
         <v>241175</v>
@@ -3965,7 +3965,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>2.65909695625305</v>
+        <v>2.65909671783447</v>
       </c>
       <c r="H124" t="n">
         <v>451934</v>
@@ -4226,7 +4226,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.47801113128662</v>
+        <v>2.4780113697052</v>
       </c>
       <c r="H133" t="n">
         <v>352159</v>
@@ -4487,7 +4487,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G142" t="n">
-        <v>2.59428715705872</v>
+        <v>2.59428739547729</v>
       </c>
       <c r="H142" t="n">
         <v>656732</v>
@@ -4661,7 +4661,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G148" t="n">
-        <v>2.65337824821472</v>
+        <v>2.6533784866333</v>
       </c>
       <c r="H148" t="n">
         <v>325972</v>
@@ -4719,7 +4719,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698459625244</v>
+        <v>2.37698483467102</v>
       </c>
       <c r="H150" t="n">
         <v>918463</v>
@@ -4748,7 +4748,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G151" t="n">
-        <v>2.31408143043518</v>
+        <v>2.3140811920166</v>
       </c>
       <c r="H151" t="n">
         <v>639368</v>
@@ -4806,7 +4806,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G153" t="n">
-        <v>2.24927163124084</v>
+        <v>2.24927186965942</v>
       </c>
       <c r="H153" t="n">
         <v>332222</v>
@@ -4864,7 +4864,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G155" t="n">
-        <v>2.32551860809326</v>
+        <v>2.32551836967468</v>
       </c>
       <c r="H155" t="n">
         <v>305944</v>
@@ -4980,7 +4980,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>2.33504939079285</v>
+        <v>2.33504915237427</v>
       </c>
       <c r="H159" t="n">
         <v>248797</v>
@@ -5067,7 +5067,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>2.2111485004425</v>
+        <v>2.21114873886108</v>
       </c>
       <c r="H162" t="n">
         <v>380323</v>
@@ -5212,7 +5212,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258543968201</v>
+        <v>2.22258567810059</v>
       </c>
       <c r="H167" t="n">
         <v>324769</v>
@@ -5299,7 +5299,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.17683744430542</v>
+        <v>2.176837682724</v>
       </c>
       <c r="H170" t="n">
         <v>631538</v>
@@ -5328,7 +5328,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G171" t="n">
-        <v>2.2244918346405</v>
+        <v>2.22449207305908</v>
       </c>
       <c r="H171" t="n">
         <v>376315</v>
@@ -5444,7 +5444,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G175" t="n">
-        <v>2.2244918346405</v>
+        <v>2.22449207305908</v>
       </c>
       <c r="H175" t="n">
         <v>209639</v>
@@ -5473,7 +5473,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G176" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H176" t="n">
         <v>181659</v>
@@ -5502,7 +5502,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H177" t="n">
         <v>239497</v>
@@ -5531,7 +5531,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211646080017</v>
+        <v>2.23211622238159</v>
       </c>
       <c r="H178" t="n">
         <v>189602</v>
@@ -5560,7 +5560,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G179" t="n">
-        <v>2.19780540466309</v>
+        <v>2.19780516624451</v>
       </c>
       <c r="H179" t="n">
         <v>319118</v>
@@ -5589,7 +5589,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G180" t="n">
-        <v>2.15396356582642</v>
+        <v>2.153963804245</v>
       </c>
       <c r="H180" t="n">
         <v>353939</v>
@@ -5676,7 +5676,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.07771730422974</v>
+        <v>2.07771706581116</v>
       </c>
       <c r="H183" t="n">
         <v>428647</v>
@@ -5705,7 +5705,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G184" t="n">
-        <v>2.07771730422974</v>
+        <v>2.07771706581116</v>
       </c>
       <c r="H184" t="n">
         <v>406878</v>
@@ -5734,7 +5734,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484318733215</v>
+        <v>2.05484294891357</v>
       </c>
       <c r="H185" t="n">
         <v>188205</v>
@@ -5821,7 +5821,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G188" t="n">
-        <v>2.08534169197083</v>
+        <v>2.0853419303894</v>
       </c>
       <c r="H188" t="n">
         <v>141186</v>
@@ -5908,7 +5908,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765813350677</v>
+        <v>1.99765837192535</v>
       </c>
       <c r="H191" t="n">
         <v>217002</v>
@@ -6024,7 +6024,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G195" t="n">
-        <v>1.96525359153748</v>
+        <v>1.96525371074677</v>
       </c>
       <c r="H195" t="n">
         <v>560311</v>
@@ -6053,7 +6053,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.99003386497498</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H196" t="n">
         <v>598584</v>
@@ -6082,7 +6082,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.99003386497498</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H197" t="n">
         <v>249799</v>
@@ -6111,7 +6111,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H198" t="n">
         <v>370597</v>
@@ -6430,7 +6430,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>1.91759967803955</v>
+        <v>1.91759955883026</v>
       </c>
       <c r="H209" t="n">
         <v>998577</v>
@@ -6488,7 +6488,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>1.86803925037384</v>
+        <v>1.86803936958313</v>
       </c>
       <c r="H211" t="n">
         <v>545183</v>
@@ -6517,7 +6517,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186632633209</v>
+        <v>1.89186644554138</v>
       </c>
       <c r="H212" t="n">
         <v>467560</v>
@@ -6604,7 +6604,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.86803925037384</v>
+        <v>1.86803936958313</v>
       </c>
       <c r="H215" t="n">
         <v>225249</v>
@@ -6633,7 +6633,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G216" t="n">
-        <v>1.84802460670471</v>
+        <v>1.84802448749542</v>
       </c>
       <c r="H216" t="n">
         <v>332041</v>
@@ -6720,7 +6720,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038521766663</v>
+        <v>1.82038533687592</v>
       </c>
       <c r="H219" t="n">
         <v>227009</v>
@@ -6778,7 +6778,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G221" t="n">
-        <v>1.80227673053741</v>
+        <v>1.8022768497467</v>
       </c>
       <c r="H221" t="n">
         <v>462867</v>
@@ -7039,7 +7039,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G230" t="n">
-        <v>1.78512120246887</v>
+        <v>1.78512132167816</v>
       </c>
       <c r="H230" t="n">
         <v>640171</v>
@@ -7068,7 +7068,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>1.80608904361725</v>
+        <v>1.80608892440796</v>
       </c>
       <c r="H231" t="n">
         <v>343567</v>
@@ -7097,7 +7097,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G232" t="n">
-        <v>1.818479180336</v>
+        <v>1.81847906112671</v>
       </c>
       <c r="H232" t="n">
         <v>294423</v>
@@ -7155,7 +7155,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.71554613113403</v>
+        <v>1.71554625034332</v>
       </c>
       <c r="H234" t="n">
         <v>705149</v>
@@ -7329,7 +7329,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G240" t="n">
-        <v>1.79465210437775</v>
+        <v>1.79465198516846</v>
       </c>
       <c r="H240" t="n">
         <v>447469</v>
@@ -7358,7 +7358,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83372831344604</v>
+        <v>1.83372843265533</v>
       </c>
       <c r="H241" t="n">
         <v>613856</v>
@@ -7445,7 +7445,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.87757003307343</v>
+        <v>1.87757015228271</v>
       </c>
       <c r="H244" t="n">
         <v>527721</v>
@@ -7619,7 +7619,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.95572292804718</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H250" t="n">
         <v>638755</v>
@@ -7677,7 +7677,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287821769714</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H252" t="n">
         <v>603474</v>
@@ -7706,7 +7706,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.95572292804718</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H253" t="n">
         <v>461640</v>
@@ -7851,7 +7851,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252662658691</v>
+        <v>2.14252686500549</v>
       </c>
       <c r="H258" t="n">
         <v>1054327</v>
@@ -7880,7 +7880,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G259" t="n">
-        <v>2.08534169197083</v>
+        <v>2.0853419303894</v>
       </c>
       <c r="H259" t="n">
         <v>1171318</v>
@@ -7938,7 +7938,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G261" t="n">
-        <v>2.08534169197083</v>
+        <v>2.0853419303894</v>
       </c>
       <c r="H261" t="n">
         <v>1109093</v>
@@ -7967,7 +7967,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G262" t="n">
-        <v>2.06437420845032</v>
+        <v>2.06437397003174</v>
       </c>
       <c r="H262" t="n">
         <v>432968</v>
@@ -8228,7 +8228,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.96334755420685</v>
+        <v>1.96334743499756</v>
       </c>
       <c r="H271" t="n">
         <v>1260265</v>
@@ -8257,7 +8257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.9347550868988</v>
+        <v>1.93475496768951</v>
       </c>
       <c r="H272" t="n">
         <v>1120465</v>
@@ -8286,7 +8286,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287821769714</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H273" t="n">
         <v>655413</v>
@@ -8344,7 +8344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287821769714</v>
+        <v>1.97287833690643</v>
       </c>
       <c r="H275" t="n">
         <v>590585</v>
@@ -8402,7 +8402,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765813350677</v>
+        <v>1.99765837192535</v>
       </c>
       <c r="H277" t="n">
         <v>1178960</v>
@@ -8489,7 +8489,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G280" t="n">
-        <v>1.8594616651535</v>
+        <v>1.85946154594421</v>
       </c>
       <c r="H280" t="n">
         <v>1197568</v>
@@ -8721,7 +8721,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G288" t="n">
-        <v>1.89472556114197</v>
+        <v>1.89472568035126</v>
       </c>
       <c r="H288" t="n">
         <v>588961</v>
@@ -8895,7 +8895,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.9214118719101</v>
+        <v>1.92141199111938</v>
       </c>
       <c r="H294" t="n">
         <v>315857</v>
@@ -8953,7 +8953,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G296" t="n">
-        <v>1.89091336727142</v>
+        <v>1.89091324806213</v>
       </c>
       <c r="H296" t="n">
         <v>272700</v>
@@ -9011,7 +9011,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000433921814</v>
+        <v>1.95000422000885</v>
       </c>
       <c r="H298" t="n">
         <v>1498299</v>
@@ -9040,7 +9040,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.95572292804718</v>
+        <v>1.95572280883789</v>
       </c>
       <c r="H299" t="n">
         <v>494953</v>
@@ -9156,7 +9156,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471079826355</v>
+        <v>1.87471091747284</v>
       </c>
       <c r="H303" t="n">
         <v>726032</v>
@@ -9185,7 +9185,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661707401276</v>
+        <v>1.87661695480347</v>
       </c>
       <c r="H304" t="n">
         <v>488529</v>
@@ -9330,7 +9330,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.99003386497498</v>
+        <v>1.9900336265564</v>
       </c>
       <c r="H309" t="n">
         <v>821834</v>
@@ -9388,7 +9388,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G311" t="n">
-        <v>2.08534169197083</v>
+        <v>2.0853419303894</v>
       </c>
       <c r="H311" t="n">
         <v>3113532</v>
@@ -9446,7 +9446,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G313" t="n">
-        <v>2.10249757766724</v>
+        <v>2.10249733924866</v>
       </c>
       <c r="H313" t="n">
         <v>1169471</v>
@@ -9562,7 +9562,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730666160583</v>
+        <v>2.16730690002441</v>
       </c>
       <c r="H317" t="n">
         <v>2091344</v>
@@ -9649,7 +9649,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>2.25880241394043</v>
+        <v>2.25880265235901</v>
       </c>
       <c r="H320" t="n">
         <v>1458698</v>
@@ -9678,7 +9678,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.25880241394043</v>
+        <v>2.25880265235901</v>
       </c>
       <c r="H321" t="n">
         <v>490380</v>
@@ -9765,7 +9765,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24355363845825</v>
+        <v>2.24355340003967</v>
       </c>
       <c r="H324" t="n">
         <v>869705</v>
@@ -10142,7 +10142,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G337" t="n">
-        <v>2.42463850975037</v>
+        <v>2.42463874816895</v>
       </c>
       <c r="H337" t="n">
         <v>563874</v>
@@ -10200,7 +10200,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270330429077</v>
+        <v>2.38270306587219</v>
       </c>
       <c r="H339" t="n">
         <v>350392</v>
@@ -10229,7 +10229,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G340" t="n">
-        <v>2.36554765701294</v>
+        <v>2.36554789543152</v>
       </c>
       <c r="H340" t="n">
         <v>423860</v>
@@ -10490,7 +10490,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G349" t="n">
-        <v>2.68578314781189</v>
+        <v>2.68578290939331</v>
       </c>
       <c r="H349" t="n">
         <v>873271</v>
@@ -10519,7 +10519,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>2.68578314781189</v>
+        <v>2.68578290939331</v>
       </c>
       <c r="H350" t="n">
         <v>855548</v>
@@ -10548,7 +10548,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G351" t="n">
-        <v>2.68578314781189</v>
+        <v>2.68578290939331</v>
       </c>
       <c r="H351" t="n">
         <v>812058</v>
@@ -10577,7 +10577,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>2.57331943511963</v>
+        <v>2.57331967353821</v>
       </c>
       <c r="H352" t="n">
         <v>1478509</v>
@@ -10693,7 +10693,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058832168579</v>
+        <v>2.60058856010437</v>
       </c>
       <c r="H356" t="n">
         <v>605694</v>
@@ -10925,7 +10925,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806646347046</v>
+        <v>2.70806670188904</v>
       </c>
       <c r="H364" t="n">
         <v>849448</v>
@@ -10983,7 +10983,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715969085693</v>
+        <v>2.77715992927551</v>
       </c>
       <c r="H366" t="n">
         <v>1578655</v>
@@ -11128,7 +11128,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H371" t="n">
         <v>692586</v>
@@ -11157,7 +11157,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.7291784286499</v>
+        <v>2.72917866706848</v>
       </c>
       <c r="H372" t="n">
         <v>600785</v>
@@ -11331,7 +11331,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514095306396</v>
+        <v>2.82514119148254</v>
       </c>
       <c r="H378" t="n">
         <v>369015</v>
@@ -11447,7 +11447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H382" t="n">
         <v>194578</v>
@@ -11534,7 +11534,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H385" t="n">
         <v>512623</v>
@@ -11621,7 +11621,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.8980724811554</v>
+        <v>2.89807271957397</v>
       </c>
       <c r="H388" t="n">
         <v>1185420</v>
@@ -11766,7 +11766,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H393" t="n">
         <v>1082817</v>
@@ -11795,7 +11795,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645787239075</v>
+        <v>2.93645763397217</v>
       </c>
       <c r="H394" t="n">
         <v>382748</v>
@@ -11940,7 +11940,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363183021545</v>
+        <v>3.00363159179688</v>
       </c>
       <c r="H399" t="n">
         <v>217171</v>
@@ -11969,7 +11969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757561683655</v>
+        <v>3.14757537841797</v>
       </c>
       <c r="H400" t="n">
         <v>1320738</v>
@@ -12288,7 +12288,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343867301941</v>
+        <v>3.29343891143799</v>
       </c>
       <c r="H411" t="n">
         <v>758243</v>
@@ -12375,7 +12375,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H414" t="n">
         <v>480519</v>
@@ -12462,7 +12462,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818446159363</v>
+        <v>3.22818422317505</v>
       </c>
       <c r="H417" t="n">
         <v>285532</v>
@@ -12491,7 +12491,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747614860535</v>
+        <v>3.19747638702393</v>
       </c>
       <c r="H418" t="n">
         <v>195515</v>
@@ -12636,7 +12636,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596053123474</v>
+        <v>3.18596076965332</v>
       </c>
       <c r="H423" t="n">
         <v>127820</v>
@@ -12694,7 +12694,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040165901184</v>
+        <v>3.08040189743042</v>
       </c>
       <c r="H425" t="n">
         <v>401854</v>
@@ -12752,7 +12752,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H427" t="n">
         <v>748285</v>
@@ -12781,7 +12781,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707249641418</v>
+        <v>3.20707225799561</v>
       </c>
       <c r="H428" t="n">
         <v>535469</v>
@@ -12839,7 +12839,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020296096802</v>
+        <v>3.18020272254944</v>
       </c>
       <c r="H430" t="n">
         <v>159000</v>
@@ -13042,7 +13042,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858811378479</v>
+        <v>3.21858787536621</v>
       </c>
       <c r="H437" t="n">
         <v>851102</v>
@@ -13100,7 +13100,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H439" t="n">
         <v>269780</v>
@@ -13129,7 +13129,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616572380066</v>
+        <v>3.27616548538208</v>
       </c>
       <c r="H440" t="n">
         <v>183536</v>
@@ -13245,7 +13245,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H444" t="n">
         <v>548564</v>
@@ -13303,7 +13303,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647616386414</v>
+        <v>3.50647592544556</v>
       </c>
       <c r="H446" t="n">
         <v>1496771</v>
@@ -13361,7 +13361,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809077262878</v>
+        <v>3.46809101104736</v>
       </c>
       <c r="H448" t="n">
         <v>331930</v>
@@ -13622,7 +13622,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899802207947</v>
+        <v>3.39899778366089</v>
       </c>
       <c r="H457" t="n">
         <v>786922</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465588569641</v>
+        <v>3.45465612411499</v>
       </c>
       <c r="H458" t="n">
         <v>169837</v>
@@ -13680,7 +13680,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889831542969</v>
+        <v>3.44889855384827</v>
       </c>
       <c r="H459" t="n">
         <v>96243</v>
@@ -14028,7 +14028,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940769195557</v>
+        <v>3.57940745353699</v>
       </c>
       <c r="H471" t="n">
         <v>517225</v>
@@ -14086,7 +14086,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264340400696</v>
+        <v>3.69264364242554</v>
       </c>
       <c r="H473" t="n">
         <v>1575544</v>
@@ -14115,7 +14115,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122725486755</v>
+        <v>3.63122749328613</v>
       </c>
       <c r="H474" t="n">
         <v>392936</v>
@@ -14173,7 +14173,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223373413086</v>
+        <v>3.51223397254944</v>
       </c>
       <c r="H476" t="n">
         <v>1052005</v>
@@ -14289,7 +14289,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H480" t="n">
         <v>1897823</v>
@@ -14318,7 +14318,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H481" t="n">
         <v>1344877</v>
@@ -14376,7 +14376,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502921104431</v>
+        <v>2.49502944946289</v>
       </c>
       <c r="H483" t="n">
         <v>1113397</v>
@@ -14434,7 +14434,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736464500427</v>
+        <v>2.86736440658569</v>
       </c>
       <c r="H485" t="n">
         <v>2335973</v>
@@ -14637,7 +14637,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H492" t="n">
         <v>360031</v>
@@ -14840,7 +14840,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.84817218780518</v>
+        <v>2.8481719493866</v>
       </c>
       <c r="H499" t="n">
         <v>177776</v>
@@ -14956,7 +14956,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H503" t="n">
         <v>781804</v>
@@ -15014,7 +15014,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938338279724</v>
+        <v>2.81938314437866</v>
       </c>
       <c r="H505" t="n">
         <v>362332</v>
@@ -15043,7 +15043,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H506" t="n">
         <v>249155</v>
@@ -15072,7 +15072,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H507" t="n">
         <v>199788</v>
@@ -15101,7 +15101,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230889320374</v>
+        <v>2.70230865478516</v>
       </c>
       <c r="H508" t="n">
         <v>228947</v>
@@ -15130,7 +15130,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H509" t="n">
         <v>305291</v>
@@ -15275,7 +15275,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928367614746</v>
+        <v>2.86928391456604</v>
       </c>
       <c r="H514" t="n">
         <v>468533</v>
@@ -15420,7 +15420,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80210995674133</v>
+        <v>2.80211019515991</v>
       </c>
       <c r="H519" t="n">
         <v>477584</v>
@@ -15478,7 +15478,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75412845611572</v>
+        <v>2.7541286945343</v>
       </c>
       <c r="H521" t="n">
         <v>402806</v>
@@ -15565,7 +15565,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877477645874</v>
+        <v>2.73877453804016</v>
       </c>
       <c r="H524" t="n">
         <v>549359</v>
@@ -15594,7 +15594,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563829421997</v>
+        <v>2.57563805580139</v>
       </c>
       <c r="H525" t="n">
         <v>7158793</v>
@@ -15652,7 +15652,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614719390869</v>
+        <v>2.70614743232727</v>
       </c>
       <c r="H527" t="n">
         <v>1136471</v>
@@ -15739,7 +15739,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H530" t="n">
         <v>821537</v>
@@ -15797,7 +15797,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H532" t="n">
         <v>874097</v>
@@ -15942,7 +15942,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.54301071166992</v>
+        <v>2.5430109500885</v>
       </c>
       <c r="H537" t="n">
         <v>1383977</v>
@@ -16377,7 +16377,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685550689697</v>
+        <v>2.73685526847839</v>
       </c>
       <c r="H552" t="n">
         <v>1598171</v>
@@ -16406,7 +16406,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H553" t="n">
         <v>899641</v>
@@ -16435,7 +16435,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H554" t="n">
         <v>740489</v>
@@ -16464,7 +16464,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503546714783</v>
+        <v>2.68503570556641</v>
       </c>
       <c r="H555" t="n">
         <v>586866</v>
@@ -16522,7 +16522,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H557" t="n">
         <v>744218</v>
@@ -16638,7 +16638,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281803131104</v>
+        <v>2.83281779289246</v>
       </c>
       <c r="H561" t="n">
         <v>568824</v>
@@ -16667,7 +16667,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019092559814</v>
+        <v>2.80019068717957</v>
       </c>
       <c r="H562" t="n">
         <v>509608</v>
@@ -16783,7 +16783,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H566" t="n">
         <v>264829</v>
@@ -16812,7 +16812,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75029015541077</v>
+        <v>2.75028991699219</v>
       </c>
       <c r="H567" t="n">
         <v>219381</v>
@@ -16870,7 +16870,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008520126343</v>
+        <v>2.66008543968201</v>
       </c>
       <c r="H569" t="n">
         <v>328641</v>
@@ -16928,7 +16928,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978101730347</v>
+        <v>2.61978077888489</v>
       </c>
       <c r="H571" t="n">
         <v>581272</v>
@@ -17247,7 +17247,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.7426130771637</v>
+        <v>2.74261331558228</v>
       </c>
       <c r="H582" t="n">
         <v>328175</v>
@@ -17305,7 +17305,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.7675633430481</v>
+        <v>2.76756358146667</v>
       </c>
       <c r="H584" t="n">
         <v>285733</v>
@@ -17334,7 +17334,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.784836769104</v>
+        <v>2.78483653068542</v>
       </c>
       <c r="H585" t="n">
         <v>250096</v>
@@ -17421,7 +17421,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574354171753</v>
+        <v>2.71574330329895</v>
       </c>
       <c r="H588" t="n">
         <v>505464</v>
@@ -17450,7 +17450,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301672935486</v>
+        <v>2.73301696777344</v>
       </c>
       <c r="H589" t="n">
         <v>256840</v>
@@ -17508,7 +17508,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958208084106</v>
+        <v>2.71958231925964</v>
       </c>
       <c r="H591" t="n">
         <v>1596803</v>
@@ -17595,7 +17595,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735862731934</v>
+        <v>2.67735838890076</v>
       </c>
       <c r="H594" t="n">
         <v>422850</v>
@@ -17624,7 +17624,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190524101257</v>
+        <v>2.71190500259399</v>
       </c>
       <c r="H595" t="n">
         <v>576828</v>
@@ -17682,7 +17682,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H597" t="n">
         <v>284034</v>
@@ -17711,7 +17711,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.7042281627655</v>
+        <v>2.70422792434692</v>
       </c>
       <c r="H598" t="n">
         <v>201687</v>
@@ -17827,7 +17827,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6927125453949</v>
+        <v>2.69271230697632</v>
       </c>
       <c r="H602" t="n">
         <v>368932</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533988952637</v>
+        <v>2.72533965110779</v>
       </c>
       <c r="H603" t="n">
         <v>435948</v>
@@ -17972,7 +17972,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.3721969127655</v>
+        <v>2.37219715118408</v>
       </c>
       <c r="H607" t="n">
         <v>1221882</v>
@@ -80183,6 +80183,35 @@
         <v>540856</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.267500013113022</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.268999993801117</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.263999998569489</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.263000011444092</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.263000011444092</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>37157</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GEO.MI.xlsx
+++ b/data/GEO.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>3.59599804878235</v>
+        <v>3.59599781036377</v>
       </c>
       <c r="H3" t="n">
         <v>611692</v>
@@ -572,7 +572,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37930393218994</v>
+        <v>3.37930417060852</v>
       </c>
       <c r="H7" t="n">
         <v>489296</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>3.44655394554138</v>
+        <v>3.44655418395996</v>
       </c>
       <c r="H8" t="n">
         <v>335339</v>
@@ -717,7 +717,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G12" t="n">
-        <v>3.32886672019958</v>
+        <v>3.32886648178101</v>
       </c>
       <c r="H12" t="n">
         <v>597600</v>
@@ -804,7 +804,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.38864421844482</v>
+        <v>3.3886444568634</v>
       </c>
       <c r="H15" t="n">
         <v>742869</v>
@@ -862,7 +862,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G17" t="n">
-        <v>3.43160963058472</v>
+        <v>3.43160939216614</v>
       </c>
       <c r="H17" t="n">
         <v>415584</v>
@@ -891,7 +891,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52127623558044</v>
+        <v>3.52127575874329</v>
       </c>
       <c r="H18" t="n">
         <v>372353</v>
@@ -949,7 +949,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G20" t="n">
-        <v>3.36062359809875</v>
+        <v>3.36062383651733</v>
       </c>
       <c r="H20" t="n">
         <v>463309</v>
@@ -1007,7 +1007,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G22" t="n">
-        <v>3.31579041481018</v>
+        <v>3.3157901763916</v>
       </c>
       <c r="H22" t="n">
         <v>1122003</v>
@@ -1094,7 +1094,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>3.25788068771362</v>
+        <v>3.2578809261322</v>
       </c>
       <c r="H25" t="n">
         <v>832589</v>
@@ -1181,7 +1181,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>2.64329195022583</v>
+        <v>2.64329218864441</v>
       </c>
       <c r="H28" t="n">
         <v>888507</v>
@@ -1210,7 +1210,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77405571937561</v>
+        <v>2.77405548095703</v>
       </c>
       <c r="H29" t="n">
         <v>784919</v>
@@ -1297,7 +1297,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72922253608704</v>
+        <v>2.72922229766846</v>
       </c>
       <c r="H32" t="n">
         <v>485309</v>
@@ -1442,7 +1442,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G37" t="n">
-        <v>2.57604217529297</v>
+        <v>2.57604193687439</v>
       </c>
       <c r="H37" t="n">
         <v>886852</v>
@@ -1471,7 +1471,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52747273445129</v>
+        <v>2.52747297286987</v>
       </c>
       <c r="H38" t="n">
         <v>913911</v>
@@ -1500,7 +1500,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46395921707153</v>
+        <v>2.46395945549011</v>
       </c>
       <c r="H39" t="n">
         <v>414034</v>
@@ -1529,7 +1529,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.53120923042297</v>
+        <v>2.53120899200439</v>
       </c>
       <c r="H40" t="n">
         <v>622697</v>
@@ -1587,7 +1587,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G42" t="n">
-        <v>2.77592372894287</v>
+        <v>2.77592349052429</v>
       </c>
       <c r="H42" t="n">
         <v>2052418</v>
@@ -1616,7 +1616,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>2.76471519470215</v>
+        <v>2.76471543312073</v>
       </c>
       <c r="H43" t="n">
         <v>1274763</v>
@@ -1645,7 +1645,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>2.76471519470215</v>
+        <v>2.76471543312073</v>
       </c>
       <c r="H44" t="n">
         <v>1144614</v>
@@ -1674,7 +1674,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G45" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H45" t="n">
         <v>644573</v>
@@ -1703,7 +1703,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G46" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H46" t="n">
         <v>1083110</v>
@@ -1790,7 +1790,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G49" t="n">
-        <v>2.62274384498596</v>
+        <v>2.62274360656738</v>
       </c>
       <c r="H49" t="n">
         <v>618759</v>
@@ -1819,7 +1819,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78526425361633</v>
+        <v>2.78526401519775</v>
       </c>
       <c r="H50" t="n">
         <v>3240146</v>
@@ -1848,7 +1848,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>2.78339576721191</v>
+        <v>2.78339600563049</v>
       </c>
       <c r="H51" t="n">
         <v>927105</v>
@@ -1906,7 +1906,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>2.76471519470215</v>
+        <v>2.76471543312073</v>
       </c>
       <c r="H53" t="n">
         <v>939951</v>
@@ -1935,7 +1935,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G54" t="n">
-        <v>2.73856258392334</v>
+        <v>2.73856282234192</v>
       </c>
       <c r="H54" t="n">
         <v>631029</v>
@@ -1964,7 +1964,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G55" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H55" t="n">
         <v>571416</v>
@@ -1993,7 +1993,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>2.75350689888</v>
+        <v>2.75350713729858</v>
       </c>
       <c r="H56" t="n">
         <v>617931</v>
@@ -2022,7 +2022,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>2.74603509902954</v>
+        <v>2.74603486061096</v>
       </c>
       <c r="H57" t="n">
         <v>468215</v>
@@ -2080,7 +2080,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G59" t="n">
-        <v>2.71988224983215</v>
+        <v>2.71988201141357</v>
       </c>
       <c r="H59" t="n">
         <v>486311</v>
@@ -2138,7 +2138,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>2.65076446533203</v>
+        <v>2.65076422691345</v>
       </c>
       <c r="H61" t="n">
         <v>421361</v>
@@ -2167,7 +2167,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G62" t="n">
-        <v>2.68625688552856</v>
+        <v>2.68625712394714</v>
       </c>
       <c r="H62" t="n">
         <v>751565</v>
@@ -2254,7 +2254,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>2.64889645576477</v>
+        <v>2.64889597892761</v>
       </c>
       <c r="H65" t="n">
         <v>389941</v>
@@ -2370,7 +2370,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G69" t="n">
-        <v>2.57791018486023</v>
+        <v>2.57791042327881</v>
       </c>
       <c r="H69" t="n">
         <v>847648</v>
@@ -2399,7 +2399,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G70" t="n">
-        <v>2.56296586990356</v>
+        <v>2.56296563148499</v>
       </c>
       <c r="H70" t="n">
         <v>616769</v>
@@ -2486,7 +2486,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G73" t="n">
-        <v>2.58911871910095</v>
+        <v>2.58911848068237</v>
       </c>
       <c r="H73" t="n">
         <v>526922</v>
@@ -2689,7 +2689,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>2.68065309524536</v>
+        <v>2.68065285682678</v>
       </c>
       <c r="H80" t="n">
         <v>263802</v>
@@ -2834,7 +2834,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G85" t="n">
-        <v>2.65263223648071</v>
+        <v>2.65263247489929</v>
       </c>
       <c r="H85" t="n">
         <v>83792</v>
@@ -2863,7 +2863,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G86" t="n">
-        <v>2.63208365440369</v>
+        <v>2.63208413124084</v>
       </c>
       <c r="H86" t="n">
         <v>115454</v>
@@ -2892,7 +2892,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G87" t="n">
-        <v>2.62087559700012</v>
+        <v>2.62087535858154</v>
       </c>
       <c r="H87" t="n">
         <v>251095</v>
@@ -2921,7 +2921,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>2.62461161613464</v>
+        <v>2.62461137771606</v>
       </c>
       <c r="H88" t="n">
         <v>90442</v>
@@ -2950,7 +2950,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G89" t="n">
-        <v>2.58911871910095</v>
+        <v>2.58911848068237</v>
       </c>
       <c r="H89" t="n">
         <v>154887</v>
@@ -2979,7 +2979,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G90" t="n">
-        <v>2.51066017150879</v>
+        <v>2.51066040992737</v>
       </c>
       <c r="H90" t="n">
         <v>447636</v>
@@ -3066,7 +3066,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G93" t="n">
-        <v>2.58538222312927</v>
+        <v>2.58538246154785</v>
       </c>
       <c r="H93" t="n">
         <v>366421</v>
@@ -3095,7 +3095,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G94" t="n">
-        <v>2.56483387947083</v>
+        <v>2.5648341178894</v>
       </c>
       <c r="H94" t="n">
         <v>359206</v>
@@ -3153,7 +3153,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>2.65450024604797</v>
+        <v>2.65450048446655</v>
       </c>
       <c r="H96" t="n">
         <v>228387</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G104" t="n">
-        <v>2.84971308708191</v>
+        <v>2.84971284866333</v>
       </c>
       <c r="H104" t="n">
         <v>323531</v>
@@ -3414,7 +3414,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88783621788025</v>
+        <v>2.88783645629883</v>
       </c>
       <c r="H105" t="n">
         <v>248649</v>
@@ -3443,7 +3443,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G106" t="n">
-        <v>2.93358421325684</v>
+        <v>2.93358445167542</v>
       </c>
       <c r="H106" t="n">
         <v>403679</v>
@@ -3472,7 +3472,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92595958709717</v>
+        <v>2.92595934867859</v>
       </c>
       <c r="H107" t="n">
         <v>323008</v>
@@ -3762,7 +3762,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G117" t="n">
-        <v>2.73153066635132</v>
+        <v>2.7315309047699</v>
       </c>
       <c r="H117" t="n">
         <v>277740</v>
@@ -3878,7 +3878,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G121" t="n">
-        <v>2.89546084403992</v>
+        <v>2.8954610824585</v>
       </c>
       <c r="H121" t="n">
         <v>241175</v>
@@ -4081,7 +4081,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>2.65719079971313</v>
+        <v>2.65719056129456</v>
       </c>
       <c r="H128" t="n">
         <v>191013</v>
@@ -4110,7 +4110,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G129" t="n">
-        <v>2.72200012207031</v>
+        <v>2.72199988365173</v>
       </c>
       <c r="H129" t="n">
         <v>335865</v>
@@ -4139,7 +4139,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>2.59619355201721</v>
+        <v>2.59619331359863</v>
       </c>
       <c r="H130" t="n">
         <v>222114</v>
@@ -4197,7 +4197,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G132" t="n">
-        <v>2.46276211738586</v>
+        <v>2.46276235580444</v>
       </c>
       <c r="H132" t="n">
         <v>543169</v>
@@ -4226,7 +4226,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>2.4780113697052</v>
+        <v>2.47801113128662</v>
       </c>
       <c r="H133" t="n">
         <v>352159</v>
@@ -4255,7 +4255,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G134" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563575744629</v>
       </c>
       <c r="H134" t="n">
         <v>360643</v>
@@ -4313,7 +4313,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.57141351699829</v>
+        <v>2.57141327857971</v>
       </c>
       <c r="H136" t="n">
         <v>548868</v>
@@ -4458,7 +4458,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>2.53329014778137</v>
+        <v>2.53328990936279</v>
       </c>
       <c r="H141" t="n">
         <v>619648</v>
@@ -4487,7 +4487,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G142" t="n">
-        <v>2.59428739547729</v>
+        <v>2.59428691864014</v>
       </c>
       <c r="H142" t="n">
         <v>656732</v>
@@ -4574,7 +4574,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>2.6400351524353</v>
+        <v>2.64003491401672</v>
       </c>
       <c r="H145" t="n">
         <v>342261</v>
@@ -4632,7 +4632,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G147" t="n">
-        <v>2.65719079971313</v>
+        <v>2.65719056129456</v>
       </c>
       <c r="H147" t="n">
         <v>531605</v>
@@ -4661,7 +4661,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G148" t="n">
-        <v>2.6533784866333</v>
+        <v>2.65337824821472</v>
       </c>
       <c r="H148" t="n">
         <v>325972</v>
@@ -4690,7 +4690,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G149" t="n">
-        <v>2.4551374912262</v>
+        <v>2.45513725280762</v>
       </c>
       <c r="H149" t="n">
         <v>1587031</v>
@@ -4719,7 +4719,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>2.37698483467102</v>
+        <v>2.37698459625244</v>
       </c>
       <c r="H150" t="n">
         <v>918463</v>
@@ -4748,7 +4748,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G151" t="n">
-        <v>2.3140811920166</v>
+        <v>2.31408143043518</v>
       </c>
       <c r="H151" t="n">
         <v>639368</v>
@@ -4835,7 +4835,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G154" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H154" t="n">
         <v>314927</v>
@@ -4980,7 +4980,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>2.33504915237427</v>
+        <v>2.33504939079285</v>
       </c>
       <c r="H159" t="n">
         <v>248797</v>
@@ -5067,7 +5067,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>2.21114873886108</v>
+        <v>2.2111485004425</v>
       </c>
       <c r="H162" t="n">
         <v>380323</v>
@@ -5212,7 +5212,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G167" t="n">
-        <v>2.22258567810059</v>
+        <v>2.22258543968201</v>
       </c>
       <c r="H167" t="n">
         <v>324769</v>
@@ -5299,7 +5299,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G170" t="n">
-        <v>2.176837682724</v>
+        <v>2.17683744430542</v>
       </c>
       <c r="H170" t="n">
         <v>631538</v>
@@ -5328,7 +5328,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G171" t="n">
-        <v>2.22449207305908</v>
+        <v>2.2244918346405</v>
       </c>
       <c r="H171" t="n">
         <v>376315</v>
@@ -5386,7 +5386,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G173" t="n">
-        <v>2.26070880889893</v>
+        <v>2.2607090473175</v>
       </c>
       <c r="H173" t="n">
         <v>145572</v>
@@ -5444,7 +5444,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G175" t="n">
-        <v>2.22449207305908</v>
+        <v>2.2244918346405</v>
       </c>
       <c r="H175" t="n">
         <v>209639</v>
@@ -5502,7 +5502,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G177" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H177" t="n">
         <v>239497</v>
@@ -5531,7 +5531,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23211622238159</v>
+        <v>2.23211646080017</v>
       </c>
       <c r="H178" t="n">
         <v>189602</v>
@@ -5560,7 +5560,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G179" t="n">
-        <v>2.19780516624451</v>
+        <v>2.19780540466309</v>
       </c>
       <c r="H179" t="n">
         <v>319118</v>
@@ -5618,7 +5618,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G181" t="n">
-        <v>2.14633917808533</v>
+        <v>2.14633893966675</v>
       </c>
       <c r="H181" t="n">
         <v>324447</v>
@@ -5647,7 +5647,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G182" t="n">
-        <v>2.12727761268616</v>
+        <v>2.12727737426758</v>
       </c>
       <c r="H182" t="n">
         <v>624125</v>
@@ -5676,7 +5676,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.07771706581116</v>
+        <v>2.07771754264832</v>
       </c>
       <c r="H183" t="n">
         <v>428647</v>
@@ -5705,7 +5705,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G184" t="n">
-        <v>2.07771706581116</v>
+        <v>2.07771754264832</v>
       </c>
       <c r="H184" t="n">
         <v>406878</v>
@@ -5734,7 +5734,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G185" t="n">
-        <v>2.05484294891357</v>
+        <v>2.05484318733215</v>
       </c>
       <c r="H185" t="n">
         <v>188205</v>
@@ -5821,7 +5821,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G188" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H188" t="n">
         <v>141186</v>
@@ -5908,7 +5908,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G191" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H191" t="n">
         <v>217002</v>
@@ -5937,7 +5937,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G192" t="n">
-        <v>1.98812747001648</v>
+        <v>1.98812758922577</v>
       </c>
       <c r="H192" t="n">
         <v>240368</v>
@@ -6024,7 +6024,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G195" t="n">
-        <v>1.96525371074677</v>
+        <v>1.96525359153748</v>
       </c>
       <c r="H195" t="n">
         <v>560311</v>
@@ -6053,7 +6053,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G196" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H196" t="n">
         <v>598584</v>
@@ -6082,7 +6082,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G197" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H197" t="n">
         <v>249799</v>
@@ -6111,7 +6111,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G198" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000445842743</v>
       </c>
       <c r="H198" t="n">
         <v>370597</v>
@@ -6169,7 +6169,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G200" t="n">
-        <v>1.95191061496735</v>
+        <v>1.95191049575806</v>
       </c>
       <c r="H200" t="n">
         <v>1432038</v>
@@ -6285,7 +6285,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96144139766693</v>
+        <v>1.96144151687622</v>
       </c>
       <c r="H204" t="n">
         <v>352781</v>
@@ -6430,7 +6430,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>1.91759955883026</v>
+        <v>1.91759967803955</v>
       </c>
       <c r="H209" t="n">
         <v>998577</v>
@@ -6459,7 +6459,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>1.8871009349823</v>
+        <v>1.88710105419159</v>
       </c>
       <c r="H210" t="n">
         <v>691856</v>
@@ -6517,7 +6517,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>1.89186644554138</v>
+        <v>1.89186632633209</v>
       </c>
       <c r="H212" t="n">
         <v>467560</v>
@@ -6633,7 +6633,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G216" t="n">
-        <v>1.84802448749542</v>
+        <v>1.84802460670471</v>
       </c>
       <c r="H216" t="n">
         <v>332041</v>
@@ -6691,7 +6691,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G218" t="n">
-        <v>1.81657290458679</v>
+        <v>1.81657302379608</v>
       </c>
       <c r="H218" t="n">
         <v>381126</v>
@@ -6720,7 +6720,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G219" t="n">
-        <v>1.82038533687592</v>
+        <v>1.82038509845734</v>
       </c>
       <c r="H219" t="n">
         <v>227009</v>
@@ -6807,7 +6807,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95762872695923</v>
+        <v>1.95762884616852</v>
       </c>
       <c r="H222" t="n">
         <v>2654520</v>
@@ -7068,7 +7068,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>1.80608892440796</v>
+        <v>1.80608904361725</v>
       </c>
       <c r="H231" t="n">
         <v>343567</v>
@@ -7184,7 +7184,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G235" t="n">
-        <v>1.75081038475037</v>
+        <v>1.75081026554108</v>
       </c>
       <c r="H235" t="n">
         <v>480374</v>
@@ -7213,7 +7213,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G236" t="n">
-        <v>1.77559041976929</v>
+        <v>1.77559053897858</v>
       </c>
       <c r="H236" t="n">
         <v>499172</v>
@@ -7242,7 +7242,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G237" t="n">
-        <v>1.74509179592133</v>
+        <v>1.74509191513062</v>
       </c>
       <c r="H237" t="n">
         <v>547803</v>
@@ -7271,7 +7271,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G238" t="n">
-        <v>1.77082502841949</v>
+        <v>1.77082514762878</v>
       </c>
       <c r="H238" t="n">
         <v>468353</v>
@@ -7300,7 +7300,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>1.77273118495941</v>
+        <v>1.77273106575012</v>
       </c>
       <c r="H239" t="n">
         <v>570721</v>
@@ -7329,7 +7329,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G240" t="n">
-        <v>1.79465198516846</v>
+        <v>1.79465210437775</v>
       </c>
       <c r="H240" t="n">
         <v>447469</v>
@@ -7387,7 +7387,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G242" t="n">
-        <v>1.85660231113434</v>
+        <v>1.85660243034363</v>
       </c>
       <c r="H242" t="n">
         <v>464622</v>
@@ -7416,7 +7416,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G243" t="n">
-        <v>1.84993088245392</v>
+        <v>1.84993076324463</v>
       </c>
       <c r="H243" t="n">
         <v>467341</v>
@@ -7590,7 +7590,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G249" t="n">
-        <v>1.95953500270844</v>
+        <v>1.95953512191772</v>
       </c>
       <c r="H249" t="n">
         <v>720423</v>
@@ -7619,7 +7619,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G250" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H250" t="n">
         <v>638755</v>
@@ -7648,7 +7648,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G251" t="n">
-        <v>1.96144139766693</v>
+        <v>1.96144151687622</v>
       </c>
       <c r="H251" t="n">
         <v>332742</v>
@@ -7677,7 +7677,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H252" t="n">
         <v>603474</v>
@@ -7706,7 +7706,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H253" t="n">
         <v>461640</v>
@@ -7735,7 +7735,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G254" t="n">
-        <v>1.97097206115723</v>
+        <v>1.97097218036652</v>
       </c>
       <c r="H254" t="n">
         <v>225821</v>
@@ -7764,7 +7764,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G255" t="n">
-        <v>1.99575245380402</v>
+        <v>1.99575233459473</v>
       </c>
       <c r="H255" t="n">
         <v>1478455</v>
@@ -7793,7 +7793,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G256" t="n">
-        <v>2.00528311729431</v>
+        <v>2.00528287887573</v>
       </c>
       <c r="H256" t="n">
         <v>1223137</v>
@@ -7851,7 +7851,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G258" t="n">
-        <v>2.14252686500549</v>
+        <v>2.14252662658691</v>
       </c>
       <c r="H258" t="n">
         <v>1054327</v>
@@ -7880,7 +7880,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G259" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H259" t="n">
         <v>1171318</v>
@@ -7909,7 +7909,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.05674934387207</v>
+        <v>2.05674958229065</v>
       </c>
       <c r="H260" t="n">
         <v>1146682</v>
@@ -7938,7 +7938,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G261" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H261" t="n">
         <v>1109093</v>
@@ -8054,7 +8054,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="n">
-        <v>2.12727761268616</v>
+        <v>2.12727737426758</v>
       </c>
       <c r="H265" t="n">
         <v>1746792</v>
@@ -8257,7 +8257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.93475496768951</v>
+        <v>1.9347550868988</v>
       </c>
       <c r="H272" t="n">
         <v>1120465</v>
@@ -8286,7 +8286,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G273" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H273" t="n">
         <v>655413</v>
@@ -8344,7 +8344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>1.97287833690643</v>
+        <v>1.97287809848785</v>
       </c>
       <c r="H275" t="n">
         <v>590585</v>
@@ -8373,7 +8373,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G276" t="n">
-        <v>1.95381665229797</v>
+        <v>1.95381653308868</v>
       </c>
       <c r="H276" t="n">
         <v>465152</v>
@@ -8402,7 +8402,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.99765837192535</v>
+        <v>1.99765813350677</v>
       </c>
       <c r="H277" t="n">
         <v>1178960</v>
@@ -8605,7 +8605,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G284" t="n">
-        <v>1.81657290458679</v>
+        <v>1.81657302379608</v>
       </c>
       <c r="H284" t="n">
         <v>431389</v>
@@ -8750,7 +8750,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G289" t="n">
-        <v>1.94237983226776</v>
+        <v>1.94237995147705</v>
       </c>
       <c r="H289" t="n">
         <v>792908</v>
@@ -8895,7 +8895,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G294" t="n">
-        <v>1.92141199111938</v>
+        <v>1.9214118719101</v>
       </c>
       <c r="H294" t="n">
         <v>315857</v>
@@ -9011,7 +9011,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G298" t="n">
-        <v>1.95000422000885</v>
+        <v>1.95000445842743</v>
       </c>
       <c r="H298" t="n">
         <v>1498299</v>
@@ -9040,7 +9040,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>1.95572280883789</v>
+        <v>1.95572292804718</v>
       </c>
       <c r="H299" t="n">
         <v>494953</v>
@@ -9069,7 +9069,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>1.97478449344635</v>
+        <v>1.97478437423706</v>
       </c>
       <c r="H300" t="n">
         <v>1084282</v>
@@ -9098,7 +9098,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G301" t="n">
-        <v>1.95762872695923</v>
+        <v>1.95762884616852</v>
       </c>
       <c r="H301" t="n">
         <v>941040</v>
@@ -9156,7 +9156,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G303" t="n">
-        <v>1.87471091747284</v>
+        <v>1.87471079826355</v>
       </c>
       <c r="H303" t="n">
         <v>726032</v>
@@ -9185,7 +9185,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G304" t="n">
-        <v>1.87661695480347</v>
+        <v>1.87661707401276</v>
       </c>
       <c r="H304" t="n">
         <v>488529</v>
@@ -9272,7 +9272,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>1.8871009349823</v>
+        <v>1.88710105419159</v>
       </c>
       <c r="H307" t="n">
         <v>569597</v>
@@ -9330,7 +9330,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G309" t="n">
-        <v>1.9900336265564</v>
+        <v>1.99003386497498</v>
       </c>
       <c r="H309" t="n">
         <v>821834</v>
@@ -9359,7 +9359,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G310" t="n">
-        <v>2.0148138999939</v>
+        <v>2.01481413841248</v>
       </c>
       <c r="H310" t="n">
         <v>1837811</v>
@@ -9388,7 +9388,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G311" t="n">
-        <v>2.0853419303894</v>
+        <v>2.08534169197083</v>
       </c>
       <c r="H311" t="n">
         <v>3113532</v>
@@ -9475,7 +9475,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.04912495613098</v>
+        <v>2.0491247177124</v>
       </c>
       <c r="H314" t="n">
         <v>1011370</v>
@@ -9562,7 +9562,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G317" t="n">
-        <v>2.16730690002441</v>
+        <v>2.16730666160583</v>
       </c>
       <c r="H317" t="n">
         <v>2091344</v>
@@ -9620,7 +9620,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G319" t="n">
-        <v>2.35029864311218</v>
+        <v>2.3502984046936</v>
       </c>
       <c r="H319" t="n">
         <v>3123574</v>
@@ -9736,7 +9736,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G323" t="n">
-        <v>2.28548908233643</v>
+        <v>2.28548884391785</v>
       </c>
       <c r="H323" t="n">
         <v>900752</v>
@@ -9939,7 +9939,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>2.30645704269409</v>
+        <v>2.30645680427551</v>
       </c>
       <c r="H330" t="n">
         <v>409387</v>
@@ -10055,7 +10055,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G334" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H334" t="n">
         <v>425667</v>
@@ -10084,7 +10084,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G335" t="n">
-        <v>2.3159875869751</v>
+        <v>2.31598734855652</v>
       </c>
       <c r="H335" t="n">
         <v>541475</v>
@@ -10142,7 +10142,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G337" t="n">
-        <v>2.42463874816895</v>
+        <v>2.42463850975037</v>
       </c>
       <c r="H337" t="n">
         <v>563874</v>
@@ -10171,7 +10171,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>2.42082643508911</v>
+        <v>2.42082667350769</v>
       </c>
       <c r="H338" t="n">
         <v>795192</v>
@@ -10200,7 +10200,7 @@
         <v>2.5</v>
       </c>
       <c r="G339" t="n">
-        <v>2.38270306587219</v>
+        <v>2.38270330429077</v>
       </c>
       <c r="H339" t="n">
         <v>350392</v>
@@ -10316,7 +10316,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G343" t="n">
-        <v>2.41129565238953</v>
+        <v>2.41129541397095</v>
       </c>
       <c r="H343" t="n">
         <v>830346</v>
@@ -10403,7 +10403,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G346" t="n">
-        <v>2.48563599586487</v>
+        <v>2.48563575744629</v>
       </c>
       <c r="H346" t="n">
         <v>1281154</v>
@@ -10490,7 +10490,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G349" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578338623047</v>
       </c>
       <c r="H349" t="n">
         <v>873271</v>
@@ -10519,7 +10519,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578338623047</v>
       </c>
       <c r="H350" t="n">
         <v>855548</v>
@@ -10548,7 +10548,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G351" t="n">
-        <v>2.68578290939331</v>
+        <v>2.68578338623047</v>
       </c>
       <c r="H351" t="n">
         <v>812058</v>
@@ -10577,7 +10577,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>2.57331967353821</v>
+        <v>2.57331943511963</v>
       </c>
       <c r="H352" t="n">
         <v>1478509</v>
@@ -10693,7 +10693,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G356" t="n">
-        <v>2.60058856010437</v>
+        <v>2.60058832168579</v>
       </c>
       <c r="H356" t="n">
         <v>605694</v>
@@ -10925,7 +10925,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>2.70806670188904</v>
+        <v>2.70806646347046</v>
       </c>
       <c r="H364" t="n">
         <v>849448</v>
@@ -10983,7 +10983,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>2.77715992927551</v>
+        <v>2.77715969085693</v>
       </c>
       <c r="H366" t="n">
         <v>1578655</v>
@@ -11128,7 +11128,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H371" t="n">
         <v>692586</v>
@@ -11157,7 +11157,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G372" t="n">
-        <v>2.72917866706848</v>
+        <v>2.7291784286499</v>
       </c>
       <c r="H372" t="n">
         <v>600785</v>
@@ -11331,7 +11331,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G378" t="n">
-        <v>2.82514119148254</v>
+        <v>2.82514095306396</v>
       </c>
       <c r="H378" t="n">
         <v>369015</v>
@@ -11447,7 +11447,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H382" t="n">
         <v>194578</v>
@@ -11534,7 +11534,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G385" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H385" t="n">
         <v>512623</v>
@@ -11621,7 +11621,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>2.89807271957397</v>
+        <v>2.8980724811554</v>
       </c>
       <c r="H388" t="n">
         <v>1185420</v>
@@ -11766,7 +11766,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H393" t="n">
         <v>1082817</v>
@@ -11795,7 +11795,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G394" t="n">
-        <v>2.93645763397217</v>
+        <v>2.93645787239075</v>
       </c>
       <c r="H394" t="n">
         <v>382748</v>
@@ -11940,7 +11940,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>3.00363159179688</v>
+        <v>3.00363183021545</v>
       </c>
       <c r="H399" t="n">
         <v>217171</v>
@@ -11969,7 +11969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>3.14757537841797</v>
+        <v>3.14757561683655</v>
       </c>
       <c r="H400" t="n">
         <v>1320738</v>
@@ -12288,7 +12288,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G411" t="n">
-        <v>3.29343891143799</v>
+        <v>3.29343867301941</v>
       </c>
       <c r="H411" t="n">
         <v>758243</v>
@@ -12375,7 +12375,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H414" t="n">
         <v>480519</v>
@@ -12462,7 +12462,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G417" t="n">
-        <v>3.22818422317505</v>
+        <v>3.22818446159363</v>
       </c>
       <c r="H417" t="n">
         <v>285532</v>
@@ -12491,7 +12491,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G418" t="n">
-        <v>3.19747638702393</v>
+        <v>3.19747614860535</v>
       </c>
       <c r="H418" t="n">
         <v>195515</v>
@@ -12636,7 +12636,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G423" t="n">
-        <v>3.18596076965332</v>
+        <v>3.18596053123474</v>
       </c>
       <c r="H423" t="n">
         <v>127820</v>
@@ -12694,7 +12694,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.08040189743042</v>
+        <v>3.08040165901184</v>
       </c>
       <c r="H425" t="n">
         <v>401854</v>
@@ -12752,7 +12752,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G427" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H427" t="n">
         <v>748285</v>
@@ -12781,7 +12781,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G428" t="n">
-        <v>3.20707225799561</v>
+        <v>3.20707249641418</v>
       </c>
       <c r="H428" t="n">
         <v>535469</v>
@@ -12839,7 +12839,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G430" t="n">
-        <v>3.18020272254944</v>
+        <v>3.18020296096802</v>
       </c>
       <c r="H430" t="n">
         <v>159000</v>
@@ -13042,7 +13042,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G437" t="n">
-        <v>3.21858787536621</v>
+        <v>3.21858811378479</v>
       </c>
       <c r="H437" t="n">
         <v>851102</v>
@@ -13100,7 +13100,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G439" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H439" t="n">
         <v>269780</v>
@@ -13129,7 +13129,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G440" t="n">
-        <v>3.27616548538208</v>
+        <v>3.27616572380066</v>
       </c>
       <c r="H440" t="n">
         <v>183536</v>
@@ -13245,7 +13245,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H444" t="n">
         <v>548564</v>
@@ -13303,7 +13303,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G446" t="n">
-        <v>3.50647592544556</v>
+        <v>3.50647616386414</v>
       </c>
       <c r="H446" t="n">
         <v>1496771</v>
@@ -13361,7 +13361,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G448" t="n">
-        <v>3.46809101104736</v>
+        <v>3.46809077262878</v>
       </c>
       <c r="H448" t="n">
         <v>331930</v>
@@ -13622,7 +13622,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G457" t="n">
-        <v>3.39899778366089</v>
+        <v>3.39899802207947</v>
       </c>
       <c r="H457" t="n">
         <v>786922</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>3.45465612411499</v>
+        <v>3.45465588569641</v>
       </c>
       <c r="H458" t="n">
         <v>169837</v>
@@ -13680,7 +13680,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G459" t="n">
-        <v>3.44889855384827</v>
+        <v>3.44889831542969</v>
       </c>
       <c r="H459" t="n">
         <v>96243</v>
@@ -14028,7 +14028,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>3.57940745353699</v>
+        <v>3.57940769195557</v>
       </c>
       <c r="H471" t="n">
         <v>517225</v>
@@ -14086,7 +14086,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G473" t="n">
-        <v>3.69264364242554</v>
+        <v>3.69264340400696</v>
       </c>
       <c r="H473" t="n">
         <v>1575544</v>
@@ -14115,7 +14115,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G474" t="n">
-        <v>3.63122749328613</v>
+        <v>3.63122725486755</v>
       </c>
       <c r="H474" t="n">
         <v>392936</v>
@@ -14173,7 +14173,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G476" t="n">
-        <v>3.51223397254944</v>
+        <v>3.51223373413086</v>
       </c>
       <c r="H476" t="n">
         <v>1052005</v>
@@ -14289,7 +14289,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H480" t="n">
         <v>1897823</v>
@@ -14318,7 +14318,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H481" t="n">
         <v>1344877</v>
@@ -14376,7 +14376,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49502944946289</v>
+        <v>2.49502921104431</v>
       </c>
       <c r="H483" t="n">
         <v>1113397</v>
@@ -14434,7 +14434,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G485" t="n">
-        <v>2.86736440658569</v>
+        <v>2.86736464500427</v>
       </c>
       <c r="H485" t="n">
         <v>2335973</v>
@@ -14637,7 +14637,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G492" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H492" t="n">
         <v>360031</v>
@@ -14840,7 +14840,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G499" t="n">
-        <v>2.8481719493866</v>
+        <v>2.84817218780518</v>
       </c>
       <c r="H499" t="n">
         <v>177776</v>
@@ -14956,7 +14956,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G503" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H503" t="n">
         <v>781804</v>
@@ -15014,7 +15014,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G505" t="n">
-        <v>2.81938314437866</v>
+        <v>2.81938338279724</v>
       </c>
       <c r="H505" t="n">
         <v>362332</v>
@@ -15043,7 +15043,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G506" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H506" t="n">
         <v>249155</v>
@@ -15072,7 +15072,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H507" t="n">
         <v>199788</v>
@@ -15101,7 +15101,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G508" t="n">
-        <v>2.70230865478516</v>
+        <v>2.70230889320374</v>
       </c>
       <c r="H508" t="n">
         <v>228947</v>
@@ -15130,7 +15130,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G509" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H509" t="n">
         <v>305291</v>
@@ -15275,7 +15275,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G514" t="n">
-        <v>2.86928391456604</v>
+        <v>2.86928367614746</v>
       </c>
       <c r="H514" t="n">
         <v>468533</v>
@@ -15420,7 +15420,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.80211019515991</v>
+        <v>2.80210995674133</v>
       </c>
       <c r="H519" t="n">
         <v>477584</v>
@@ -15478,7 +15478,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.7541286945343</v>
+        <v>2.75412845611572</v>
       </c>
       <c r="H521" t="n">
         <v>402806</v>
@@ -15565,7 +15565,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G524" t="n">
-        <v>2.73877453804016</v>
+        <v>2.73877477645874</v>
       </c>
       <c r="H524" t="n">
         <v>549359</v>
@@ -15594,7 +15594,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G525" t="n">
-        <v>2.57563805580139</v>
+        <v>2.57563829421997</v>
       </c>
       <c r="H525" t="n">
         <v>7158793</v>
@@ -15652,7 +15652,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G527" t="n">
-        <v>2.70614743232727</v>
+        <v>2.70614719390869</v>
       </c>
       <c r="H527" t="n">
         <v>1136471</v>
@@ -15739,7 +15739,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G530" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H530" t="n">
         <v>821537</v>
@@ -15797,7 +15797,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G532" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H532" t="n">
         <v>874097</v>
@@ -15942,7 +15942,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.5430109500885</v>
+        <v>2.54301071166992</v>
       </c>
       <c r="H537" t="n">
         <v>1383977</v>
@@ -16377,7 +16377,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73685526847839</v>
+        <v>2.73685550689697</v>
       </c>
       <c r="H552" t="n">
         <v>1598171</v>
@@ -16406,7 +16406,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H553" t="n">
         <v>899641</v>
@@ -16435,7 +16435,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G554" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H554" t="n">
         <v>740489</v>
@@ -16464,7 +16464,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G555" t="n">
-        <v>2.68503570556641</v>
+        <v>2.68503546714783</v>
       </c>
       <c r="H555" t="n">
         <v>586866</v>
@@ -16522,7 +16522,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G557" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H557" t="n">
         <v>744218</v>
@@ -16638,7 +16638,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G561" t="n">
-        <v>2.83281779289246</v>
+        <v>2.83281803131104</v>
       </c>
       <c r="H561" t="n">
         <v>568824</v>
@@ -16667,7 +16667,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G562" t="n">
-        <v>2.80019068717957</v>
+        <v>2.80019092559814</v>
       </c>
       <c r="H562" t="n">
         <v>509608</v>
@@ -16783,7 +16783,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G566" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H566" t="n">
         <v>264829</v>
@@ -16812,7 +16812,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75028991699219</v>
+        <v>2.75029015541077</v>
       </c>
       <c r="H567" t="n">
         <v>219381</v>
@@ -16870,7 +16870,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G569" t="n">
-        <v>2.66008543968201</v>
+        <v>2.66008520126343</v>
       </c>
       <c r="H569" t="n">
         <v>328641</v>
@@ -16928,7 +16928,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.61978077888489</v>
+        <v>2.61978101730347</v>
       </c>
       <c r="H571" t="n">
         <v>581272</v>
@@ -17247,7 +17247,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74261331558228</v>
+        <v>2.7426130771637</v>
       </c>
       <c r="H582" t="n">
         <v>328175</v>
@@ -17305,7 +17305,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G584" t="n">
-        <v>2.76756358146667</v>
+        <v>2.7675633430481</v>
       </c>
       <c r="H584" t="n">
         <v>285733</v>
@@ -17334,7 +17334,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78483653068542</v>
+        <v>2.784836769104</v>
       </c>
       <c r="H585" t="n">
         <v>250096</v>
@@ -17421,7 +17421,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.71574330329895</v>
+        <v>2.71574354171753</v>
       </c>
       <c r="H588" t="n">
         <v>505464</v>
@@ -17450,7 +17450,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73301696777344</v>
+        <v>2.73301672935486</v>
       </c>
       <c r="H589" t="n">
         <v>256840</v>
@@ -17508,7 +17508,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G591" t="n">
-        <v>2.71958231925964</v>
+        <v>2.71958208084106</v>
       </c>
       <c r="H591" t="n">
         <v>1596803</v>
@@ -17595,7 +17595,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>2.67735838890076</v>
+        <v>2.67735862731934</v>
       </c>
       <c r="H594" t="n">
         <v>422850</v>
@@ -17624,7 +17624,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G595" t="n">
-        <v>2.71190500259399</v>
+        <v>2.71190524101257</v>
       </c>
       <c r="H595" t="n">
         <v>576828</v>
@@ -17682,7 +17682,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G597" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H597" t="n">
         <v>284034</v>
@@ -17711,7 +17711,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G598" t="n">
-        <v>2.70422792434692</v>
+        <v>2.7042281627655</v>
       </c>
       <c r="H598" t="n">
         <v>201687</v>
@@ -17827,7 +17827,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>2.69271230697632</v>
+        <v>2.6927125453949</v>
       </c>
       <c r="H602" t="n">
         <v>368932</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.72533965110779</v>
+        <v>2.72533988952637</v>
       </c>
       <c r="H603" t="n">
         <v>435948</v>
@@ -17972,7 +17972,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G607" t="n">
-        <v>2.37219715118408</v>
+        <v>2.3721969127655</v>
       </c>
       <c r="H607" t="n">
         <v>1221882</v>
@@ -80200,7 +80200,7 @@
         <v>0.268999993801117</v>
       </c>
       <c r="E2753" t="n">
-        <v>0.263999998569489</v>
+        <v>0.263000011444092</v>
       </c>
       <c r="F2753" t="n">
         <v>0.263000011444092</v>
@@ -80209,9 +80209,38 @@
         <v>0.263000011444092</v>
       </c>
       <c r="H2753" t="n">
-        <v>37157</v>
+        <v>50976</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>0.261500000953674</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>165172</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
